--- a/results-table.xlsx
+++ b/results-table.xlsx
@@ -334,6 +334,81 @@
   </cellStyleXfs>
   <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -352,86 +427,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -556,6 +556,44 @@
         <a:xfrm>
           <a:off x="9328589" y="10871263"/>
           <a:ext cx="7832286" cy="6131796"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>103</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>155238</xdr:colOff>
+      <xdr:row>122</xdr:row>
+      <xdr:rowOff>128633</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Рисунок 5"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="612588" y="19259176"/>
+          <a:ext cx="13632179" cy="3677163"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -858,758 +896,753 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="7" t="s">
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="8"/>
-      <c r="J1" s="8"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
     </row>
     <row r="2" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="4"/>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="8"/>
+      <c r="A2" s="31"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="34"/>
+      <c r="J2" s="34"/>
     </row>
     <row r="5" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="12">
+      <c r="A5" s="1">
         <v>45839</v>
       </c>
     </row>
     <row r="6" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="9" t="s">
+      <c r="A6" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="11"/>
-      <c r="J6" s="24" t="s">
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="35"/>
+      <c r="J6" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="K6" s="25"/>
-      <c r="L6" s="25"/>
-      <c r="M6" s="25"/>
-      <c r="N6" s="25"/>
-      <c r="O6" s="26"/>
+      <c r="K6" s="10"/>
+      <c r="L6" s="10"/>
+      <c r="M6" s="10"/>
+      <c r="N6" s="10"/>
+      <c r="O6" s="11"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A7" s="15" t="s">
+      <c r="A7" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="13"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="16"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="14"/>
-      <c r="L7" s="14"/>
-      <c r="M7" s="14"/>
-      <c r="N7" s="14"/>
-      <c r="O7" s="27"/>
+      <c r="B7" s="21"/>
+      <c r="C7" s="21"/>
+      <c r="D7" s="21"/>
+      <c r="E7" s="21"/>
+      <c r="F7" s="22"/>
+      <c r="J7" s="12"/>
+      <c r="K7" s="13"/>
+      <c r="L7" s="13"/>
+      <c r="M7" s="13"/>
+      <c r="N7" s="13"/>
+      <c r="O7" s="14"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A8" s="17"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="18"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="14"/>
-      <c r="L8" s="14"/>
-      <c r="M8" s="14"/>
-      <c r="N8" s="14"/>
-      <c r="O8" s="27"/>
+      <c r="A8" s="23"/>
+      <c r="B8" s="13"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="24"/>
+      <c r="J8" s="12"/>
+      <c r="K8" s="13"/>
+      <c r="L8" s="13"/>
+      <c r="M8" s="13"/>
+      <c r="N8" s="13"/>
+      <c r="O8" s="14"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A9" s="17"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="18"/>
-      <c r="J9" s="7"/>
-      <c r="K9" s="14"/>
-      <c r="L9" s="14"/>
-      <c r="M9" s="14"/>
-      <c r="N9" s="14"/>
-      <c r="O9" s="27"/>
+      <c r="A9" s="23"/>
+      <c r="B9" s="13"/>
+      <c r="C9" s="13"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="24"/>
+      <c r="J9" s="12"/>
+      <c r="K9" s="13"/>
+      <c r="L9" s="13"/>
+      <c r="M9" s="13"/>
+      <c r="N9" s="13"/>
+      <c r="O9" s="14"/>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A10" s="19"/>
-      <c r="B10" s="20"/>
-      <c r="C10" s="20"/>
-      <c r="D10" s="20"/>
-      <c r="E10" s="20"/>
-      <c r="F10" s="21"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="14"/>
-      <c r="L10" s="14"/>
-      <c r="M10" s="14"/>
-      <c r="N10" s="14"/>
-      <c r="O10" s="27"/>
+      <c r="A10" s="25"/>
+      <c r="B10" s="26"/>
+      <c r="C10" s="26"/>
+      <c r="D10" s="26"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="27"/>
+      <c r="J10" s="12"/>
+      <c r="K10" s="13"/>
+      <c r="L10" s="13"/>
+      <c r="M10" s="13"/>
+      <c r="N10" s="13"/>
+      <c r="O10" s="14"/>
     </row>
     <row r="11" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="15" t="s">
+      <c r="A11" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="13"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="16"/>
-      <c r="J11" s="7"/>
-      <c r="K11" s="14"/>
-      <c r="L11" s="14"/>
-      <c r="M11" s="14"/>
-      <c r="N11" s="14"/>
-      <c r="O11" s="27"/>
+      <c r="B11" s="21"/>
+      <c r="C11" s="21"/>
+      <c r="D11" s="21"/>
+      <c r="E11" s="21"/>
+      <c r="F11" s="22"/>
+      <c r="J11" s="12"/>
+      <c r="K11" s="13"/>
+      <c r="L11" s="13"/>
+      <c r="M11" s="13"/>
+      <c r="N11" s="13"/>
+      <c r="O11" s="14"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A12" s="17"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="18"/>
-      <c r="J12" s="7"/>
-      <c r="K12" s="14"/>
-      <c r="L12" s="14"/>
-      <c r="M12" s="14"/>
-      <c r="N12" s="14"/>
-      <c r="O12" s="27"/>
+      <c r="A12" s="23"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="24"/>
+      <c r="J12" s="12"/>
+      <c r="K12" s="13"/>
+      <c r="L12" s="13"/>
+      <c r="M12" s="13"/>
+      <c r="N12" s="13"/>
+      <c r="O12" s="14"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A13" s="17"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="18"/>
-      <c r="J13" s="7"/>
-      <c r="K13" s="14"/>
-      <c r="L13" s="14"/>
-      <c r="M13" s="14"/>
-      <c r="N13" s="14"/>
-      <c r="O13" s="27"/>
+      <c r="A13" s="23"/>
+      <c r="B13" s="13"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="24"/>
+      <c r="J13" s="12"/>
+      <c r="K13" s="13"/>
+      <c r="L13" s="13"/>
+      <c r="M13" s="13"/>
+      <c r="N13" s="13"/>
+      <c r="O13" s="14"/>
     </row>
     <row r="14" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="19"/>
-      <c r="B14" s="20"/>
-      <c r="C14" s="20"/>
-      <c r="D14" s="20"/>
-      <c r="E14" s="20"/>
-      <c r="F14" s="21"/>
-      <c r="J14" s="28"/>
-      <c r="K14" s="29"/>
-      <c r="L14" s="29"/>
-      <c r="M14" s="29"/>
-      <c r="N14" s="29"/>
-      <c r="O14" s="30"/>
+      <c r="A14" s="25"/>
+      <c r="B14" s="26"/>
+      <c r="C14" s="26"/>
+      <c r="D14" s="26"/>
+      <c r="E14" s="26"/>
+      <c r="F14" s="27"/>
+      <c r="J14" s="15"/>
+      <c r="K14" s="16"/>
+      <c r="L14" s="16"/>
+      <c r="M14" s="16"/>
+      <c r="N14" s="16"/>
+      <c r="O14" s="17"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A15" s="32"/>
-      <c r="B15" s="32"/>
+      <c r="A15" s="8"/>
+      <c r="B15" s="8"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A16" s="22" t="s">
+      <c r="A16" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="B16" s="23"/>
+      <c r="B16" s="19"/>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A17" s="33" t="s">
+      <c r="A17" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A25" s="31" t="s">
+      <c r="A25" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A52" s="15" t="s">
+      <c r="A52" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="B52" s="13"/>
-      <c r="C52" s="13"/>
-      <c r="D52" s="13"/>
-      <c r="E52" s="13"/>
-      <c r="F52" s="13"/>
-      <c r="G52" s="13"/>
-      <c r="H52" s="13"/>
-      <c r="I52" s="13"/>
-      <c r="J52" s="13"/>
-      <c r="K52" s="13"/>
-      <c r="L52" s="13"/>
-      <c r="M52" s="13"/>
-      <c r="N52" s="13"/>
-      <c r="O52" s="16"/>
+      <c r="B52" s="21"/>
+      <c r="C52" s="21"/>
+      <c r="D52" s="21"/>
+      <c r="E52" s="21"/>
+      <c r="F52" s="21"/>
+      <c r="G52" s="21"/>
+      <c r="H52" s="21"/>
+      <c r="I52" s="21"/>
+      <c r="J52" s="21"/>
+      <c r="K52" s="21"/>
+      <c r="L52" s="21"/>
+      <c r="M52" s="21"/>
+      <c r="N52" s="21"/>
+      <c r="O52" s="22"/>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A53" s="17"/>
-      <c r="B53" s="14"/>
-      <c r="C53" s="14"/>
-      <c r="D53" s="14"/>
-      <c r="E53" s="14"/>
-      <c r="F53" s="14"/>
-      <c r="G53" s="14"/>
-      <c r="H53" s="14"/>
-      <c r="I53" s="14"/>
-      <c r="J53" s="14"/>
-      <c r="K53" s="14"/>
-      <c r="L53" s="14"/>
-      <c r="M53" s="14"/>
-      <c r="N53" s="14"/>
-      <c r="O53" s="18"/>
+      <c r="A53" s="23"/>
+      <c r="B53" s="13"/>
+      <c r="C53" s="13"/>
+      <c r="D53" s="13"/>
+      <c r="E53" s="13"/>
+      <c r="F53" s="13"/>
+      <c r="G53" s="13"/>
+      <c r="H53" s="13"/>
+      <c r="I53" s="13"/>
+      <c r="J53" s="13"/>
+      <c r="K53" s="13"/>
+      <c r="L53" s="13"/>
+      <c r="M53" s="13"/>
+      <c r="N53" s="13"/>
+      <c r="O53" s="24"/>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A54" s="17"/>
-      <c r="B54" s="14"/>
-      <c r="C54" s="14"/>
-      <c r="D54" s="14"/>
-      <c r="E54" s="14"/>
-      <c r="F54" s="14"/>
-      <c r="G54" s="14"/>
-      <c r="H54" s="14"/>
-      <c r="I54" s="14"/>
-      <c r="J54" s="14"/>
-      <c r="K54" s="14"/>
-      <c r="L54" s="14"/>
-      <c r="M54" s="14"/>
-      <c r="N54" s="14"/>
-      <c r="O54" s="18"/>
+      <c r="A54" s="23"/>
+      <c r="B54" s="13"/>
+      <c r="C54" s="13"/>
+      <c r="D54" s="13"/>
+      <c r="E54" s="13"/>
+      <c r="F54" s="13"/>
+      <c r="G54" s="13"/>
+      <c r="H54" s="13"/>
+      <c r="I54" s="13"/>
+      <c r="J54" s="13"/>
+      <c r="K54" s="13"/>
+      <c r="L54" s="13"/>
+      <c r="M54" s="13"/>
+      <c r="N54" s="13"/>
+      <c r="O54" s="24"/>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A55" s="17"/>
-      <c r="B55" s="14"/>
-      <c r="C55" s="14"/>
-      <c r="D55" s="14"/>
-      <c r="E55" s="14"/>
-      <c r="F55" s="14"/>
-      <c r="G55" s="14"/>
-      <c r="H55" s="14"/>
-      <c r="I55" s="14"/>
-      <c r="J55" s="14"/>
-      <c r="K55" s="14"/>
-      <c r="L55" s="14"/>
-      <c r="M55" s="14"/>
-      <c r="N55" s="14"/>
-      <c r="O55" s="18"/>
+      <c r="A55" s="23"/>
+      <c r="B55" s="13"/>
+      <c r="C55" s="13"/>
+      <c r="D55" s="13"/>
+      <c r="E55" s="13"/>
+      <c r="F55" s="13"/>
+      <c r="G55" s="13"/>
+      <c r="H55" s="13"/>
+      <c r="I55" s="13"/>
+      <c r="J55" s="13"/>
+      <c r="K55" s="13"/>
+      <c r="L55" s="13"/>
+      <c r="M55" s="13"/>
+      <c r="N55" s="13"/>
+      <c r="O55" s="24"/>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A56" s="17"/>
-      <c r="B56" s="14"/>
-      <c r="C56" s="14"/>
-      <c r="D56" s="14"/>
-      <c r="E56" s="14"/>
-      <c r="F56" s="14"/>
-      <c r="G56" s="14"/>
-      <c r="H56" s="14"/>
-      <c r="I56" s="14"/>
-      <c r="J56" s="14"/>
-      <c r="K56" s="14"/>
-      <c r="L56" s="14"/>
-      <c r="M56" s="14"/>
-      <c r="N56" s="14"/>
-      <c r="O56" s="18"/>
+      <c r="A56" s="23"/>
+      <c r="B56" s="13"/>
+      <c r="C56" s="13"/>
+      <c r="D56" s="13"/>
+      <c r="E56" s="13"/>
+      <c r="F56" s="13"/>
+      <c r="G56" s="13"/>
+      <c r="H56" s="13"/>
+      <c r="I56" s="13"/>
+      <c r="J56" s="13"/>
+      <c r="K56" s="13"/>
+      <c r="L56" s="13"/>
+      <c r="M56" s="13"/>
+      <c r="N56" s="13"/>
+      <c r="O56" s="24"/>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A57" s="19"/>
-      <c r="B57" s="20"/>
-      <c r="C57" s="20"/>
-      <c r="D57" s="20"/>
-      <c r="E57" s="20"/>
-      <c r="F57" s="20"/>
-      <c r="G57" s="20"/>
-      <c r="H57" s="20"/>
-      <c r="I57" s="20"/>
-      <c r="J57" s="20"/>
-      <c r="K57" s="20"/>
-      <c r="L57" s="20"/>
-      <c r="M57" s="20"/>
-      <c r="N57" s="20"/>
-      <c r="O57" s="21"/>
+      <c r="A57" s="25"/>
+      <c r="B57" s="26"/>
+      <c r="C57" s="26"/>
+      <c r="D57" s="26"/>
+      <c r="E57" s="26"/>
+      <c r="F57" s="26"/>
+      <c r="G57" s="26"/>
+      <c r="H57" s="26"/>
+      <c r="I57" s="26"/>
+      <c r="J57" s="26"/>
+      <c r="K57" s="26"/>
+      <c r="L57" s="26"/>
+      <c r="M57" s="26"/>
+      <c r="N57" s="26"/>
+      <c r="O57" s="27"/>
     </row>
     <row r="59" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="15" t="s">
+      <c r="A59" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="B59" s="13"/>
-      <c r="C59" s="13"/>
-      <c r="D59" s="13"/>
-      <c r="E59" s="13"/>
-      <c r="F59" s="13"/>
-      <c r="G59" s="13"/>
-      <c r="H59" s="13"/>
-      <c r="I59" s="13"/>
-      <c r="J59" s="13"/>
-      <c r="K59" s="13"/>
-      <c r="L59" s="13"/>
-      <c r="M59" s="13"/>
-      <c r="N59" s="13"/>
-      <c r="O59" s="16"/>
+      <c r="B59" s="21"/>
+      <c r="C59" s="21"/>
+      <c r="D59" s="21"/>
+      <c r="E59" s="21"/>
+      <c r="F59" s="21"/>
+      <c r="G59" s="21"/>
+      <c r="H59" s="21"/>
+      <c r="I59" s="21"/>
+      <c r="J59" s="21"/>
+      <c r="K59" s="21"/>
+      <c r="L59" s="21"/>
+      <c r="M59" s="21"/>
+      <c r="N59" s="21"/>
+      <c r="O59" s="22"/>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A60" s="17"/>
-      <c r="B60" s="14"/>
-      <c r="C60" s="14"/>
-      <c r="D60" s="14"/>
-      <c r="E60" s="14"/>
-      <c r="F60" s="14"/>
-      <c r="G60" s="14"/>
-      <c r="H60" s="14"/>
-      <c r="I60" s="14"/>
-      <c r="J60" s="14"/>
-      <c r="K60" s="14"/>
-      <c r="L60" s="14"/>
-      <c r="M60" s="14"/>
-      <c r="N60" s="14"/>
-      <c r="O60" s="18"/>
+      <c r="A60" s="23"/>
+      <c r="B60" s="13"/>
+      <c r="C60" s="13"/>
+      <c r="D60" s="13"/>
+      <c r="E60" s="13"/>
+      <c r="F60" s="13"/>
+      <c r="G60" s="13"/>
+      <c r="H60" s="13"/>
+      <c r="I60" s="13"/>
+      <c r="J60" s="13"/>
+      <c r="K60" s="13"/>
+      <c r="L60" s="13"/>
+      <c r="M60" s="13"/>
+      <c r="N60" s="13"/>
+      <c r="O60" s="24"/>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A61" s="17"/>
-      <c r="B61" s="14"/>
-      <c r="C61" s="14"/>
-      <c r="D61" s="14"/>
-      <c r="E61" s="14"/>
-      <c r="F61" s="14"/>
-      <c r="G61" s="14"/>
-      <c r="H61" s="14"/>
-      <c r="I61" s="14"/>
-      <c r="J61" s="14"/>
-      <c r="K61" s="14"/>
-      <c r="L61" s="14"/>
-      <c r="M61" s="14"/>
-      <c r="N61" s="14"/>
-      <c r="O61" s="18"/>
+      <c r="A61" s="23"/>
+      <c r="B61" s="13"/>
+      <c r="C61" s="13"/>
+      <c r="D61" s="13"/>
+      <c r="E61" s="13"/>
+      <c r="F61" s="13"/>
+      <c r="G61" s="13"/>
+      <c r="H61" s="13"/>
+      <c r="I61" s="13"/>
+      <c r="J61" s="13"/>
+      <c r="K61" s="13"/>
+      <c r="L61" s="13"/>
+      <c r="M61" s="13"/>
+      <c r="N61" s="13"/>
+      <c r="O61" s="24"/>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A62" s="17"/>
-      <c r="B62" s="14"/>
-      <c r="C62" s="14"/>
-      <c r="D62" s="14"/>
-      <c r="E62" s="14"/>
-      <c r="F62" s="14"/>
-      <c r="G62" s="14"/>
-      <c r="H62" s="14"/>
-      <c r="I62" s="14"/>
-      <c r="J62" s="14"/>
-      <c r="K62" s="14"/>
-      <c r="L62" s="14"/>
-      <c r="M62" s="14"/>
-      <c r="N62" s="14"/>
-      <c r="O62" s="18"/>
+      <c r="A62" s="23"/>
+      <c r="B62" s="13"/>
+      <c r="C62" s="13"/>
+      <c r="D62" s="13"/>
+      <c r="E62" s="13"/>
+      <c r="F62" s="13"/>
+      <c r="G62" s="13"/>
+      <c r="H62" s="13"/>
+      <c r="I62" s="13"/>
+      <c r="J62" s="13"/>
+      <c r="K62" s="13"/>
+      <c r="L62" s="13"/>
+      <c r="M62" s="13"/>
+      <c r="N62" s="13"/>
+      <c r="O62" s="24"/>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A63" s="17"/>
-      <c r="B63" s="14"/>
-      <c r="C63" s="14"/>
-      <c r="D63" s="14"/>
-      <c r="E63" s="14"/>
-      <c r="F63" s="14"/>
-      <c r="G63" s="14"/>
-      <c r="H63" s="14"/>
-      <c r="I63" s="14"/>
-      <c r="J63" s="14"/>
-      <c r="K63" s="14"/>
-      <c r="L63" s="14"/>
-      <c r="M63" s="14"/>
-      <c r="N63" s="14"/>
-      <c r="O63" s="18"/>
+      <c r="A63" s="23"/>
+      <c r="B63" s="13"/>
+      <c r="C63" s="13"/>
+      <c r="D63" s="13"/>
+      <c r="E63" s="13"/>
+      <c r="F63" s="13"/>
+      <c r="G63" s="13"/>
+      <c r="H63" s="13"/>
+      <c r="I63" s="13"/>
+      <c r="J63" s="13"/>
+      <c r="K63" s="13"/>
+      <c r="L63" s="13"/>
+      <c r="M63" s="13"/>
+      <c r="N63" s="13"/>
+      <c r="O63" s="24"/>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A64" s="17"/>
-      <c r="B64" s="14"/>
-      <c r="C64" s="14"/>
-      <c r="D64" s="14"/>
-      <c r="E64" s="14"/>
-      <c r="F64" s="14"/>
-      <c r="G64" s="14"/>
-      <c r="H64" s="14"/>
-      <c r="I64" s="14"/>
-      <c r="J64" s="14"/>
-      <c r="K64" s="14"/>
-      <c r="L64" s="14"/>
-      <c r="M64" s="14"/>
-      <c r="N64" s="14"/>
-      <c r="O64" s="18"/>
+      <c r="A64" s="23"/>
+      <c r="B64" s="13"/>
+      <c r="C64" s="13"/>
+      <c r="D64" s="13"/>
+      <c r="E64" s="13"/>
+      <c r="F64" s="13"/>
+      <c r="G64" s="13"/>
+      <c r="H64" s="13"/>
+      <c r="I64" s="13"/>
+      <c r="J64" s="13"/>
+      <c r="K64" s="13"/>
+      <c r="L64" s="13"/>
+      <c r="M64" s="13"/>
+      <c r="N64" s="13"/>
+      <c r="O64" s="24"/>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A65" s="17"/>
-      <c r="B65" s="14"/>
-      <c r="C65" s="14"/>
-      <c r="D65" s="14"/>
-      <c r="E65" s="14"/>
-      <c r="F65" s="14"/>
-      <c r="G65" s="14"/>
-      <c r="H65" s="14"/>
-      <c r="I65" s="14"/>
-      <c r="J65" s="14"/>
-      <c r="K65" s="14"/>
-      <c r="L65" s="14"/>
-      <c r="M65" s="14"/>
-      <c r="N65" s="14"/>
-      <c r="O65" s="18"/>
+      <c r="A65" s="23"/>
+      <c r="B65" s="13"/>
+      <c r="C65" s="13"/>
+      <c r="D65" s="13"/>
+      <c r="E65" s="13"/>
+      <c r="F65" s="13"/>
+      <c r="G65" s="13"/>
+      <c r="H65" s="13"/>
+      <c r="I65" s="13"/>
+      <c r="J65" s="13"/>
+      <c r="K65" s="13"/>
+      <c r="L65" s="13"/>
+      <c r="M65" s="13"/>
+      <c r="N65" s="13"/>
+      <c r="O65" s="24"/>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A66" s="17"/>
-      <c r="B66" s="14"/>
-      <c r="C66" s="14"/>
-      <c r="D66" s="14"/>
-      <c r="E66" s="14"/>
-      <c r="F66" s="14"/>
-      <c r="G66" s="14"/>
-      <c r="H66" s="14"/>
-      <c r="I66" s="14"/>
-      <c r="J66" s="14"/>
-      <c r="K66" s="14"/>
-      <c r="L66" s="14"/>
-      <c r="M66" s="14"/>
-      <c r="N66" s="14"/>
-      <c r="O66" s="18"/>
+      <c r="A66" s="23"/>
+      <c r="B66" s="13"/>
+      <c r="C66" s="13"/>
+      <c r="D66" s="13"/>
+      <c r="E66" s="13"/>
+      <c r="F66" s="13"/>
+      <c r="G66" s="13"/>
+      <c r="H66" s="13"/>
+      <c r="I66" s="13"/>
+      <c r="J66" s="13"/>
+      <c r="K66" s="13"/>
+      <c r="L66" s="13"/>
+      <c r="M66" s="13"/>
+      <c r="N66" s="13"/>
+      <c r="O66" s="24"/>
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A67" s="17"/>
-      <c r="B67" s="14"/>
-      <c r="C67" s="14"/>
-      <c r="D67" s="14"/>
-      <c r="E67" s="14"/>
-      <c r="F67" s="14"/>
-      <c r="G67" s="14"/>
-      <c r="H67" s="14"/>
-      <c r="I67" s="14"/>
-      <c r="J67" s="14"/>
-      <c r="K67" s="14"/>
-      <c r="L67" s="14"/>
-      <c r="M67" s="14"/>
-      <c r="N67" s="14"/>
-      <c r="O67" s="18"/>
+      <c r="A67" s="23"/>
+      <c r="B67" s="13"/>
+      <c r="C67" s="13"/>
+      <c r="D67" s="13"/>
+      <c r="E67" s="13"/>
+      <c r="F67" s="13"/>
+      <c r="G67" s="13"/>
+      <c r="H67" s="13"/>
+      <c r="I67" s="13"/>
+      <c r="J67" s="13"/>
+      <c r="K67" s="13"/>
+      <c r="L67" s="13"/>
+      <c r="M67" s="13"/>
+      <c r="N67" s="13"/>
+      <c r="O67" s="24"/>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A68" s="17"/>
-      <c r="B68" s="14"/>
-      <c r="C68" s="14"/>
-      <c r="D68" s="14"/>
-      <c r="E68" s="14"/>
-      <c r="F68" s="14"/>
-      <c r="G68" s="14"/>
-      <c r="H68" s="14"/>
-      <c r="I68" s="14"/>
-      <c r="J68" s="14"/>
-      <c r="K68" s="14"/>
-      <c r="L68" s="14"/>
-      <c r="M68" s="14"/>
-      <c r="N68" s="14"/>
-      <c r="O68" s="18"/>
+      <c r="A68" s="23"/>
+      <c r="B68" s="13"/>
+      <c r="C68" s="13"/>
+      <c r="D68" s="13"/>
+      <c r="E68" s="13"/>
+      <c r="F68" s="13"/>
+      <c r="G68" s="13"/>
+      <c r="H68" s="13"/>
+      <c r="I68" s="13"/>
+      <c r="J68" s="13"/>
+      <c r="K68" s="13"/>
+      <c r="L68" s="13"/>
+      <c r="M68" s="13"/>
+      <c r="N68" s="13"/>
+      <c r="O68" s="24"/>
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A69" s="17"/>
-      <c r="B69" s="14"/>
-      <c r="C69" s="14"/>
-      <c r="D69" s="14"/>
-      <c r="E69" s="14"/>
-      <c r="F69" s="14"/>
-      <c r="G69" s="14"/>
-      <c r="H69" s="14"/>
-      <c r="I69" s="14"/>
-      <c r="J69" s="14"/>
-      <c r="K69" s="14"/>
-      <c r="L69" s="14"/>
-      <c r="M69" s="14"/>
-      <c r="N69" s="14"/>
-      <c r="O69" s="18"/>
+      <c r="A69" s="23"/>
+      <c r="B69" s="13"/>
+      <c r="C69" s="13"/>
+      <c r="D69" s="13"/>
+      <c r="E69" s="13"/>
+      <c r="F69" s="13"/>
+      <c r="G69" s="13"/>
+      <c r="H69" s="13"/>
+      <c r="I69" s="13"/>
+      <c r="J69" s="13"/>
+      <c r="K69" s="13"/>
+      <c r="L69" s="13"/>
+      <c r="M69" s="13"/>
+      <c r="N69" s="13"/>
+      <c r="O69" s="24"/>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A70" s="17"/>
-      <c r="B70" s="14"/>
-      <c r="C70" s="14"/>
-      <c r="D70" s="14"/>
-      <c r="E70" s="14"/>
-      <c r="F70" s="14"/>
-      <c r="G70" s="14"/>
-      <c r="H70" s="14"/>
-      <c r="I70" s="14"/>
-      <c r="J70" s="14"/>
-      <c r="K70" s="14"/>
-      <c r="L70" s="14"/>
-      <c r="M70" s="14"/>
-      <c r="N70" s="14"/>
-      <c r="O70" s="18"/>
+      <c r="A70" s="23"/>
+      <c r="B70" s="13"/>
+      <c r="C70" s="13"/>
+      <c r="D70" s="13"/>
+      <c r="E70" s="13"/>
+      <c r="F70" s="13"/>
+      <c r="G70" s="13"/>
+      <c r="H70" s="13"/>
+      <c r="I70" s="13"/>
+      <c r="J70" s="13"/>
+      <c r="K70" s="13"/>
+      <c r="L70" s="13"/>
+      <c r="M70" s="13"/>
+      <c r="N70" s="13"/>
+      <c r="O70" s="24"/>
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A71" s="17"/>
-      <c r="B71" s="14"/>
-      <c r="C71" s="14"/>
-      <c r="D71" s="14"/>
-      <c r="E71" s="14"/>
-      <c r="F71" s="14"/>
-      <c r="G71" s="14"/>
-      <c r="H71" s="14"/>
-      <c r="I71" s="14"/>
-      <c r="J71" s="14"/>
-      <c r="K71" s="14"/>
-      <c r="L71" s="14"/>
-      <c r="M71" s="14"/>
-      <c r="N71" s="14"/>
-      <c r="O71" s="18"/>
+      <c r="A71" s="23"/>
+      <c r="B71" s="13"/>
+      <c r="C71" s="13"/>
+      <c r="D71" s="13"/>
+      <c r="E71" s="13"/>
+      <c r="F71" s="13"/>
+      <c r="G71" s="13"/>
+      <c r="H71" s="13"/>
+      <c r="I71" s="13"/>
+      <c r="J71" s="13"/>
+      <c r="K71" s="13"/>
+      <c r="L71" s="13"/>
+      <c r="M71" s="13"/>
+      <c r="N71" s="13"/>
+      <c r="O71" s="24"/>
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A72" s="17"/>
-      <c r="B72" s="14"/>
-      <c r="C72" s="14"/>
-      <c r="D72" s="14"/>
-      <c r="E72" s="14"/>
-      <c r="F72" s="14"/>
-      <c r="G72" s="14"/>
-      <c r="H72" s="14"/>
-      <c r="I72" s="14"/>
-      <c r="J72" s="14"/>
-      <c r="K72" s="14"/>
-      <c r="L72" s="14"/>
-      <c r="M72" s="14"/>
-      <c r="N72" s="14"/>
-      <c r="O72" s="18"/>
+      <c r="A72" s="23"/>
+      <c r="B72" s="13"/>
+      <c r="C72" s="13"/>
+      <c r="D72" s="13"/>
+      <c r="E72" s="13"/>
+      <c r="F72" s="13"/>
+      <c r="G72" s="13"/>
+      <c r="H72" s="13"/>
+      <c r="I72" s="13"/>
+      <c r="J72" s="13"/>
+      <c r="K72" s="13"/>
+      <c r="L72" s="13"/>
+      <c r="M72" s="13"/>
+      <c r="N72" s="13"/>
+      <c r="O72" s="24"/>
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A73" s="19"/>
-      <c r="B73" s="20"/>
-      <c r="C73" s="20"/>
-      <c r="D73" s="20"/>
-      <c r="E73" s="20"/>
-      <c r="F73" s="20"/>
-      <c r="G73" s="20"/>
-      <c r="H73" s="20"/>
-      <c r="I73" s="20"/>
-      <c r="J73" s="20"/>
-      <c r="K73" s="20"/>
-      <c r="L73" s="20"/>
-      <c r="M73" s="20"/>
-      <c r="N73" s="20"/>
-      <c r="O73" s="21"/>
+      <c r="A73" s="25"/>
+      <c r="B73" s="26"/>
+      <c r="C73" s="26"/>
+      <c r="D73" s="26"/>
+      <c r="E73" s="26"/>
+      <c r="F73" s="26"/>
+      <c r="G73" s="26"/>
+      <c r="H73" s="26"/>
+      <c r="I73" s="26"/>
+      <c r="J73" s="26"/>
+      <c r="K73" s="26"/>
+      <c r="L73" s="26"/>
+      <c r="M73" s="26"/>
+      <c r="N73" s="26"/>
+      <c r="O73" s="27"/>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A75" s="9" t="s">
+      <c r="A75" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B75" s="10"/>
-      <c r="C75" s="10"/>
-      <c r="D75" s="34" t="s">
+      <c r="B75" s="6"/>
+      <c r="C75" s="6"/>
+      <c r="D75" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E75" s="34"/>
-      <c r="F75" s="34"/>
-      <c r="G75" s="34"/>
-      <c r="H75" s="34"/>
-      <c r="I75" s="34"/>
-      <c r="J75" s="34"/>
-      <c r="K75" s="34"/>
-      <c r="L75" s="34"/>
+      <c r="E75" s="7"/>
+      <c r="F75" s="7"/>
+      <c r="G75" s="7"/>
+      <c r="H75" s="7"/>
+      <c r="I75" s="7"/>
+      <c r="J75" s="7"/>
+      <c r="K75" s="7"/>
+      <c r="L75" s="7"/>
     </row>
     <row r="76" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="D76" s="35" t="s">
+      <c r="D76" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E76" s="35"/>
-      <c r="F76" s="35"/>
-      <c r="G76" s="35"/>
-      <c r="H76" s="35"/>
-      <c r="I76" s="35"/>
-      <c r="J76" s="35"/>
-      <c r="K76" s="35"/>
-      <c r="L76" s="35"/>
+      <c r="E76" s="4"/>
+      <c r="F76" s="4"/>
+      <c r="G76" s="4"/>
+      <c r="H76" s="4"/>
+      <c r="I76" s="4"/>
+      <c r="J76" s="4"/>
+      <c r="K76" s="4"/>
+      <c r="L76" s="4"/>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="D77" s="35"/>
-      <c r="E77" s="35"/>
-      <c r="F77" s="35"/>
-      <c r="G77" s="35"/>
-      <c r="H77" s="35"/>
-      <c r="I77" s="35"/>
-      <c r="J77" s="35"/>
-      <c r="K77" s="35"/>
-      <c r="L77" s="35"/>
+      <c r="D77" s="4"/>
+      <c r="E77" s="4"/>
+      <c r="F77" s="4"/>
+      <c r="G77" s="4"/>
+      <c r="H77" s="4"/>
+      <c r="I77" s="4"/>
+      <c r="J77" s="4"/>
+      <c r="K77" s="4"/>
+      <c r="L77" s="4"/>
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="D78" s="35"/>
-      <c r="E78" s="35"/>
-      <c r="F78" s="35"/>
-      <c r="G78" s="35"/>
-      <c r="H78" s="35"/>
-      <c r="I78" s="35"/>
-      <c r="J78" s="35"/>
-      <c r="K78" s="35"/>
-      <c r="L78" s="35"/>
+      <c r="D78" s="4"/>
+      <c r="E78" s="4"/>
+      <c r="F78" s="4"/>
+      <c r="G78" s="4"/>
+      <c r="H78" s="4"/>
+      <c r="I78" s="4"/>
+      <c r="J78" s="4"/>
+      <c r="K78" s="4"/>
+      <c r="L78" s="4"/>
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="D79" s="35"/>
-      <c r="E79" s="35"/>
-      <c r="F79" s="35"/>
-      <c r="G79" s="35"/>
-      <c r="H79" s="35"/>
-      <c r="I79" s="35"/>
-      <c r="J79" s="35"/>
-      <c r="K79" s="35"/>
-      <c r="L79" s="35"/>
+      <c r="D79" s="4"/>
+      <c r="E79" s="4"/>
+      <c r="F79" s="4"/>
+      <c r="G79" s="4"/>
+      <c r="H79" s="4"/>
+      <c r="I79" s="4"/>
+      <c r="J79" s="4"/>
+      <c r="K79" s="4"/>
+      <c r="L79" s="4"/>
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="D80" s="35"/>
-      <c r="E80" s="35"/>
-      <c r="F80" s="35"/>
-      <c r="G80" s="35"/>
-      <c r="H80" s="35"/>
-      <c r="I80" s="35"/>
-      <c r="J80" s="35"/>
-      <c r="K80" s="35"/>
-      <c r="L80" s="35"/>
+      <c r="D80" s="4"/>
+      <c r="E80" s="4"/>
+      <c r="F80" s="4"/>
+      <c r="G80" s="4"/>
+      <c r="H80" s="4"/>
+      <c r="I80" s="4"/>
+      <c r="J80" s="4"/>
+      <c r="K80" s="4"/>
+      <c r="L80" s="4"/>
     </row>
     <row r="81" spans="4:12" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="D81" s="35" t="s">
+      <c r="D81" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E81" s="35"/>
-      <c r="F81" s="35"/>
-      <c r="G81" s="35"/>
-      <c r="H81" s="35"/>
-      <c r="I81" s="35"/>
-      <c r="J81" s="35"/>
-      <c r="K81" s="35"/>
-      <c r="L81" s="35"/>
+      <c r="E81" s="4"/>
+      <c r="F81" s="4"/>
+      <c r="G81" s="4"/>
+      <c r="H81" s="4"/>
+      <c r="I81" s="4"/>
+      <c r="J81" s="4"/>
+      <c r="K81" s="4"/>
+      <c r="L81" s="4"/>
     </row>
     <row r="82" spans="4:12" x14ac:dyDescent="0.35">
-      <c r="D82" s="35"/>
-      <c r="E82" s="35"/>
-      <c r="F82" s="35"/>
-      <c r="G82" s="35"/>
-      <c r="H82" s="35"/>
-      <c r="I82" s="35"/>
-      <c r="J82" s="35"/>
-      <c r="K82" s="35"/>
-      <c r="L82" s="35"/>
+      <c r="D82" s="4"/>
+      <c r="E82" s="4"/>
+      <c r="F82" s="4"/>
+      <c r="G82" s="4"/>
+      <c r="H82" s="4"/>
+      <c r="I82" s="4"/>
+      <c r="J82" s="4"/>
+      <c r="K82" s="4"/>
+      <c r="L82" s="4"/>
     </row>
     <row r="83" spans="4:12" x14ac:dyDescent="0.35">
-      <c r="D83" s="35"/>
-      <c r="E83" s="35"/>
-      <c r="F83" s="35"/>
-      <c r="G83" s="35"/>
-      <c r="H83" s="35"/>
-      <c r="I83" s="35"/>
-      <c r="J83" s="35"/>
-      <c r="K83" s="35"/>
-      <c r="L83" s="35"/>
+      <c r="D83" s="4"/>
+      <c r="E83" s="4"/>
+      <c r="F83" s="4"/>
+      <c r="G83" s="4"/>
+      <c r="H83" s="4"/>
+      <c r="I83" s="4"/>
+      <c r="J83" s="4"/>
+      <c r="K83" s="4"/>
+      <c r="L83" s="4"/>
     </row>
     <row r="84" spans="4:12" x14ac:dyDescent="0.35">
-      <c r="D84" s="35"/>
-      <c r="E84" s="35"/>
-      <c r="F84" s="35"/>
-      <c r="G84" s="35"/>
-      <c r="H84" s="35"/>
-      <c r="I84" s="35"/>
-      <c r="J84" s="35"/>
-      <c r="K84" s="35"/>
-      <c r="L84" s="35"/>
+      <c r="D84" s="4"/>
+      <c r="E84" s="4"/>
+      <c r="F84" s="4"/>
+      <c r="G84" s="4"/>
+      <c r="H84" s="4"/>
+      <c r="I84" s="4"/>
+      <c r="J84" s="4"/>
+      <c r="K84" s="4"/>
+      <c r="L84" s="4"/>
     </row>
     <row r="85" spans="4:12" x14ac:dyDescent="0.35">
-      <c r="D85" s="35"/>
-      <c r="E85" s="35"/>
-      <c r="F85" s="35"/>
-      <c r="G85" s="35"/>
-      <c r="H85" s="35"/>
-      <c r="I85" s="35"/>
-      <c r="J85" s="35"/>
-      <c r="K85" s="35"/>
-      <c r="L85" s="35"/>
+      <c r="D85" s="4"/>
+      <c r="E85" s="4"/>
+      <c r="F85" s="4"/>
+      <c r="G85" s="4"/>
+      <c r="H85" s="4"/>
+      <c r="I85" s="4"/>
+      <c r="J85" s="4"/>
+      <c r="K85" s="4"/>
+      <c r="L85" s="4"/>
     </row>
     <row r="86" spans="4:12" x14ac:dyDescent="0.35">
-      <c r="D86" s="35"/>
-      <c r="E86" s="35"/>
-      <c r="F86" s="35"/>
-      <c r="G86" s="35"/>
-      <c r="H86" s="35"/>
-      <c r="I86" s="35"/>
-      <c r="J86" s="35"/>
-      <c r="K86" s="35"/>
-      <c r="L86" s="35"/>
+      <c r="D86" s="4"/>
+      <c r="E86" s="4"/>
+      <c r="F86" s="4"/>
+      <c r="G86" s="4"/>
+      <c r="H86" s="4"/>
+      <c r="I86" s="4"/>
+      <c r="J86" s="4"/>
+      <c r="K86" s="4"/>
+      <c r="L86" s="4"/>
     </row>
     <row r="87" spans="4:12" x14ac:dyDescent="0.35">
-      <c r="D87" s="35"/>
-      <c r="E87" s="35"/>
-      <c r="F87" s="35"/>
-      <c r="G87" s="35"/>
-      <c r="H87" s="35"/>
-      <c r="I87" s="35"/>
-      <c r="J87" s="35"/>
-      <c r="K87" s="35"/>
-      <c r="L87" s="35"/>
+      <c r="D87" s="4"/>
+      <c r="E87" s="4"/>
+      <c r="F87" s="4"/>
+      <c r="G87" s="4"/>
+      <c r="H87" s="4"/>
+      <c r="I87" s="4"/>
+      <c r="J87" s="4"/>
+      <c r="K87" s="4"/>
+      <c r="L87" s="4"/>
     </row>
     <row r="88" spans="4:12" x14ac:dyDescent="0.35">
-      <c r="D88" s="35"/>
-      <c r="E88" s="35"/>
-      <c r="F88" s="35"/>
-      <c r="G88" s="35"/>
-      <c r="H88" s="35"/>
-      <c r="I88" s="35"/>
-      <c r="J88" s="35"/>
-      <c r="K88" s="35"/>
-      <c r="L88" s="35"/>
+      <c r="D88" s="4"/>
+      <c r="E88" s="4"/>
+      <c r="F88" s="4"/>
+      <c r="G88" s="4"/>
+      <c r="H88" s="4"/>
+      <c r="I88" s="4"/>
+      <c r="J88" s="4"/>
+      <c r="K88" s="4"/>
+      <c r="L88" s="4"/>
     </row>
     <row r="89" spans="4:12" x14ac:dyDescent="0.35">
-      <c r="D89" s="35"/>
-      <c r="E89" s="35"/>
-      <c r="F89" s="35"/>
-      <c r="G89" s="35"/>
-      <c r="H89" s="35"/>
-      <c r="I89" s="35"/>
-      <c r="J89" s="35"/>
-      <c r="K89" s="35"/>
-      <c r="L89" s="35"/>
+      <c r="D89" s="4"/>
+      <c r="E89" s="4"/>
+      <c r="F89" s="4"/>
+      <c r="G89" s="4"/>
+      <c r="H89" s="4"/>
+      <c r="I89" s="4"/>
+      <c r="J89" s="4"/>
+      <c r="K89" s="4"/>
+      <c r="L89" s="4"/>
     </row>
     <row r="90" spans="4:12" x14ac:dyDescent="0.35">
-      <c r="D90" s="35"/>
-      <c r="E90" s="35"/>
-      <c r="F90" s="35"/>
-      <c r="G90" s="35"/>
-      <c r="H90" s="35"/>
-      <c r="I90" s="35"/>
-      <c r="J90" s="35"/>
-      <c r="K90" s="35"/>
-      <c r="L90" s="35"/>
+      <c r="D90" s="4"/>
+      <c r="E90" s="4"/>
+      <c r="F90" s="4"/>
+      <c r="G90" s="4"/>
+      <c r="H90" s="4"/>
+      <c r="I90" s="4"/>
+      <c r="J90" s="4"/>
+      <c r="K90" s="4"/>
+      <c r="L90" s="4"/>
     </row>
     <row r="91" spans="4:12" x14ac:dyDescent="0.35">
-      <c r="D91" s="35"/>
-      <c r="E91" s="35"/>
-      <c r="F91" s="35"/>
-      <c r="G91" s="35"/>
-      <c r="H91" s="35"/>
-      <c r="I91" s="35"/>
-      <c r="J91" s="35"/>
-      <c r="K91" s="35"/>
-      <c r="L91" s="35"/>
+      <c r="D91" s="4"/>
+      <c r="E91" s="4"/>
+      <c r="F91" s="4"/>
+      <c r="G91" s="4"/>
+      <c r="H91" s="4"/>
+      <c r="I91" s="4"/>
+      <c r="J91" s="4"/>
+      <c r="K91" s="4"/>
+      <c r="L91" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="D81:L91"/>
-    <mergeCell ref="A75:C75"/>
-    <mergeCell ref="D75:L75"/>
-    <mergeCell ref="D76:L80"/>
-    <mergeCell ref="A15:B15"/>
     <mergeCell ref="J6:O14"/>
     <mergeCell ref="A16:B16"/>
     <mergeCell ref="A52:O57"/>
@@ -1619,6 +1652,11 @@
     <mergeCell ref="A6:F6"/>
     <mergeCell ref="A7:F10"/>
     <mergeCell ref="A11:F14"/>
+    <mergeCell ref="D81:L91"/>
+    <mergeCell ref="A75:C75"/>
+    <mergeCell ref="D75:L75"/>
+    <mergeCell ref="D76:L80"/>
+    <mergeCell ref="A15:B15"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" r:id="rId1"/>

--- a/results-table.xlsx
+++ b/results-table.xlsx
@@ -16,15 +16,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="21">
   <si>
     <t>https://github.com/AntoneoDaCoder/online-compiler</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> - актуальная ссылка на репозиторий (приватный)</t>
-  </si>
-  <si>
-    <t>Создана данная таблица</t>
   </si>
   <si>
     <t>Тестирование текущей реализации компилятора - создание отдельной Job в Kybernetes на каждый запрос выполнения кода</t>
@@ -51,9 +45,6 @@
     <t>Варианты решения проблем:</t>
   </si>
   <si>
-    <t xml:space="preserve">Промежуточные выводы: даже при оптимизированном (?) варианте компиляции, в случае когда запросов не очень много (тестовый фронт послал всего 6), задержка ответа от сервера - 16 секунд (для кода, который например не попадает в установленный таймаут, для всех текущих тестов он был выставлен в 12000 мс). Для референса был использован онлайн-компилятор OneCompiler, который, если верить инструментам разработчика в браузере Google Chrome, выдавал ответ на тот же тестовый код за 6(!)мс. Для того, чтобы job долго не висела активной (например, какая-то ошибка в поде), для нее на данный момент установлен activeDeadlineSeconds как 60. В случае малого количества запросов, это не мешает, но как видно из теста даже с 5 циклами (30 запросов), происходит следующая ситуация: приходят запросы, запускаются job (из мониторинга lens видно, что сам kubernetes ставит задачи в некую очередь в случае нехватки ресурсов, выделенных по квоте), те job, которые не смогли встать в выполнение, висят в состоянии pending все то время, пока их не сможет scheduler поставить на выполнение, а activeDeadlineSeconds тем временем истекает. И к тому моменту, как высвободятся ресурсы, те job, которые не могли запуститься, автоматически убиваются kubernetesом исходя из activeDeadlineSeconds, поскольку так то, в текущем варианте, все 30 job создаются одновременно (а вот выполнение происходит по мере освобождения системных ресурсов, выделенных кластеру). Соответственно, под с кодом не запускается, запрос остается невыполненным, API не посылает callback на фронт (видно из параметра latency). Поэтому, для текущего варианта не вижу смысла проводить дальнейшие тесты с большим количеством запросов, поскольку из данных результатов очевидно, что сервер не справится. Справа скриншот из lens, который описывает ситуацию. </t>
-  </si>
-  <si>
     <t>1. Попробовать занизить запрос одного пода по памяти, скажем, до 128-96 Мб</t>
   </si>
   <si>
@@ -62,12 +53,157 @@
   <si>
     <t>3. Пересмотреть алгоритм компиляции + запуска кода. Отказаться от создания job на каждый запрос, вместо этого при старте сервера создавать некий фиксированный пул worker-job с подами, предзагружать в них dotnet (прогревать иными словами) и через какие-либо механизмы (gRPC, REST и т.д.) передавать туда код на выполнение. Либо гибридный вариант: текущий механизм компиляции + пул прогретых воркеров, но для этого потребуется переписать сам раннер так, чтобы он запускал процессы с кодом, а не через reflection, дабы не убивать контейнер раннера, а только запущенный им процесс в случае timeout/невключенной в сценарий ошибки.</t>
   </si>
+  <si>
+    <t xml:space="preserve">Примененные ограничения: кластер (CPU=2,Mem=2048Mb); лимит Pod = 96Mb, resource quota=1Gb (10 постоянно работающих подов) </t>
+  </si>
+  <si>
+    <t>10 циклов</t>
+  </si>
+  <si>
+    <t>30 циклов</t>
+  </si>
+  <si>
+    <t>Текущий вариант компиляции: улучшенный вариант предыдущего подхода (все так же компиляция в памяти), однако немного другая система управления и выполнения пользовательского кода (вместо создания раннера на каждый запрос на данный момент используется подход с некоторым фиксированным числом долгоживущих контейнеров, которые принимают запрос с сервера и вместо Reflection запускают код в отдельном процессе внутри себя). Причина миграции на текущий вариант: относительно долгий ответ от сервера с результатами + неудобство сборов результатов (требовалось раз в какое-то время опрашивать кубернетес о статусах подов и потом некрасиво их парсить) + сложности реализации таймаута и его отслеживания (предыдущий вариант приводил к потере некоторых запросов, а решение этой проблемы было некрасивым и значительно загрязняло код API)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Промежуточные выводы: данный вариант превосходит все предыдущие: 1. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Скорость</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (хотя все таки не получилось и близко достичь скорости ответа OneCompiler, данный вариант работает намного быстрее всех предыдущих, причем </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">стабильно. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Даже при большом для такого рода тестового проекта количестве одновременных запросов (60) среднее время ожидания ответа сервера менее 10 секунд, что конечно не то чтобы прям совсем быстро, но терпимо, ни в какое сравнение с предыдущими вариантами реализации); 2. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Стабильность</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (хотя в процессе разработки было обнаружено некоторое количество весьма неприятных багов, по итогу, при тестах этого варианта было совершено наименьшее количество остановок кластера и перезапуска сервера. А после всех доработок, сервер успешно продолжил работу без видимых ошибок/промедлений, выдал +- такую же скорость для 1, 5 и 10 циклов тестирования даже после одновременного получения 180 запросов на выполнение); 3. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Удобство разработки и поддержк</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">и (стало намного удобнее работать с результатами выполнения, они формируются внутри самого пода, сериализуются и отправляются по http внутри сети кубика на API; с этим отпала необходимость дергать кластер чтобы опросить поды + создавать отдельные потоки на прослушку результатов; код самого API стал намного чище, упростились почти все сервисы, само API стало чисто асинхронным, не требует никаких доп пакетов (кроме k8s для работы с кластером, на данный момент)); 4. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Безопасность </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(данный вариант наиболее безопасный из всех, поскольку помимо наложения ограничений на сам контейнер (без сети, отключен рут доступ и т.д.), сам пользовательский код выполняется внутри отдельного процесса (в связи с этим упрощаются требования к синтаксическому дереву, не надо отлавливать всякие приколы по типу Environment.Exit(), которые в предыдущем варианте бы уронили сам под, поскольку там код выполнялся в том же процессе, что и сам раннер))</t>
+    </r>
+  </si>
+  <si>
+    <t>Мои наблюдения по ресурсам (на текущий момент): 1Gb RAM в принципе достаточен под деплоймент раннеров компилятора, если не предполагается компиляции кода, написанного больше чем на 1-м языке (поскольку остальные языки либо потребуют отдельный деплоймент подов, предназначенных только для них, либо придется усложнять логику самого раннера, что в теории может потребовать больше места под сам под/больше оперативной памяти (что уменьшит общее кол-во подов, которые можно выделить из 1 гигабайта оперативы)). Под сишарп пока хватает и 96Мб на контейнер, код выполняется (хотя не писал варианты где надо скажем выделить пару-тройку массивов на больше чем 10000 элементов, возможно тут можно упереться в память, но это скорее зависит от самих задачек, который пользователь должен будет писать и отправлять на проверку)</t>
+  </si>
+  <si>
+    <t>Что можно проверить: 1. Балансировку работы с запросами (на данный момент, она заключается просто в отправке любого запроса на первый свободный под из всего деплоймента, в теории, хороший вариант по идее может немного снизить среднее время задержки). 2. Параллельная обработка нескольких запросов одним подом (на данный момент пока один под выполняет в момент времени только один пользовательский запрос, можно попробовать сделать квоту запросов которую может принять один под (например, 5), и тогда общее количество запросов которые одномоментно может обработать весь текущий кластер будет 50 вместо 10. Но поскольку 5 параллельно обрабатываемых запросов = 6 процессов внутри пода (+ основной, который запускает дочерние, слушает запросы и отправляет ответы API) = больше оперативной памяти под сам под (т.е иными словами, может не хватить 96Мб, требует тестов). В теории, если такой вариант покажет такие же или даже лучше результаты, то значит можно будет снизить необходимое количество памяти под весь деплоймент (например, 5 подов с квотой 5 запросов будут работать так же, как 10 с 1, значит можно снизить память с 1 гига до 512 мб), либо в оставшееся место воткнуть поды под другой язык); 3. Поискать варианты микрооптимизаций раннеров/api в существующих опенсорсных вариантах (опять же возвращаясь к 6мс ответу от OneCompiler)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - актуальная ссылка на репозиторий</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Промежуточные выводы: даже при оптимизированном (?) варианте компиляции, в случае когда запросов не очень много (тестовый фронт послал всего 6), задержка ответа от сервера - 16 секунд (для кода, который например не попадает в установленный таймаут, для всех текущих тестов он был выставлен в 12000 мс). Для референса был использован онлайн-компилятор OneCompiler, который, если верить инструментам разработчика в браузере Google Chrome, выдавал ответ на тот же тестовый код за +-300(!)мс. Для того, чтобы job долго не висела активной (например, какая-то ошибка в поде), для нее на данный момент установлен activeDeadlineSeconds как 60. В случае малого количества запросов, это не мешает, но как видно из теста даже с 5 циклами (30 запросов), происходит следующая ситуация: приходят запросы, запускаются job (из мониторинга lens видно, что сам kubernetes ставит задачи в некую очередь в случае нехватки ресурсов, выделенных по квоте), те job, которые не смогли встать в выполнение, висят в состоянии pending все то время, пока их не сможет scheduler поставить на выполнение, а activeDeadlineSeconds тем временем истекает. И к тому моменту, как высвободятся ресурсы, те job, которые не могли запуститься, автоматически убиваются kubernetesом исходя из activeDeadlineSeconds, поскольку так то, в текущем варианте, все 30 job создаются одновременно (а вот выполнение происходит по мере освобождения системных ресурсов, выделенных кластеру). Соответственно, под с кодом не запускается, запрос остается невыполненным, API не посылает callback на фронт (видно из параметра latency). Поэтому, для текущего варианта не вижу смысла проводить дальнейшие тесты с большим количеством запросов, поскольку из данных результатов очевидно, что сервер не справится. Справа скриншот из lens, который описывает ситуацию. </t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -85,6 +221,25 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -94,7 +249,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="22">
+  <borders count="24">
     <border>
       <left/>
       <right/>
@@ -327,16 +482,111 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -364,9 +614,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -377,36 +624,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
@@ -430,9 +647,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
@@ -453,15 +667,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>19050</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>140502</xdr:rowOff>
+      <xdr:colOff>130175</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>156377</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>532437</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>25626</xdr:rowOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>40312</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>41501</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -478,8 +692,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="628650" y="2921802"/>
-          <a:ext cx="11486187" cy="1174174"/>
+          <a:off x="733425" y="3204377"/>
+          <a:ext cx="11371887" cy="1218624"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -567,19 +781,19 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>103</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>84445</xdr:colOff>
+      <xdr:row>124</xdr:row>
+      <xdr:rowOff>151761</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>155238</xdr:colOff>
-      <xdr:row>122</xdr:row>
-      <xdr:rowOff>128633</xdr:rowOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>347250</xdr:colOff>
+      <xdr:row>131</xdr:row>
+      <xdr:rowOff>105034</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Рисунок 5"/>
+        <xdr:cNvPr id="5" name="Рисунок 4"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -592,8 +806,274 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="612588" y="19259176"/>
-          <a:ext cx="13632179" cy="3677163"/>
+          <a:off x="687695" y="23773761"/>
+          <a:ext cx="11724555" cy="1286773"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>584841</xdr:colOff>
+      <xdr:row>132</xdr:row>
+      <xdr:rowOff>31963</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>354972</xdr:colOff>
+      <xdr:row>147</xdr:row>
+      <xdr:rowOff>35064</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Рисунок 6"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="584841" y="25177963"/>
+          <a:ext cx="7104381" cy="2860601"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>43090</xdr:colOff>
+      <xdr:row>151</xdr:row>
+      <xdr:rowOff>79374</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>109881</xdr:colOff>
+      <xdr:row>182</xdr:row>
+      <xdr:rowOff>19595</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Рисунок 7"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="646340" y="28844874"/>
+          <a:ext cx="12131791" cy="5845721"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>598715</xdr:colOff>
+      <xdr:row>182</xdr:row>
+      <xdr:rowOff>111124</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>15542</xdr:colOff>
+      <xdr:row>196</xdr:row>
+      <xdr:rowOff>73391</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Рисунок 8"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="598715" y="34782124"/>
+          <a:ext cx="7354327" cy="2629267"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>201</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>144341</xdr:colOff>
+      <xdr:row>255</xdr:row>
+      <xdr:rowOff>79375</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Рисунок 9"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="95250" y="38576250"/>
+          <a:ext cx="12209341" cy="10271125"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>238125</xdr:colOff>
+      <xdr:row>256</xdr:row>
+      <xdr:rowOff>31750</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>267728</xdr:colOff>
+      <xdr:row>270</xdr:row>
+      <xdr:rowOff>155965</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="Рисунок 10"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="238125" y="48990250"/>
+          <a:ext cx="7363853" cy="2791215"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>158750</xdr:colOff>
+      <xdr:row>275</xdr:row>
+      <xdr:rowOff>174625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>54985</xdr:colOff>
+      <xdr:row>291</xdr:row>
+      <xdr:rowOff>60734</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="Рисунок 12"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="158750" y="53133625"/>
+          <a:ext cx="7230485" cy="2934110"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>54429</xdr:colOff>
+      <xdr:row>96</xdr:row>
+      <xdr:rowOff>62166</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>298379</xdr:colOff>
+      <xdr:row>115</xdr:row>
+      <xdr:rowOff>93558</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="Рисунок 13"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="54429" y="17506523"/>
+          <a:ext cx="13089093" cy="3478535"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -892,217 +1372,924 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O91"/>
+  <dimension ref="A1:AE342"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="9.90625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="12" t="s">
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="37" t="s">
+        <v>19</v>
+      </c>
+      <c r="I1" s="48"/>
+      <c r="J1" s="48"/>
+    </row>
+    <row r="2" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="45"/>
+      <c r="B2" s="46"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="46"/>
+      <c r="E2" s="46"/>
+      <c r="F2" s="46"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="37"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+    </row>
+    <row r="5" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="2"/>
+    </row>
+    <row r="6" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="22"/>
+      <c r="B6" s="22"/>
+      <c r="C6" s="22"/>
+      <c r="D6" s="22"/>
+      <c r="E6" s="22"/>
+      <c r="F6" s="22"/>
+      <c r="J6" s="34" t="s">
+        <v>3</v>
+      </c>
+      <c r="K6" s="35"/>
+      <c r="L6" s="35"/>
+      <c r="M6" s="35"/>
+      <c r="N6" s="35"/>
+      <c r="O6" s="36"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A7" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
-    </row>
-    <row r="2" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="31"/>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="33"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="34"/>
-      <c r="J2" s="34"/>
-    </row>
-    <row r="5" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="1">
-        <v>45839</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="35"/>
-      <c r="J6" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="K6" s="10"/>
-      <c r="L6" s="10"/>
-      <c r="M6" s="10"/>
-      <c r="N6" s="10"/>
-      <c r="O6" s="11"/>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A7" s="20" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="21"/>
-      <c r="C7" s="21"/>
-      <c r="D7" s="21"/>
-      <c r="E7" s="21"/>
-      <c r="F7" s="22"/>
-      <c r="J7" s="12"/>
+      <c r="B7" s="10"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="11"/>
+      <c r="J7" s="37"/>
       <c r="K7" s="13"/>
       <c r="L7" s="13"/>
       <c r="M7" s="13"/>
       <c r="N7" s="13"/>
-      <c r="O7" s="14"/>
+      <c r="O7" s="38"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A8" s="23"/>
+      <c r="A8" s="12"/>
       <c r="B8" s="13"/>
       <c r="C8" s="13"/>
       <c r="D8" s="13"/>
       <c r="E8" s="13"/>
-      <c r="F8" s="24"/>
-      <c r="J8" s="12"/>
+      <c r="F8" s="14"/>
+      <c r="J8" s="37"/>
       <c r="K8" s="13"/>
       <c r="L8" s="13"/>
       <c r="M8" s="13"/>
       <c r="N8" s="13"/>
-      <c r="O8" s="14"/>
+      <c r="O8" s="38"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A9" s="23"/>
+      <c r="A9" s="12"/>
       <c r="B9" s="13"/>
       <c r="C9" s="13"/>
       <c r="D9" s="13"/>
       <c r="E9" s="13"/>
-      <c r="F9" s="24"/>
-      <c r="J9" s="12"/>
+      <c r="F9" s="14"/>
+      <c r="J9" s="37"/>
       <c r="K9" s="13"/>
       <c r="L9" s="13"/>
       <c r="M9" s="13"/>
       <c r="N9" s="13"/>
-      <c r="O9" s="14"/>
+      <c r="O9" s="38"/>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A10" s="25"/>
-      <c r="B10" s="26"/>
-      <c r="C10" s="26"/>
-      <c r="D10" s="26"/>
-      <c r="E10" s="26"/>
-      <c r="F10" s="27"/>
-      <c r="J10" s="12"/>
+      <c r="A10" s="15"/>
+      <c r="B10" s="16"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="17"/>
+      <c r="J10" s="37"/>
       <c r="K10" s="13"/>
       <c r="L10" s="13"/>
       <c r="M10" s="13"/>
       <c r="N10" s="13"/>
-      <c r="O10" s="14"/>
+      <c r="O10" s="38"/>
     </row>
     <row r="11" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="20" t="s">
-        <v>8</v>
+      <c r="A11" s="9" t="s">
+        <v>6</v>
       </c>
-      <c r="B11" s="21"/>
-      <c r="C11" s="21"/>
-      <c r="D11" s="21"/>
-      <c r="E11" s="21"/>
-      <c r="F11" s="22"/>
-      <c r="J11" s="12"/>
+      <c r="B11" s="10"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="11"/>
+      <c r="J11" s="37"/>
       <c r="K11" s="13"/>
       <c r="L11" s="13"/>
       <c r="M11" s="13"/>
       <c r="N11" s="13"/>
-      <c r="O11" s="14"/>
+      <c r="O11" s="38"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A12" s="23"/>
+      <c r="A12" s="12"/>
       <c r="B12" s="13"/>
       <c r="C12" s="13"/>
       <c r="D12" s="13"/>
       <c r="E12" s="13"/>
-      <c r="F12" s="24"/>
-      <c r="J12" s="12"/>
+      <c r="F12" s="14"/>
+      <c r="J12" s="37"/>
       <c r="K12" s="13"/>
       <c r="L12" s="13"/>
       <c r="M12" s="13"/>
       <c r="N12" s="13"/>
-      <c r="O12" s="14"/>
+      <c r="O12" s="38"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A13" s="23"/>
+      <c r="A13" s="12"/>
       <c r="B13" s="13"/>
       <c r="C13" s="13"/>
       <c r="D13" s="13"/>
       <c r="E13" s="13"/>
-      <c r="F13" s="24"/>
-      <c r="J13" s="12"/>
+      <c r="F13" s="14"/>
+      <c r="J13" s="37"/>
       <c r="K13" s="13"/>
       <c r="L13" s="13"/>
       <c r="M13" s="13"/>
       <c r="N13" s="13"/>
-      <c r="O13" s="14"/>
+      <c r="O13" s="38"/>
     </row>
     <row r="14" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="25"/>
-      <c r="B14" s="26"/>
-      <c r="C14" s="26"/>
-      <c r="D14" s="26"/>
-      <c r="E14" s="26"/>
-      <c r="F14" s="27"/>
-      <c r="J14" s="15"/>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="16"/>
-      <c r="O14" s="17"/>
+      <c r="A14" s="15"/>
+      <c r="B14" s="16"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="17"/>
+      <c r="J14" s="39"/>
+      <c r="K14" s="40"/>
+      <c r="L14" s="40"/>
+      <c r="M14" s="40"/>
+      <c r="N14" s="40"/>
+      <c r="O14" s="41"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A15" s="8"/>
-      <c r="B15" s="8"/>
+      <c r="A15" s="33"/>
+      <c r="B15" s="33"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A16" s="18" t="s">
+      <c r="A16" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="B16" s="28"/>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A17" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B16" s="19"/>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A17" s="3" t="s">
-        <v>6</v>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="B18" s="18"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="19"/>
+      <c r="H18" s="19"/>
+      <c r="I18" s="19"/>
+      <c r="J18" s="19"/>
+      <c r="K18" s="19"/>
+      <c r="L18" s="19"/>
+      <c r="M18" s="19"/>
+      <c r="N18" s="19"/>
+      <c r="O18" s="19"/>
+      <c r="P18" s="19"/>
+      <c r="Q18" s="19"/>
+      <c r="R18" s="19"/>
+      <c r="S18" s="19"/>
+      <c r="T18" s="19"/>
+      <c r="U18" s="19"/>
+      <c r="V18" s="20"/>
+    </row>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="B19" s="21"/>
+      <c r="C19" s="22"/>
+      <c r="D19" s="22"/>
+      <c r="E19" s="22"/>
+      <c r="F19" s="22"/>
+      <c r="G19" s="22"/>
+      <c r="H19" s="22"/>
+      <c r="I19" s="22"/>
+      <c r="J19" s="22"/>
+      <c r="K19" s="22"/>
+      <c r="L19" s="22"/>
+      <c r="M19" s="22"/>
+      <c r="N19" s="22"/>
+      <c r="O19" s="22"/>
+      <c r="P19" s="22"/>
+      <c r="Q19" s="22"/>
+      <c r="R19" s="22"/>
+      <c r="S19" s="22"/>
+      <c r="T19" s="22"/>
+      <c r="U19" s="22"/>
+      <c r="V19" s="23"/>
+    </row>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="B20" s="21"/>
+      <c r="C20" s="22"/>
+      <c r="D20" s="22"/>
+      <c r="E20" s="22"/>
+      <c r="F20" s="22"/>
+      <c r="G20" s="22"/>
+      <c r="H20" s="22"/>
+      <c r="I20" s="22"/>
+      <c r="J20" s="22"/>
+      <c r="K20" s="22"/>
+      <c r="L20" s="22"/>
+      <c r="M20" s="22"/>
+      <c r="N20" s="22"/>
+      <c r="O20" s="22"/>
+      <c r="P20" s="22"/>
+      <c r="Q20" s="22"/>
+      <c r="R20" s="22"/>
+      <c r="S20" s="22"/>
+      <c r="T20" s="22"/>
+      <c r="U20" s="22"/>
+      <c r="V20" s="23"/>
+    </row>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="B21" s="21"/>
+      <c r="C21" s="22"/>
+      <c r="D21" s="22"/>
+      <c r="E21" s="22"/>
+      <c r="F21" s="22"/>
+      <c r="G21" s="22"/>
+      <c r="H21" s="22"/>
+      <c r="I21" s="22"/>
+      <c r="J21" s="22"/>
+      <c r="K21" s="22"/>
+      <c r="L21" s="22"/>
+      <c r="M21" s="22"/>
+      <c r="N21" s="22"/>
+      <c r="O21" s="22"/>
+      <c r="P21" s="22"/>
+      <c r="Q21" s="22"/>
+      <c r="R21" s="22"/>
+      <c r="S21" s="22"/>
+      <c r="T21" s="22"/>
+      <c r="U21" s="22"/>
+      <c r="V21" s="23"/>
+    </row>
+    <row r="22" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="B22" s="21"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="22"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="22"/>
+      <c r="H22" s="22"/>
+      <c r="I22" s="22"/>
+      <c r="J22" s="22"/>
+      <c r="K22" s="22"/>
+      <c r="L22" s="22"/>
+      <c r="M22" s="22"/>
+      <c r="N22" s="22"/>
+      <c r="O22" s="22"/>
+      <c r="P22" s="22"/>
+      <c r="Q22" s="22"/>
+      <c r="R22" s="22"/>
+      <c r="S22" s="22"/>
+      <c r="T22" s="22"/>
+      <c r="U22" s="22"/>
+      <c r="V22" s="23"/>
+    </row>
+    <row r="23" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="B23" s="24"/>
+      <c r="C23" s="25"/>
+      <c r="D23" s="25"/>
+      <c r="E23" s="25"/>
+      <c r="F23" s="25"/>
+      <c r="G23" s="25"/>
+      <c r="H23" s="25"/>
+      <c r="I23" s="25"/>
+      <c r="J23" s="25"/>
+      <c r="K23" s="25"/>
+      <c r="L23" s="25"/>
+      <c r="M23" s="25"/>
+      <c r="N23" s="25"/>
+      <c r="O23" s="25"/>
+      <c r="P23" s="25"/>
+      <c r="Q23" s="25"/>
+      <c r="R23" s="25"/>
+      <c r="S23" s="25"/>
+      <c r="T23" s="25"/>
+      <c r="U23" s="25"/>
+      <c r="V23" s="26"/>
+    </row>
+    <row r="25" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A25" s="6" t="s">
+        <v>5</v>
       </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A25" s="2" t="s">
+      <c r="B25" s="18"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="19"/>
+      <c r="H25" s="19"/>
+      <c r="I25" s="19"/>
+      <c r="J25" s="19"/>
+      <c r="K25" s="19"/>
+      <c r="L25" s="19"/>
+      <c r="M25" s="19"/>
+      <c r="N25" s="19"/>
+      <c r="O25" s="19"/>
+      <c r="P25" s="19"/>
+      <c r="Q25" s="19"/>
+      <c r="R25" s="19"/>
+      <c r="S25" s="19"/>
+      <c r="T25" s="19"/>
+      <c r="U25" s="20"/>
+    </row>
+    <row r="26" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="B26" s="21"/>
+      <c r="C26" s="22"/>
+      <c r="D26" s="22"/>
+      <c r="E26" s="22"/>
+      <c r="F26" s="22"/>
+      <c r="G26" s="22"/>
+      <c r="H26" s="22"/>
+      <c r="I26" s="22"/>
+      <c r="J26" s="22"/>
+      <c r="K26" s="22"/>
+      <c r="L26" s="22"/>
+      <c r="M26" s="22"/>
+      <c r="N26" s="22"/>
+      <c r="O26" s="22"/>
+      <c r="P26" s="22"/>
+      <c r="Q26" s="22"/>
+      <c r="R26" s="22"/>
+      <c r="S26" s="22"/>
+      <c r="T26" s="22"/>
+      <c r="U26" s="23"/>
+    </row>
+    <row r="27" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="B27" s="21"/>
+      <c r="C27" s="22"/>
+      <c r="D27" s="22"/>
+      <c r="E27" s="22"/>
+      <c r="F27" s="22"/>
+      <c r="G27" s="22"/>
+      <c r="H27" s="22"/>
+      <c r="I27" s="22"/>
+      <c r="J27" s="22"/>
+      <c r="K27" s="22"/>
+      <c r="L27" s="22"/>
+      <c r="M27" s="22"/>
+      <c r="N27" s="22"/>
+      <c r="O27" s="22"/>
+      <c r="P27" s="22"/>
+      <c r="Q27" s="22"/>
+      <c r="R27" s="22"/>
+      <c r="S27" s="22"/>
+      <c r="T27" s="22"/>
+      <c r="U27" s="23"/>
+    </row>
+    <row r="28" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="B28" s="21"/>
+      <c r="C28" s="22"/>
+      <c r="D28" s="22"/>
+      <c r="E28" s="22"/>
+      <c r="F28" s="22"/>
+      <c r="G28" s="22"/>
+      <c r="H28" s="22"/>
+      <c r="I28" s="22"/>
+      <c r="J28" s="22"/>
+      <c r="K28" s="22"/>
+      <c r="L28" s="22"/>
+      <c r="M28" s="22"/>
+      <c r="N28" s="22"/>
+      <c r="O28" s="22"/>
+      <c r="P28" s="22"/>
+      <c r="Q28" s="22"/>
+      <c r="R28" s="22"/>
+      <c r="S28" s="22"/>
+      <c r="T28" s="22"/>
+      <c r="U28" s="23"/>
+    </row>
+    <row r="29" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="B29" s="21"/>
+      <c r="C29" s="22"/>
+      <c r="D29" s="22"/>
+      <c r="E29" s="22"/>
+      <c r="F29" s="22"/>
+      <c r="G29" s="22"/>
+      <c r="H29" s="22"/>
+      <c r="I29" s="22"/>
+      <c r="J29" s="22"/>
+      <c r="K29" s="22"/>
+      <c r="L29" s="22"/>
+      <c r="M29" s="22"/>
+      <c r="N29" s="22"/>
+      <c r="O29" s="22"/>
+      <c r="P29" s="22"/>
+      <c r="Q29" s="22"/>
+      <c r="R29" s="22"/>
+      <c r="S29" s="22"/>
+      <c r="T29" s="22"/>
+      <c r="U29" s="23"/>
+    </row>
+    <row r="30" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="B30" s="21"/>
+      <c r="C30" s="22"/>
+      <c r="D30" s="22"/>
+      <c r="E30" s="22"/>
+      <c r="F30" s="22"/>
+      <c r="G30" s="22"/>
+      <c r="H30" s="22"/>
+      <c r="I30" s="22"/>
+      <c r="J30" s="22"/>
+      <c r="K30" s="22"/>
+      <c r="L30" s="22"/>
+      <c r="M30" s="22"/>
+      <c r="N30" s="22"/>
+      <c r="O30" s="22"/>
+      <c r="P30" s="22"/>
+      <c r="Q30" s="22"/>
+      <c r="R30" s="22"/>
+      <c r="S30" s="22"/>
+      <c r="T30" s="22"/>
+      <c r="U30" s="23"/>
+    </row>
+    <row r="31" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="B31" s="21"/>
+      <c r="C31" s="22"/>
+      <c r="D31" s="22"/>
+      <c r="E31" s="22"/>
+      <c r="F31" s="22"/>
+      <c r="G31" s="22"/>
+      <c r="H31" s="22"/>
+      <c r="I31" s="22"/>
+      <c r="J31" s="22"/>
+      <c r="K31" s="22"/>
+      <c r="L31" s="22"/>
+      <c r="M31" s="22"/>
+      <c r="N31" s="22"/>
+      <c r="O31" s="22"/>
+      <c r="P31" s="22"/>
+      <c r="Q31" s="22"/>
+      <c r="R31" s="22"/>
+      <c r="S31" s="22"/>
+      <c r="T31" s="22"/>
+      <c r="U31" s="23"/>
+    </row>
+    <row r="32" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="B32" s="21"/>
+      <c r="C32" s="22"/>
+      <c r="D32" s="22"/>
+      <c r="E32" s="22"/>
+      <c r="F32" s="22"/>
+      <c r="G32" s="22"/>
+      <c r="H32" s="22"/>
+      <c r="I32" s="22"/>
+      <c r="J32" s="22"/>
+      <c r="K32" s="22"/>
+      <c r="L32" s="22"/>
+      <c r="M32" s="22"/>
+      <c r="N32" s="22"/>
+      <c r="O32" s="22"/>
+      <c r="P32" s="22"/>
+      <c r="Q32" s="22"/>
+      <c r="R32" s="22"/>
+      <c r="S32" s="22"/>
+      <c r="T32" s="22"/>
+      <c r="U32" s="23"/>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.35">
+      <c r="B33" s="21"/>
+      <c r="C33" s="22"/>
+      <c r="D33" s="22"/>
+      <c r="E33" s="22"/>
+      <c r="F33" s="22"/>
+      <c r="G33" s="22"/>
+      <c r="H33" s="22"/>
+      <c r="I33" s="22"/>
+      <c r="J33" s="22"/>
+      <c r="K33" s="22"/>
+      <c r="L33" s="22"/>
+      <c r="M33" s="22"/>
+      <c r="N33" s="22"/>
+      <c r="O33" s="22"/>
+      <c r="P33" s="22"/>
+      <c r="Q33" s="22"/>
+      <c r="R33" s="22"/>
+      <c r="S33" s="22"/>
+      <c r="T33" s="22"/>
+      <c r="U33" s="23"/>
+    </row>
+    <row r="34" spans="2:21" x14ac:dyDescent="0.35">
+      <c r="B34" s="21"/>
+      <c r="C34" s="22"/>
+      <c r="D34" s="22"/>
+      <c r="E34" s="22"/>
+      <c r="F34" s="22"/>
+      <c r="G34" s="22"/>
+      <c r="H34" s="22"/>
+      <c r="I34" s="22"/>
+      <c r="J34" s="22"/>
+      <c r="K34" s="22"/>
+      <c r="L34" s="22"/>
+      <c r="M34" s="22"/>
+      <c r="N34" s="22"/>
+      <c r="O34" s="22"/>
+      <c r="P34" s="22"/>
+      <c r="Q34" s="22"/>
+      <c r="R34" s="22"/>
+      <c r="S34" s="22"/>
+      <c r="T34" s="22"/>
+      <c r="U34" s="23"/>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.35">
+      <c r="B35" s="21"/>
+      <c r="C35" s="22"/>
+      <c r="D35" s="22"/>
+      <c r="E35" s="22"/>
+      <c r="F35" s="22"/>
+      <c r="G35" s="22"/>
+      <c r="H35" s="22"/>
+      <c r="I35" s="22"/>
+      <c r="J35" s="22"/>
+      <c r="K35" s="22"/>
+      <c r="L35" s="22"/>
+      <c r="M35" s="22"/>
+      <c r="N35" s="22"/>
+      <c r="O35" s="22"/>
+      <c r="P35" s="22"/>
+      <c r="Q35" s="22"/>
+      <c r="R35" s="22"/>
+      <c r="S35" s="22"/>
+      <c r="T35" s="22"/>
+      <c r="U35" s="23"/>
+    </row>
+    <row r="36" spans="2:21" x14ac:dyDescent="0.35">
+      <c r="B36" s="21"/>
+      <c r="C36" s="22"/>
+      <c r="D36" s="22"/>
+      <c r="E36" s="22"/>
+      <c r="F36" s="22"/>
+      <c r="G36" s="22"/>
+      <c r="H36" s="22"/>
+      <c r="I36" s="22"/>
+      <c r="J36" s="22"/>
+      <c r="K36" s="22"/>
+      <c r="L36" s="22"/>
+      <c r="M36" s="22"/>
+      <c r="N36" s="22"/>
+      <c r="O36" s="22"/>
+      <c r="P36" s="22"/>
+      <c r="Q36" s="22"/>
+      <c r="R36" s="22"/>
+      <c r="S36" s="22"/>
+      <c r="T36" s="22"/>
+      <c r="U36" s="23"/>
+    </row>
+    <row r="37" spans="2:21" x14ac:dyDescent="0.35">
+      <c r="B37" s="21"/>
+      <c r="C37" s="22"/>
+      <c r="D37" s="22"/>
+      <c r="E37" s="22"/>
+      <c r="F37" s="22"/>
+      <c r="G37" s="22"/>
+      <c r="H37" s="22"/>
+      <c r="I37" s="22"/>
+      <c r="J37" s="22"/>
+      <c r="K37" s="22"/>
+      <c r="L37" s="22"/>
+      <c r="M37" s="22"/>
+      <c r="N37" s="22"/>
+      <c r="O37" s="22"/>
+      <c r="P37" s="22"/>
+      <c r="Q37" s="22"/>
+      <c r="R37" s="22"/>
+      <c r="S37" s="22"/>
+      <c r="T37" s="22"/>
+      <c r="U37" s="23"/>
+    </row>
+    <row r="38" spans="2:21" x14ac:dyDescent="0.35">
+      <c r="B38" s="21"/>
+      <c r="C38" s="22"/>
+      <c r="D38" s="22"/>
+      <c r="E38" s="22"/>
+      <c r="F38" s="22"/>
+      <c r="G38" s="22"/>
+      <c r="H38" s="22"/>
+      <c r="I38" s="22"/>
+      <c r="J38" s="22"/>
+      <c r="K38" s="22"/>
+      <c r="L38" s="22"/>
+      <c r="M38" s="22"/>
+      <c r="N38" s="22"/>
+      <c r="O38" s="22"/>
+      <c r="P38" s="22"/>
+      <c r="Q38" s="22"/>
+      <c r="R38" s="22"/>
+      <c r="S38" s="22"/>
+      <c r="T38" s="22"/>
+      <c r="U38" s="23"/>
+    </row>
+    <row r="39" spans="2:21" x14ac:dyDescent="0.35">
+      <c r="B39" s="21"/>
+      <c r="C39" s="22"/>
+      <c r="D39" s="22"/>
+      <c r="E39" s="22"/>
+      <c r="F39" s="22"/>
+      <c r="G39" s="22"/>
+      <c r="H39" s="22"/>
+      <c r="I39" s="22"/>
+      <c r="J39" s="22"/>
+      <c r="K39" s="22"/>
+      <c r="L39" s="22"/>
+      <c r="M39" s="22"/>
+      <c r="N39" s="22"/>
+      <c r="O39" s="22"/>
+      <c r="P39" s="22"/>
+      <c r="Q39" s="22"/>
+      <c r="R39" s="22"/>
+      <c r="S39" s="22"/>
+      <c r="T39" s="22"/>
+      <c r="U39" s="23"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.35">
+      <c r="B40" s="21"/>
+      <c r="C40" s="22"/>
+      <c r="D40" s="22"/>
+      <c r="E40" s="22"/>
+      <c r="F40" s="22"/>
+      <c r="G40" s="22"/>
+      <c r="H40" s="22"/>
+      <c r="I40" s="22"/>
+      <c r="J40" s="22"/>
+      <c r="K40" s="22"/>
+      <c r="L40" s="22"/>
+      <c r="M40" s="22"/>
+      <c r="N40" s="22"/>
+      <c r="O40" s="22"/>
+      <c r="P40" s="22"/>
+      <c r="Q40" s="22"/>
+      <c r="R40" s="22"/>
+      <c r="S40" s="22"/>
+      <c r="T40" s="22"/>
+      <c r="U40" s="23"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.35">
+      <c r="B41" s="21"/>
+      <c r="C41" s="22"/>
+      <c r="D41" s="22"/>
+      <c r="E41" s="22"/>
+      <c r="F41" s="22"/>
+      <c r="G41" s="22"/>
+      <c r="H41" s="22"/>
+      <c r="I41" s="22"/>
+      <c r="J41" s="22"/>
+      <c r="K41" s="22"/>
+      <c r="L41" s="22"/>
+      <c r="M41" s="22"/>
+      <c r="N41" s="22"/>
+      <c r="O41" s="22"/>
+      <c r="P41" s="22"/>
+      <c r="Q41" s="22"/>
+      <c r="R41" s="22"/>
+      <c r="S41" s="22"/>
+      <c r="T41" s="22"/>
+      <c r="U41" s="23"/>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.35">
+      <c r="B42" s="21"/>
+      <c r="C42" s="22"/>
+      <c r="D42" s="22"/>
+      <c r="E42" s="22"/>
+      <c r="F42" s="22"/>
+      <c r="G42" s="22"/>
+      <c r="H42" s="22"/>
+      <c r="I42" s="22"/>
+      <c r="J42" s="22"/>
+      <c r="K42" s="22"/>
+      <c r="L42" s="22"/>
+      <c r="M42" s="22"/>
+      <c r="N42" s="22"/>
+      <c r="O42" s="22"/>
+      <c r="P42" s="22"/>
+      <c r="Q42" s="22"/>
+      <c r="R42" s="22"/>
+      <c r="S42" s="22"/>
+      <c r="T42" s="22"/>
+      <c r="U42" s="23"/>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.35">
+      <c r="B43" s="21"/>
+      <c r="C43" s="22"/>
+      <c r="D43" s="22"/>
+      <c r="E43" s="22"/>
+      <c r="F43" s="22"/>
+      <c r="G43" s="22"/>
+      <c r="H43" s="22"/>
+      <c r="I43" s="22"/>
+      <c r="J43" s="22"/>
+      <c r="K43" s="22"/>
+      <c r="L43" s="22"/>
+      <c r="M43" s="22"/>
+      <c r="N43" s="22"/>
+      <c r="O43" s="22"/>
+      <c r="P43" s="22"/>
+      <c r="Q43" s="22"/>
+      <c r="R43" s="22"/>
+      <c r="S43" s="22"/>
+      <c r="T43" s="22"/>
+      <c r="U43" s="23"/>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.35">
+      <c r="B44" s="21"/>
+      <c r="C44" s="22"/>
+      <c r="D44" s="22"/>
+      <c r="E44" s="22"/>
+      <c r="F44" s="22"/>
+      <c r="G44" s="22"/>
+      <c r="H44" s="22"/>
+      <c r="I44" s="22"/>
+      <c r="J44" s="22"/>
+      <c r="K44" s="22"/>
+      <c r="L44" s="22"/>
+      <c r="M44" s="22"/>
+      <c r="N44" s="22"/>
+      <c r="O44" s="22"/>
+      <c r="P44" s="22"/>
+      <c r="Q44" s="22"/>
+      <c r="R44" s="22"/>
+      <c r="S44" s="22"/>
+      <c r="T44" s="22"/>
+      <c r="U44" s="23"/>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.35">
+      <c r="B45" s="21"/>
+      <c r="C45" s="22"/>
+      <c r="D45" s="22"/>
+      <c r="E45" s="22"/>
+      <c r="F45" s="22"/>
+      <c r="G45" s="22"/>
+      <c r="H45" s="22"/>
+      <c r="I45" s="22"/>
+      <c r="J45" s="22"/>
+      <c r="K45" s="22"/>
+      <c r="L45" s="22"/>
+      <c r="M45" s="22"/>
+      <c r="N45" s="22"/>
+      <c r="O45" s="22"/>
+      <c r="P45" s="22"/>
+      <c r="Q45" s="22"/>
+      <c r="R45" s="22"/>
+      <c r="S45" s="22"/>
+      <c r="T45" s="22"/>
+      <c r="U45" s="23"/>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.35">
+      <c r="B46" s="21"/>
+      <c r="C46" s="22"/>
+      <c r="D46" s="22"/>
+      <c r="E46" s="22"/>
+      <c r="F46" s="22"/>
+      <c r="G46" s="22"/>
+      <c r="H46" s="22"/>
+      <c r="I46" s="22"/>
+      <c r="J46" s="22"/>
+      <c r="K46" s="22"/>
+      <c r="L46" s="22"/>
+      <c r="M46" s="22"/>
+      <c r="N46" s="22"/>
+      <c r="O46" s="22"/>
+      <c r="P46" s="22"/>
+      <c r="Q46" s="22"/>
+      <c r="R46" s="22"/>
+      <c r="S46" s="22"/>
+      <c r="T46" s="22"/>
+      <c r="U46" s="23"/>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.35">
+      <c r="B47" s="21"/>
+      <c r="C47" s="22"/>
+      <c r="D47" s="22"/>
+      <c r="E47" s="22"/>
+      <c r="F47" s="22"/>
+      <c r="G47" s="22"/>
+      <c r="H47" s="22"/>
+      <c r="I47" s="22"/>
+      <c r="J47" s="22"/>
+      <c r="K47" s="22"/>
+      <c r="L47" s="22"/>
+      <c r="M47" s="22"/>
+      <c r="N47" s="22"/>
+      <c r="O47" s="22"/>
+      <c r="P47" s="22"/>
+      <c r="Q47" s="22"/>
+      <c r="R47" s="22"/>
+      <c r="S47" s="22"/>
+      <c r="T47" s="22"/>
+      <c r="U47" s="23"/>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.35">
+      <c r="B48" s="21"/>
+      <c r="C48" s="22"/>
+      <c r="D48" s="22"/>
+      <c r="E48" s="22"/>
+      <c r="F48" s="22"/>
+      <c r="G48" s="22"/>
+      <c r="H48" s="22"/>
+      <c r="I48" s="22"/>
+      <c r="J48" s="22"/>
+      <c r="K48" s="22"/>
+      <c r="L48" s="22"/>
+      <c r="M48" s="22"/>
+      <c r="N48" s="22"/>
+      <c r="O48" s="22"/>
+      <c r="P48" s="22"/>
+      <c r="Q48" s="22"/>
+      <c r="R48" s="22"/>
+      <c r="S48" s="22"/>
+      <c r="T48" s="22"/>
+      <c r="U48" s="23"/>
+    </row>
+    <row r="49" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="B49" s="21"/>
+      <c r="C49" s="22"/>
+      <c r="D49" s="22"/>
+      <c r="E49" s="22"/>
+      <c r="F49" s="22"/>
+      <c r="G49" s="22"/>
+      <c r="H49" s="22"/>
+      <c r="I49" s="22"/>
+      <c r="J49" s="22"/>
+      <c r="K49" s="22"/>
+      <c r="L49" s="22"/>
+      <c r="M49" s="22"/>
+      <c r="N49" s="22"/>
+      <c r="O49" s="22"/>
+      <c r="P49" s="22"/>
+      <c r="Q49" s="22"/>
+      <c r="R49" s="22"/>
+      <c r="S49" s="22"/>
+      <c r="T49" s="22"/>
+      <c r="U49" s="23"/>
+    </row>
+    <row r="50" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="B50" s="24"/>
+      <c r="C50" s="25"/>
+      <c r="D50" s="25"/>
+      <c r="E50" s="25"/>
+      <c r="F50" s="25"/>
+      <c r="G50" s="25"/>
+      <c r="H50" s="25"/>
+      <c r="I50" s="25"/>
+      <c r="J50" s="25"/>
+      <c r="K50" s="25"/>
+      <c r="L50" s="25"/>
+      <c r="M50" s="25"/>
+      <c r="N50" s="25"/>
+      <c r="O50" s="25"/>
+      <c r="P50" s="25"/>
+      <c r="Q50" s="25"/>
+      <c r="R50" s="25"/>
+      <c r="S50" s="25"/>
+      <c r="T50" s="25"/>
+      <c r="U50" s="26"/>
+    </row>
+    <row r="52" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A52" s="9" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A52" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="B52" s="21"/>
-      <c r="C52" s="21"/>
-      <c r="D52" s="21"/>
-      <c r="E52" s="21"/>
-      <c r="F52" s="21"/>
-      <c r="G52" s="21"/>
-      <c r="H52" s="21"/>
-      <c r="I52" s="21"/>
-      <c r="J52" s="21"/>
-      <c r="K52" s="21"/>
-      <c r="L52" s="21"/>
-      <c r="M52" s="21"/>
-      <c r="N52" s="21"/>
-      <c r="O52" s="22"/>
-    </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A53" s="23"/>
+      <c r="B52" s="10"/>
+      <c r="C52" s="10"/>
+      <c r="D52" s="10"/>
+      <c r="E52" s="10"/>
+      <c r="F52" s="10"/>
+      <c r="G52" s="10"/>
+      <c r="H52" s="10"/>
+      <c r="I52" s="10"/>
+      <c r="J52" s="10"/>
+      <c r="K52" s="10"/>
+      <c r="L52" s="10"/>
+      <c r="M52" s="10"/>
+      <c r="N52" s="10"/>
+      <c r="O52" s="11"/>
+    </row>
+    <row r="53" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A53" s="12"/>
       <c r="B53" s="13"/>
       <c r="C53" s="13"/>
       <c r="D53" s="13"/>
@@ -1116,10 +2303,10 @@
       <c r="L53" s="13"/>
       <c r="M53" s="13"/>
       <c r="N53" s="13"/>
-      <c r="O53" s="24"/>
-    </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A54" s="23"/>
+      <c r="O53" s="14"/>
+    </row>
+    <row r="54" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A54" s="12"/>
       <c r="B54" s="13"/>
       <c r="C54" s="13"/>
       <c r="D54" s="13"/>
@@ -1133,10 +2320,10 @@
       <c r="L54" s="13"/>
       <c r="M54" s="13"/>
       <c r="N54" s="13"/>
-      <c r="O54" s="24"/>
-    </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A55" s="23"/>
+      <c r="O54" s="14"/>
+    </row>
+    <row r="55" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A55" s="12"/>
       <c r="B55" s="13"/>
       <c r="C55" s="13"/>
       <c r="D55" s="13"/>
@@ -1150,10 +2337,10 @@
       <c r="L55" s="13"/>
       <c r="M55" s="13"/>
       <c r="N55" s="13"/>
-      <c r="O55" s="24"/>
-    </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A56" s="23"/>
+      <c r="O55" s="14"/>
+    </row>
+    <row r="56" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A56" s="12"/>
       <c r="B56" s="13"/>
       <c r="C56" s="13"/>
       <c r="D56" s="13"/>
@@ -1167,46 +2354,46 @@
       <c r="L56" s="13"/>
       <c r="M56" s="13"/>
       <c r="N56" s="13"/>
-      <c r="O56" s="24"/>
-    </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A57" s="25"/>
-      <c r="B57" s="26"/>
-      <c r="C57" s="26"/>
-      <c r="D57" s="26"/>
-      <c r="E57" s="26"/>
-      <c r="F57" s="26"/>
-      <c r="G57" s="26"/>
-      <c r="H57" s="26"/>
-      <c r="I57" s="26"/>
-      <c r="J57" s="26"/>
-      <c r="K57" s="26"/>
-      <c r="L57" s="26"/>
-      <c r="M57" s="26"/>
-      <c r="N57" s="26"/>
-      <c r="O57" s="27"/>
-    </row>
-    <row r="59" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="20" t="s">
-        <v>11</v>
+      <c r="O56" s="14"/>
+    </row>
+    <row r="57" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A57" s="15"/>
+      <c r="B57" s="16"/>
+      <c r="C57" s="16"/>
+      <c r="D57" s="16"/>
+      <c r="E57" s="16"/>
+      <c r="F57" s="16"/>
+      <c r="G57" s="16"/>
+      <c r="H57" s="16"/>
+      <c r="I57" s="16"/>
+      <c r="J57" s="16"/>
+      <c r="K57" s="16"/>
+      <c r="L57" s="16"/>
+      <c r="M57" s="16"/>
+      <c r="N57" s="16"/>
+      <c r="O57" s="17"/>
+    </row>
+    <row r="59" spans="1:21" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A59" s="9" t="s">
+        <v>20</v>
       </c>
-      <c r="B59" s="21"/>
-      <c r="C59" s="21"/>
-      <c r="D59" s="21"/>
-      <c r="E59" s="21"/>
-      <c r="F59" s="21"/>
-      <c r="G59" s="21"/>
-      <c r="H59" s="21"/>
-      <c r="I59" s="21"/>
-      <c r="J59" s="21"/>
-      <c r="K59" s="21"/>
-      <c r="L59" s="21"/>
-      <c r="M59" s="21"/>
-      <c r="N59" s="21"/>
-      <c r="O59" s="22"/>
-    </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A60" s="23"/>
+      <c r="B59" s="10"/>
+      <c r="C59" s="10"/>
+      <c r="D59" s="10"/>
+      <c r="E59" s="10"/>
+      <c r="F59" s="10"/>
+      <c r="G59" s="10"/>
+      <c r="H59" s="10"/>
+      <c r="I59" s="10"/>
+      <c r="J59" s="10"/>
+      <c r="K59" s="10"/>
+      <c r="L59" s="10"/>
+      <c r="M59" s="10"/>
+      <c r="N59" s="10"/>
+      <c r="O59" s="11"/>
+    </row>
+    <row r="60" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A60" s="12"/>
       <c r="B60" s="13"/>
       <c r="C60" s="13"/>
       <c r="D60" s="13"/>
@@ -1220,10 +2407,10 @@
       <c r="L60" s="13"/>
       <c r="M60" s="13"/>
       <c r="N60" s="13"/>
-      <c r="O60" s="24"/>
-    </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A61" s="23"/>
+      <c r="O60" s="14"/>
+    </row>
+    <row r="61" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A61" s="12"/>
       <c r="B61" s="13"/>
       <c r="C61" s="13"/>
       <c r="D61" s="13"/>
@@ -1237,10 +2424,10 @@
       <c r="L61" s="13"/>
       <c r="M61" s="13"/>
       <c r="N61" s="13"/>
-      <c r="O61" s="24"/>
-    </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A62" s="23"/>
+      <c r="O61" s="14"/>
+    </row>
+    <row r="62" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A62" s="12"/>
       <c r="B62" s="13"/>
       <c r="C62" s="13"/>
       <c r="D62" s="13"/>
@@ -1254,10 +2441,10 @@
       <c r="L62" s="13"/>
       <c r="M62" s="13"/>
       <c r="N62" s="13"/>
-      <c r="O62" s="24"/>
-    </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A63" s="23"/>
+      <c r="O62" s="14"/>
+    </row>
+    <row r="63" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A63" s="12"/>
       <c r="B63" s="13"/>
       <c r="C63" s="13"/>
       <c r="D63" s="13"/>
@@ -1271,10 +2458,10 @@
       <c r="L63" s="13"/>
       <c r="M63" s="13"/>
       <c r="N63" s="13"/>
-      <c r="O63" s="24"/>
-    </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A64" s="23"/>
+      <c r="O63" s="14"/>
+    </row>
+    <row r="64" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A64" s="12"/>
       <c r="B64" s="13"/>
       <c r="C64" s="13"/>
       <c r="D64" s="13"/>
@@ -1288,10 +2475,10 @@
       <c r="L64" s="13"/>
       <c r="M64" s="13"/>
       <c r="N64" s="13"/>
-      <c r="O64" s="24"/>
+      <c r="O64" s="14"/>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A65" s="23"/>
+      <c r="A65" s="12"/>
       <c r="B65" s="13"/>
       <c r="C65" s="13"/>
       <c r="D65" s="13"/>
@@ -1305,10 +2492,10 @@
       <c r="L65" s="13"/>
       <c r="M65" s="13"/>
       <c r="N65" s="13"/>
-      <c r="O65" s="24"/>
+      <c r="O65" s="14"/>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A66" s="23"/>
+      <c r="A66" s="12"/>
       <c r="B66" s="13"/>
       <c r="C66" s="13"/>
       <c r="D66" s="13"/>
@@ -1322,10 +2509,10 @@
       <c r="L66" s="13"/>
       <c r="M66" s="13"/>
       <c r="N66" s="13"/>
-      <c r="O66" s="24"/>
+      <c r="O66" s="14"/>
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A67" s="23"/>
+      <c r="A67" s="12"/>
       <c r="B67" s="13"/>
       <c r="C67" s="13"/>
       <c r="D67" s="13"/>
@@ -1339,10 +2526,10 @@
       <c r="L67" s="13"/>
       <c r="M67" s="13"/>
       <c r="N67" s="13"/>
-      <c r="O67" s="24"/>
+      <c r="O67" s="14"/>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A68" s="23"/>
+      <c r="A68" s="12"/>
       <c r="B68" s="13"/>
       <c r="C68" s="13"/>
       <c r="D68" s="13"/>
@@ -1356,10 +2543,10 @@
       <c r="L68" s="13"/>
       <c r="M68" s="13"/>
       <c r="N68" s="13"/>
-      <c r="O68" s="24"/>
+      <c r="O68" s="14"/>
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A69" s="23"/>
+      <c r="A69" s="12"/>
       <c r="B69" s="13"/>
       <c r="C69" s="13"/>
       <c r="D69" s="13"/>
@@ -1373,10 +2560,10 @@
       <c r="L69" s="13"/>
       <c r="M69" s="13"/>
       <c r="N69" s="13"/>
-      <c r="O69" s="24"/>
+      <c r="O69" s="14"/>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A70" s="23"/>
+      <c r="A70" s="12"/>
       <c r="B70" s="13"/>
       <c r="C70" s="13"/>
       <c r="D70" s="13"/>
@@ -1390,10 +2577,10 @@
       <c r="L70" s="13"/>
       <c r="M70" s="13"/>
       <c r="N70" s="13"/>
-      <c r="O70" s="24"/>
+      <c r="O70" s="14"/>
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A71" s="23"/>
+      <c r="A71" s="12"/>
       <c r="B71" s="13"/>
       <c r="C71" s="13"/>
       <c r="D71" s="13"/>
@@ -1407,10 +2594,10 @@
       <c r="L71" s="13"/>
       <c r="M71" s="13"/>
       <c r="N71" s="13"/>
-      <c r="O71" s="24"/>
+      <c r="O71" s="14"/>
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A72" s="23"/>
+      <c r="A72" s="12"/>
       <c r="B72" s="13"/>
       <c r="C72" s="13"/>
       <c r="D72" s="13"/>
@@ -1424,239 +2611,4969 @@
       <c r="L72" s="13"/>
       <c r="M72" s="13"/>
       <c r="N72" s="13"/>
-      <c r="O72" s="24"/>
+      <c r="O72" s="14"/>
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A73" s="25"/>
-      <c r="B73" s="26"/>
-      <c r="C73" s="26"/>
-      <c r="D73" s="26"/>
-      <c r="E73" s="26"/>
-      <c r="F73" s="26"/>
-      <c r="G73" s="26"/>
-      <c r="H73" s="26"/>
-      <c r="I73" s="26"/>
-      <c r="J73" s="26"/>
-      <c r="K73" s="26"/>
-      <c r="L73" s="26"/>
-      <c r="M73" s="26"/>
-      <c r="N73" s="26"/>
-      <c r="O73" s="27"/>
+      <c r="A73" s="15"/>
+      <c r="B73" s="16"/>
+      <c r="C73" s="16"/>
+      <c r="D73" s="16"/>
+      <c r="E73" s="16"/>
+      <c r="F73" s="16"/>
+      <c r="G73" s="16"/>
+      <c r="H73" s="16"/>
+      <c r="I73" s="16"/>
+      <c r="J73" s="16"/>
+      <c r="K73" s="16"/>
+      <c r="L73" s="16"/>
+      <c r="M73" s="16"/>
+      <c r="N73" s="16"/>
+      <c r="O73" s="17"/>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A75" s="5" t="s">
+      <c r="A75" s="30" t="s">
+        <v>8</v>
+      </c>
+      <c r="B75" s="31"/>
+      <c r="C75" s="31"/>
+      <c r="D75" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="E75" s="32"/>
+      <c r="F75" s="32"/>
+      <c r="G75" s="32"/>
+      <c r="H75" s="32"/>
+      <c r="I75" s="32"/>
+      <c r="J75" s="32"/>
+      <c r="K75" s="32"/>
+      <c r="L75" s="32"/>
+    </row>
+    <row r="76" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D76" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="B75" s="6"/>
-      <c r="C75" s="6"/>
-      <c r="D75" s="7" t="s">
+      <c r="E76" s="29"/>
+      <c r="F76" s="29"/>
+      <c r="G76" s="29"/>
+      <c r="H76" s="29"/>
+      <c r="I76" s="29"/>
+      <c r="J76" s="29"/>
+      <c r="K76" s="29"/>
+      <c r="L76" s="29"/>
+    </row>
+    <row r="77" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="D77" s="29"/>
+      <c r="E77" s="29"/>
+      <c r="F77" s="29"/>
+      <c r="G77" s="29"/>
+      <c r="H77" s="29"/>
+      <c r="I77" s="29"/>
+      <c r="J77" s="29"/>
+      <c r="K77" s="29"/>
+      <c r="L77" s="29"/>
+    </row>
+    <row r="78" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="D78" s="29"/>
+      <c r="E78" s="29"/>
+      <c r="F78" s="29"/>
+      <c r="G78" s="29"/>
+      <c r="H78" s="29"/>
+      <c r="I78" s="29"/>
+      <c r="J78" s="29"/>
+      <c r="K78" s="29"/>
+      <c r="L78" s="29"/>
+    </row>
+    <row r="79" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="D79" s="29"/>
+      <c r="E79" s="29"/>
+      <c r="F79" s="29"/>
+      <c r="G79" s="29"/>
+      <c r="H79" s="29"/>
+      <c r="I79" s="29"/>
+      <c r="J79" s="29"/>
+      <c r="K79" s="29"/>
+      <c r="L79" s="29"/>
+    </row>
+    <row r="80" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="D80" s="29"/>
+      <c r="E80" s="29"/>
+      <c r="F80" s="29"/>
+      <c r="G80" s="29"/>
+      <c r="H80" s="29"/>
+      <c r="I80" s="29"/>
+      <c r="J80" s="29"/>
+      <c r="K80" s="29"/>
+      <c r="L80" s="29"/>
+    </row>
+    <row r="81" spans="4:12" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D81" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="E81" s="29"/>
+      <c r="F81" s="29"/>
+      <c r="G81" s="29"/>
+      <c r="H81" s="29"/>
+      <c r="I81" s="29"/>
+      <c r="J81" s="29"/>
+      <c r="K81" s="29"/>
+      <c r="L81" s="29"/>
+    </row>
+    <row r="82" spans="4:12" x14ac:dyDescent="0.35">
+      <c r="D82" s="29"/>
+      <c r="E82" s="29"/>
+      <c r="F82" s="29"/>
+      <c r="G82" s="29"/>
+      <c r="H82" s="29"/>
+      <c r="I82" s="29"/>
+      <c r="J82" s="29"/>
+      <c r="K82" s="29"/>
+      <c r="L82" s="29"/>
+    </row>
+    <row r="83" spans="4:12" x14ac:dyDescent="0.35">
+      <c r="D83" s="29"/>
+      <c r="E83" s="29"/>
+      <c r="F83" s="29"/>
+      <c r="G83" s="29"/>
+      <c r="H83" s="29"/>
+      <c r="I83" s="29"/>
+      <c r="J83" s="29"/>
+      <c r="K83" s="29"/>
+      <c r="L83" s="29"/>
+    </row>
+    <row r="84" spans="4:12" x14ac:dyDescent="0.35">
+      <c r="D84" s="29"/>
+      <c r="E84" s="29"/>
+      <c r="F84" s="29"/>
+      <c r="G84" s="29"/>
+      <c r="H84" s="29"/>
+      <c r="I84" s="29"/>
+      <c r="J84" s="29"/>
+      <c r="K84" s="29"/>
+      <c r="L84" s="29"/>
+    </row>
+    <row r="85" spans="4:12" x14ac:dyDescent="0.35">
+      <c r="D85" s="29"/>
+      <c r="E85" s="29"/>
+      <c r="F85" s="29"/>
+      <c r="G85" s="29"/>
+      <c r="H85" s="29"/>
+      <c r="I85" s="29"/>
+      <c r="J85" s="29"/>
+      <c r="K85" s="29"/>
+      <c r="L85" s="29"/>
+    </row>
+    <row r="86" spans="4:12" x14ac:dyDescent="0.35">
+      <c r="D86" s="29"/>
+      <c r="E86" s="29"/>
+      <c r="F86" s="29"/>
+      <c r="G86" s="29"/>
+      <c r="H86" s="29"/>
+      <c r="I86" s="29"/>
+      <c r="J86" s="29"/>
+      <c r="K86" s="29"/>
+      <c r="L86" s="29"/>
+    </row>
+    <row r="87" spans="4:12" x14ac:dyDescent="0.35">
+      <c r="D87" s="29"/>
+      <c r="E87" s="29"/>
+      <c r="F87" s="29"/>
+      <c r="G87" s="29"/>
+      <c r="H87" s="29"/>
+      <c r="I87" s="29"/>
+      <c r="J87" s="29"/>
+      <c r="K87" s="29"/>
+      <c r="L87" s="29"/>
+    </row>
+    <row r="88" spans="4:12" x14ac:dyDescent="0.35">
+      <c r="D88" s="29"/>
+      <c r="E88" s="29"/>
+      <c r="F88" s="29"/>
+      <c r="G88" s="29"/>
+      <c r="H88" s="29"/>
+      <c r="I88" s="29"/>
+      <c r="J88" s="29"/>
+      <c r="K88" s="29"/>
+      <c r="L88" s="29"/>
+    </row>
+    <row r="89" spans="4:12" x14ac:dyDescent="0.35">
+      <c r="D89" s="29"/>
+      <c r="E89" s="29"/>
+      <c r="F89" s="29"/>
+      <c r="G89" s="29"/>
+      <c r="H89" s="29"/>
+      <c r="I89" s="29"/>
+      <c r="J89" s="29"/>
+      <c r="K89" s="29"/>
+      <c r="L89" s="29"/>
+    </row>
+    <row r="90" spans="4:12" x14ac:dyDescent="0.35">
+      <c r="D90" s="29"/>
+      <c r="E90" s="29"/>
+      <c r="F90" s="29"/>
+      <c r="G90" s="29"/>
+      <c r="H90" s="29"/>
+      <c r="I90" s="29"/>
+      <c r="J90" s="29"/>
+      <c r="K90" s="29"/>
+      <c r="L90" s="29"/>
+    </row>
+    <row r="91" spans="4:12" x14ac:dyDescent="0.35">
+      <c r="D91" s="29"/>
+      <c r="E91" s="29"/>
+      <c r="F91" s="29"/>
+      <c r="G91" s="29"/>
+      <c r="H91" s="29"/>
+      <c r="I91" s="29"/>
+      <c r="J91" s="29"/>
+      <c r="K91" s="29"/>
+      <c r="L91" s="29"/>
+    </row>
+    <row r="118" spans="1:29" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A118" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E75" s="7"/>
-      <c r="F75" s="7"/>
-      <c r="G75" s="7"/>
-      <c r="H75" s="7"/>
-      <c r="I75" s="7"/>
-      <c r="J75" s="7"/>
-      <c r="K75" s="7"/>
-      <c r="L75" s="7"/>
-    </row>
-    <row r="76" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="D76" s="4" t="s">
+      <c r="B118" s="10"/>
+      <c r="C118" s="10"/>
+      <c r="D118" s="10"/>
+      <c r="E118" s="10"/>
+      <c r="F118" s="11"/>
+      <c r="I118" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="J118" s="10"/>
+      <c r="K118" s="10"/>
+      <c r="L118" s="10"/>
+      <c r="M118" s="10"/>
+      <c r="N118" s="10"/>
+      <c r="O118" s="10"/>
+      <c r="P118" s="10"/>
+      <c r="Q118" s="10"/>
+      <c r="R118" s="10"/>
+      <c r="S118" s="10"/>
+      <c r="T118" s="10"/>
+      <c r="U118" s="10"/>
+      <c r="V118" s="10"/>
+      <c r="W118" s="11"/>
+      <c r="X118" s="4"/>
+      <c r="Y118" s="4"/>
+      <c r="Z118" s="4"/>
+      <c r="AA118" s="4"/>
+      <c r="AB118" s="4"/>
+      <c r="AC118" s="4"/>
+    </row>
+    <row r="119" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A119" s="12"/>
+      <c r="B119" s="13"/>
+      <c r="C119" s="13"/>
+      <c r="D119" s="13"/>
+      <c r="E119" s="13"/>
+      <c r="F119" s="14"/>
+      <c r="I119" s="12"/>
+      <c r="J119" s="13"/>
+      <c r="K119" s="13"/>
+      <c r="L119" s="13"/>
+      <c r="M119" s="13"/>
+      <c r="N119" s="13"/>
+      <c r="O119" s="13"/>
+      <c r="P119" s="13"/>
+      <c r="Q119" s="13"/>
+      <c r="R119" s="13"/>
+      <c r="S119" s="13"/>
+      <c r="T119" s="13"/>
+      <c r="U119" s="13"/>
+      <c r="V119" s="13"/>
+      <c r="W119" s="14"/>
+      <c r="X119" s="4"/>
+      <c r="Y119" s="4"/>
+      <c r="Z119" s="4"/>
+      <c r="AA119" s="4"/>
+      <c r="AB119" s="4"/>
+      <c r="AC119" s="4"/>
+    </row>
+    <row r="120" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A120" s="12"/>
+      <c r="B120" s="13"/>
+      <c r="C120" s="13"/>
+      <c r="D120" s="13"/>
+      <c r="E120" s="13"/>
+      <c r="F120" s="14"/>
+      <c r="I120" s="12"/>
+      <c r="J120" s="13"/>
+      <c r="K120" s="13"/>
+      <c r="L120" s="13"/>
+      <c r="M120" s="13"/>
+      <c r="N120" s="13"/>
+      <c r="O120" s="13"/>
+      <c r="P120" s="13"/>
+      <c r="Q120" s="13"/>
+      <c r="R120" s="13"/>
+      <c r="S120" s="13"/>
+      <c r="T120" s="13"/>
+      <c r="U120" s="13"/>
+      <c r="V120" s="13"/>
+      <c r="W120" s="14"/>
+      <c r="X120" s="4"/>
+      <c r="Y120" s="4"/>
+      <c r="Z120" s="4"/>
+      <c r="AA120" s="4"/>
+      <c r="AB120" s="4"/>
+      <c r="AC120" s="4"/>
+    </row>
+    <row r="121" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A121" s="15"/>
+      <c r="B121" s="16"/>
+      <c r="C121" s="16"/>
+      <c r="D121" s="16"/>
+      <c r="E121" s="16"/>
+      <c r="F121" s="17"/>
+      <c r="I121" s="12"/>
+      <c r="J121" s="13"/>
+      <c r="K121" s="13"/>
+      <c r="L121" s="13"/>
+      <c r="M121" s="13"/>
+      <c r="N121" s="13"/>
+      <c r="O121" s="13"/>
+      <c r="P121" s="13"/>
+      <c r="Q121" s="13"/>
+      <c r="R121" s="13"/>
+      <c r="S121" s="13"/>
+      <c r="T121" s="13"/>
+      <c r="U121" s="13"/>
+      <c r="V121" s="13"/>
+      <c r="W121" s="14"/>
+      <c r="X121" s="4"/>
+      <c r="Y121" s="4"/>
+      <c r="Z121" s="4"/>
+      <c r="AA121" s="4"/>
+      <c r="AB121" s="4"/>
+      <c r="AC121" s="4"/>
+    </row>
+    <row r="122" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="I122" s="12"/>
+      <c r="J122" s="13"/>
+      <c r="K122" s="13"/>
+      <c r="L122" s="13"/>
+      <c r="M122" s="13"/>
+      <c r="N122" s="13"/>
+      <c r="O122" s="13"/>
+      <c r="P122" s="13"/>
+      <c r="Q122" s="13"/>
+      <c r="R122" s="13"/>
+      <c r="S122" s="13"/>
+      <c r="T122" s="13"/>
+      <c r="U122" s="13"/>
+      <c r="V122" s="13"/>
+      <c r="W122" s="14"/>
+      <c r="X122" s="4"/>
+      <c r="Y122" s="4"/>
+      <c r="Z122" s="4"/>
+      <c r="AA122" s="4"/>
+      <c r="AB122" s="4"/>
+      <c r="AC122" s="4"/>
+    </row>
+    <row r="123" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A123" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="B123" s="28"/>
+      <c r="I123" s="15"/>
+      <c r="J123" s="16"/>
+      <c r="K123" s="16"/>
+      <c r="L123" s="16"/>
+      <c r="M123" s="16"/>
+      <c r="N123" s="16"/>
+      <c r="O123" s="16"/>
+      <c r="P123" s="16"/>
+      <c r="Q123" s="16"/>
+      <c r="R123" s="16"/>
+      <c r="S123" s="16"/>
+      <c r="T123" s="16"/>
+      <c r="U123" s="16"/>
+      <c r="V123" s="16"/>
+      <c r="W123" s="17"/>
+      <c r="X123" s="4"/>
+      <c r="Y123" s="4"/>
+      <c r="Z123" s="4"/>
+      <c r="AA123" s="4"/>
+      <c r="AB123" s="4"/>
+      <c r="AC123" s="4"/>
+    </row>
+    <row r="124" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A124" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="125" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A125" s="18"/>
+      <c r="B125" s="19"/>
+      <c r="C125" s="19"/>
+      <c r="D125" s="19"/>
+      <c r="E125" s="19"/>
+      <c r="F125" s="19"/>
+      <c r="G125" s="19"/>
+      <c r="H125" s="19"/>
+      <c r="I125" s="19"/>
+      <c r="J125" s="19"/>
+      <c r="K125" s="19"/>
+      <c r="L125" s="19"/>
+      <c r="M125" s="19"/>
+      <c r="N125" s="19"/>
+      <c r="O125" s="19"/>
+      <c r="P125" s="19"/>
+      <c r="Q125" s="19"/>
+      <c r="R125" s="19"/>
+      <c r="S125" s="19"/>
+      <c r="T125" s="19"/>
+      <c r="U125" s="20"/>
+    </row>
+    <row r="126" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A126" s="21"/>
+      <c r="B126" s="22"/>
+      <c r="C126" s="22"/>
+      <c r="D126" s="22"/>
+      <c r="E126" s="22"/>
+      <c r="F126" s="22"/>
+      <c r="G126" s="22"/>
+      <c r="H126" s="22"/>
+      <c r="I126" s="22"/>
+      <c r="J126" s="22"/>
+      <c r="K126" s="22"/>
+      <c r="L126" s="22"/>
+      <c r="M126" s="22"/>
+      <c r="N126" s="22"/>
+      <c r="O126" s="22"/>
+      <c r="P126" s="22"/>
+      <c r="Q126" s="22"/>
+      <c r="R126" s="22"/>
+      <c r="S126" s="22"/>
+      <c r="T126" s="22"/>
+      <c r="U126" s="23"/>
+    </row>
+    <row r="127" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A127" s="21"/>
+      <c r="B127" s="22"/>
+      <c r="C127" s="22"/>
+      <c r="D127" s="22"/>
+      <c r="E127" s="22"/>
+      <c r="F127" s="22"/>
+      <c r="G127" s="22"/>
+      <c r="H127" s="22"/>
+      <c r="I127" s="22"/>
+      <c r="J127" s="22"/>
+      <c r="K127" s="22"/>
+      <c r="L127" s="22"/>
+      <c r="M127" s="22"/>
+      <c r="N127" s="22"/>
+      <c r="O127" s="22"/>
+      <c r="P127" s="22"/>
+      <c r="Q127" s="22"/>
+      <c r="R127" s="22"/>
+      <c r="S127" s="22"/>
+      <c r="T127" s="22"/>
+      <c r="U127" s="23"/>
+    </row>
+    <row r="128" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A128" s="21"/>
+      <c r="B128" s="22"/>
+      <c r="C128" s="22"/>
+      <c r="D128" s="22"/>
+      <c r="E128" s="22"/>
+      <c r="F128" s="22"/>
+      <c r="G128" s="22"/>
+      <c r="H128" s="22"/>
+      <c r="I128" s="22"/>
+      <c r="J128" s="22"/>
+      <c r="K128" s="22"/>
+      <c r="L128" s="22"/>
+      <c r="M128" s="22"/>
+      <c r="N128" s="22"/>
+      <c r="O128" s="22"/>
+      <c r="P128" s="22"/>
+      <c r="Q128" s="22"/>
+      <c r="R128" s="22"/>
+      <c r="S128" s="22"/>
+      <c r="T128" s="22"/>
+      <c r="U128" s="23"/>
+    </row>
+    <row r="129" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A129" s="21"/>
+      <c r="B129" s="22"/>
+      <c r="C129" s="22"/>
+      <c r="D129" s="22"/>
+      <c r="E129" s="22"/>
+      <c r="F129" s="22"/>
+      <c r="G129" s="22"/>
+      <c r="H129" s="22"/>
+      <c r="I129" s="22"/>
+      <c r="J129" s="22"/>
+      <c r="K129" s="22"/>
+      <c r="L129" s="22"/>
+      <c r="M129" s="22"/>
+      <c r="N129" s="22"/>
+      <c r="O129" s="22"/>
+      <c r="P129" s="22"/>
+      <c r="Q129" s="22"/>
+      <c r="R129" s="22"/>
+      <c r="S129" s="22"/>
+      <c r="T129" s="22"/>
+      <c r="U129" s="23"/>
+    </row>
+    <row r="130" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A130" s="21"/>
+      <c r="B130" s="22"/>
+      <c r="C130" s="22"/>
+      <c r="D130" s="22"/>
+      <c r="E130" s="22"/>
+      <c r="F130" s="22"/>
+      <c r="G130" s="22"/>
+      <c r="H130" s="22"/>
+      <c r="I130" s="22"/>
+      <c r="J130" s="22"/>
+      <c r="K130" s="22"/>
+      <c r="L130" s="22"/>
+      <c r="M130" s="22"/>
+      <c r="N130" s="22"/>
+      <c r="O130" s="22"/>
+      <c r="P130" s="22"/>
+      <c r="Q130" s="22"/>
+      <c r="R130" s="22"/>
+      <c r="S130" s="22"/>
+      <c r="T130" s="22"/>
+      <c r="U130" s="23"/>
+    </row>
+    <row r="131" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A131" s="21"/>
+      <c r="B131" s="22"/>
+      <c r="C131" s="22"/>
+      <c r="D131" s="22"/>
+      <c r="E131" s="22"/>
+      <c r="F131" s="22"/>
+      <c r="G131" s="22"/>
+      <c r="H131" s="22"/>
+      <c r="I131" s="22"/>
+      <c r="J131" s="22"/>
+      <c r="K131" s="22"/>
+      <c r="L131" s="22"/>
+      <c r="M131" s="22"/>
+      <c r="N131" s="22"/>
+      <c r="O131" s="22"/>
+      <c r="P131" s="22"/>
+      <c r="Q131" s="22"/>
+      <c r="R131" s="22"/>
+      <c r="S131" s="22"/>
+      <c r="T131" s="22"/>
+      <c r="U131" s="23"/>
+    </row>
+    <row r="132" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A132" s="21"/>
+      <c r="B132" s="22"/>
+      <c r="C132" s="22"/>
+      <c r="D132" s="22"/>
+      <c r="E132" s="22"/>
+      <c r="F132" s="22"/>
+      <c r="G132" s="22"/>
+      <c r="H132" s="22"/>
+      <c r="I132" s="22"/>
+      <c r="J132" s="22"/>
+      <c r="K132" s="22"/>
+      <c r="L132" s="22"/>
+      <c r="M132" s="22"/>
+      <c r="N132" s="22"/>
+      <c r="O132" s="22"/>
+      <c r="P132" s="22"/>
+      <c r="Q132" s="22"/>
+      <c r="R132" s="22"/>
+      <c r="S132" s="22"/>
+      <c r="T132" s="22"/>
+      <c r="U132" s="23"/>
+    </row>
+    <row r="133" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A133" s="21"/>
+      <c r="B133" s="22"/>
+      <c r="C133" s="22"/>
+      <c r="D133" s="22"/>
+      <c r="E133" s="22"/>
+      <c r="F133" s="22"/>
+      <c r="G133" s="22"/>
+      <c r="H133" s="22"/>
+      <c r="I133" s="22"/>
+      <c r="J133" s="22"/>
+      <c r="K133" s="22"/>
+      <c r="L133" s="22"/>
+      <c r="M133" s="22"/>
+      <c r="N133" s="22"/>
+      <c r="O133" s="22"/>
+      <c r="P133" s="22"/>
+      <c r="Q133" s="22"/>
+      <c r="R133" s="22"/>
+      <c r="S133" s="22"/>
+      <c r="T133" s="22"/>
+      <c r="U133" s="23"/>
+    </row>
+    <row r="134" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A134" s="21"/>
+      <c r="B134" s="22"/>
+      <c r="C134" s="22"/>
+      <c r="D134" s="22"/>
+      <c r="E134" s="22"/>
+      <c r="F134" s="22"/>
+      <c r="G134" s="22"/>
+      <c r="H134" s="22"/>
+      <c r="I134" s="22"/>
+      <c r="J134" s="22"/>
+      <c r="K134" s="22"/>
+      <c r="L134" s="22"/>
+      <c r="M134" s="22"/>
+      <c r="N134" s="22"/>
+      <c r="O134" s="22"/>
+      <c r="P134" s="22"/>
+      <c r="Q134" s="22"/>
+      <c r="R134" s="22"/>
+      <c r="S134" s="22"/>
+      <c r="T134" s="22"/>
+      <c r="U134" s="23"/>
+    </row>
+    <row r="135" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A135" s="21"/>
+      <c r="B135" s="22"/>
+      <c r="C135" s="22"/>
+      <c r="D135" s="22"/>
+      <c r="E135" s="22"/>
+      <c r="F135" s="22"/>
+      <c r="G135" s="22"/>
+      <c r="H135" s="22"/>
+      <c r="I135" s="22"/>
+      <c r="J135" s="22"/>
+      <c r="K135" s="22"/>
+      <c r="L135" s="22"/>
+      <c r="M135" s="22"/>
+      <c r="N135" s="22"/>
+      <c r="O135" s="22"/>
+      <c r="P135" s="22"/>
+      <c r="Q135" s="22"/>
+      <c r="R135" s="22"/>
+      <c r="S135" s="22"/>
+      <c r="T135" s="22"/>
+      <c r="U135" s="23"/>
+    </row>
+    <row r="136" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A136" s="21"/>
+      <c r="B136" s="22"/>
+      <c r="C136" s="22"/>
+      <c r="D136" s="22"/>
+      <c r="E136" s="22"/>
+      <c r="F136" s="22"/>
+      <c r="G136" s="22"/>
+      <c r="H136" s="22"/>
+      <c r="I136" s="22"/>
+      <c r="J136" s="22"/>
+      <c r="K136" s="22"/>
+      <c r="L136" s="22"/>
+      <c r="M136" s="22"/>
+      <c r="N136" s="22"/>
+      <c r="O136" s="22"/>
+      <c r="P136" s="22"/>
+      <c r="Q136" s="22"/>
+      <c r="R136" s="22"/>
+      <c r="S136" s="22"/>
+      <c r="T136" s="22"/>
+      <c r="U136" s="23"/>
+    </row>
+    <row r="137" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A137" s="21"/>
+      <c r="B137" s="22"/>
+      <c r="C137" s="22"/>
+      <c r="D137" s="22"/>
+      <c r="E137" s="22"/>
+      <c r="F137" s="22"/>
+      <c r="G137" s="22"/>
+      <c r="H137" s="22"/>
+      <c r="I137" s="22"/>
+      <c r="J137" s="22"/>
+      <c r="K137" s="22"/>
+      <c r="L137" s="22"/>
+      <c r="M137" s="22"/>
+      <c r="N137" s="22"/>
+      <c r="O137" s="22"/>
+      <c r="P137" s="22"/>
+      <c r="Q137" s="22"/>
+      <c r="R137" s="22"/>
+      <c r="S137" s="22"/>
+      <c r="T137" s="22"/>
+      <c r="U137" s="23"/>
+    </row>
+    <row r="138" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A138" s="21"/>
+      <c r="B138" s="22"/>
+      <c r="C138" s="22"/>
+      <c r="D138" s="22"/>
+      <c r="E138" s="22"/>
+      <c r="F138" s="22"/>
+      <c r="G138" s="22"/>
+      <c r="H138" s="22"/>
+      <c r="I138" s="22"/>
+      <c r="J138" s="22"/>
+      <c r="K138" s="22"/>
+      <c r="L138" s="22"/>
+      <c r="M138" s="22"/>
+      <c r="N138" s="22"/>
+      <c r="O138" s="22"/>
+      <c r="P138" s="22"/>
+      <c r="Q138" s="22"/>
+      <c r="R138" s="22"/>
+      <c r="S138" s="22"/>
+      <c r="T138" s="22"/>
+      <c r="U138" s="23"/>
+    </row>
+    <row r="139" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A139" s="21"/>
+      <c r="B139" s="22"/>
+      <c r="C139" s="22"/>
+      <c r="D139" s="22"/>
+      <c r="E139" s="22"/>
+      <c r="F139" s="22"/>
+      <c r="G139" s="22"/>
+      <c r="H139" s="22"/>
+      <c r="I139" s="22"/>
+      <c r="J139" s="22"/>
+      <c r="K139" s="22"/>
+      <c r="L139" s="22"/>
+      <c r="M139" s="22"/>
+      <c r="N139" s="22"/>
+      <c r="O139" s="22"/>
+      <c r="P139" s="22"/>
+      <c r="Q139" s="22"/>
+      <c r="R139" s="22"/>
+      <c r="S139" s="22"/>
+      <c r="T139" s="22"/>
+      <c r="U139" s="23"/>
+    </row>
+    <row r="140" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A140" s="21"/>
+      <c r="B140" s="22"/>
+      <c r="C140" s="22"/>
+      <c r="D140" s="22"/>
+      <c r="E140" s="22"/>
+      <c r="F140" s="22"/>
+      <c r="G140" s="22"/>
+      <c r="H140" s="22"/>
+      <c r="I140" s="22"/>
+      <c r="J140" s="22"/>
+      <c r="K140" s="22"/>
+      <c r="L140" s="22"/>
+      <c r="M140" s="22"/>
+      <c r="N140" s="22"/>
+      <c r="O140" s="22"/>
+      <c r="P140" s="22"/>
+      <c r="Q140" s="22"/>
+      <c r="R140" s="22"/>
+      <c r="S140" s="22"/>
+      <c r="T140" s="22"/>
+      <c r="U140" s="23"/>
+    </row>
+    <row r="141" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A141" s="21"/>
+      <c r="B141" s="22"/>
+      <c r="C141" s="22"/>
+      <c r="D141" s="22"/>
+      <c r="E141" s="22"/>
+      <c r="F141" s="22"/>
+      <c r="G141" s="22"/>
+      <c r="H141" s="22"/>
+      <c r="I141" s="22"/>
+      <c r="J141" s="22"/>
+      <c r="K141" s="22"/>
+      <c r="L141" s="22"/>
+      <c r="M141" s="22"/>
+      <c r="N141" s="22"/>
+      <c r="O141" s="22"/>
+      <c r="P141" s="22"/>
+      <c r="Q141" s="22"/>
+      <c r="R141" s="22"/>
+      <c r="S141" s="22"/>
+      <c r="T141" s="22"/>
+      <c r="U141" s="23"/>
+    </row>
+    <row r="142" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A142" s="21"/>
+      <c r="B142" s="22"/>
+      <c r="C142" s="22"/>
+      <c r="D142" s="22"/>
+      <c r="E142" s="22"/>
+      <c r="F142" s="22"/>
+      <c r="G142" s="22"/>
+      <c r="H142" s="22"/>
+      <c r="I142" s="22"/>
+      <c r="J142" s="22"/>
+      <c r="K142" s="22"/>
+      <c r="L142" s="22"/>
+      <c r="M142" s="22"/>
+      <c r="N142" s="22"/>
+      <c r="O142" s="22"/>
+      <c r="P142" s="22"/>
+      <c r="Q142" s="22"/>
+      <c r="R142" s="22"/>
+      <c r="S142" s="22"/>
+      <c r="T142" s="22"/>
+      <c r="U142" s="23"/>
+    </row>
+    <row r="143" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A143" s="21"/>
+      <c r="B143" s="22"/>
+      <c r="C143" s="22"/>
+      <c r="D143" s="22"/>
+      <c r="E143" s="22"/>
+      <c r="F143" s="22"/>
+      <c r="G143" s="22"/>
+      <c r="H143" s="22"/>
+      <c r="I143" s="22"/>
+      <c r="J143" s="22"/>
+      <c r="K143" s="22"/>
+      <c r="L143" s="22"/>
+      <c r="M143" s="22"/>
+      <c r="N143" s="22"/>
+      <c r="O143" s="22"/>
+      <c r="P143" s="22"/>
+      <c r="Q143" s="22"/>
+      <c r="R143" s="22"/>
+      <c r="S143" s="22"/>
+      <c r="T143" s="22"/>
+      <c r="U143" s="23"/>
+    </row>
+    <row r="144" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A144" s="21"/>
+      <c r="B144" s="22"/>
+      <c r="C144" s="22"/>
+      <c r="D144" s="22"/>
+      <c r="E144" s="22"/>
+      <c r="F144" s="22"/>
+      <c r="G144" s="22"/>
+      <c r="H144" s="22"/>
+      <c r="I144" s="22"/>
+      <c r="J144" s="22"/>
+      <c r="K144" s="22"/>
+      <c r="L144" s="22"/>
+      <c r="M144" s="22"/>
+      <c r="N144" s="22"/>
+      <c r="O144" s="22"/>
+      <c r="P144" s="22"/>
+      <c r="Q144" s="22"/>
+      <c r="R144" s="22"/>
+      <c r="S144" s="22"/>
+      <c r="T144" s="22"/>
+      <c r="U144" s="23"/>
+    </row>
+    <row r="145" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A145" s="21"/>
+      <c r="B145" s="22"/>
+      <c r="C145" s="22"/>
+      <c r="D145" s="22"/>
+      <c r="E145" s="22"/>
+      <c r="F145" s="22"/>
+      <c r="G145" s="22"/>
+      <c r="H145" s="22"/>
+      <c r="I145" s="22"/>
+      <c r="J145" s="22"/>
+      <c r="K145" s="22"/>
+      <c r="L145" s="22"/>
+      <c r="M145" s="22"/>
+      <c r="N145" s="22"/>
+      <c r="O145" s="22"/>
+      <c r="P145" s="22"/>
+      <c r="Q145" s="22"/>
+      <c r="R145" s="22"/>
+      <c r="S145" s="22"/>
+      <c r="T145" s="22"/>
+      <c r="U145" s="23"/>
+    </row>
+    <row r="146" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A146" s="21"/>
+      <c r="B146" s="22"/>
+      <c r="C146" s="22"/>
+      <c r="D146" s="22"/>
+      <c r="E146" s="22"/>
+      <c r="F146" s="22"/>
+      <c r="G146" s="22"/>
+      <c r="H146" s="22"/>
+      <c r="I146" s="22"/>
+      <c r="J146" s="22"/>
+      <c r="K146" s="22"/>
+      <c r="L146" s="22"/>
+      <c r="M146" s="22"/>
+      <c r="N146" s="22"/>
+      <c r="O146" s="22"/>
+      <c r="P146" s="22"/>
+      <c r="Q146" s="22"/>
+      <c r="R146" s="22"/>
+      <c r="S146" s="22"/>
+      <c r="T146" s="22"/>
+      <c r="U146" s="23"/>
+    </row>
+    <row r="147" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A147" s="21"/>
+      <c r="B147" s="22"/>
+      <c r="C147" s="22"/>
+      <c r="D147" s="22"/>
+      <c r="E147" s="22"/>
+      <c r="F147" s="22"/>
+      <c r="G147" s="22"/>
+      <c r="H147" s="22"/>
+      <c r="I147" s="22"/>
+      <c r="J147" s="22"/>
+      <c r="K147" s="22"/>
+      <c r="L147" s="22"/>
+      <c r="M147" s="22"/>
+      <c r="N147" s="22"/>
+      <c r="O147" s="22"/>
+      <c r="P147" s="22"/>
+      <c r="Q147" s="22"/>
+      <c r="R147" s="22"/>
+      <c r="S147" s="22"/>
+      <c r="T147" s="22"/>
+      <c r="U147" s="23"/>
+    </row>
+    <row r="148" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A148" s="24"/>
+      <c r="B148" s="25"/>
+      <c r="C148" s="25"/>
+      <c r="D148" s="25"/>
+      <c r="E148" s="25"/>
+      <c r="F148" s="25"/>
+      <c r="G148" s="25"/>
+      <c r="H148" s="25"/>
+      <c r="I148" s="25"/>
+      <c r="J148" s="25"/>
+      <c r="K148" s="25"/>
+      <c r="L148" s="25"/>
+      <c r="M148" s="25"/>
+      <c r="N148" s="25"/>
+      <c r="O148" s="25"/>
+      <c r="P148" s="25"/>
+      <c r="Q148" s="25"/>
+      <c r="R148" s="25"/>
+      <c r="S148" s="25"/>
+      <c r="T148" s="25"/>
+      <c r="U148" s="26"/>
+    </row>
+    <row r="151" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A151" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="152" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A152" s="18"/>
+      <c r="B152" s="19"/>
+      <c r="C152" s="19"/>
+      <c r="D152" s="19"/>
+      <c r="E152" s="19"/>
+      <c r="F152" s="19"/>
+      <c r="G152" s="19"/>
+      <c r="H152" s="19"/>
+      <c r="I152" s="19"/>
+      <c r="J152" s="19"/>
+      <c r="K152" s="19"/>
+      <c r="L152" s="19"/>
+      <c r="M152" s="19"/>
+      <c r="N152" s="19"/>
+      <c r="O152" s="19"/>
+      <c r="P152" s="19"/>
+      <c r="Q152" s="19"/>
+      <c r="R152" s="19"/>
+      <c r="S152" s="19"/>
+      <c r="T152" s="19"/>
+      <c r="U152" s="19"/>
+      <c r="V152" s="20"/>
+    </row>
+    <row r="153" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A153" s="21"/>
+      <c r="B153" s="22"/>
+      <c r="C153" s="22"/>
+      <c r="D153" s="22"/>
+      <c r="E153" s="22"/>
+      <c r="F153" s="22"/>
+      <c r="G153" s="22"/>
+      <c r="H153" s="22"/>
+      <c r="I153" s="22"/>
+      <c r="J153" s="22"/>
+      <c r="K153" s="22"/>
+      <c r="L153" s="22"/>
+      <c r="M153" s="22"/>
+      <c r="N153" s="22"/>
+      <c r="O153" s="22"/>
+      <c r="P153" s="22"/>
+      <c r="Q153" s="22"/>
+      <c r="R153" s="22"/>
+      <c r="S153" s="22"/>
+      <c r="T153" s="22"/>
+      <c r="U153" s="22"/>
+      <c r="V153" s="23"/>
+    </row>
+    <row r="154" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A154" s="21"/>
+      <c r="B154" s="22"/>
+      <c r="C154" s="22"/>
+      <c r="D154" s="22"/>
+      <c r="E154" s="22"/>
+      <c r="F154" s="22"/>
+      <c r="G154" s="22"/>
+      <c r="H154" s="22"/>
+      <c r="I154" s="22"/>
+      <c r="J154" s="22"/>
+      <c r="K154" s="22"/>
+      <c r="L154" s="22"/>
+      <c r="M154" s="22"/>
+      <c r="N154" s="22"/>
+      <c r="O154" s="22"/>
+      <c r="P154" s="22"/>
+      <c r="Q154" s="22"/>
+      <c r="R154" s="22"/>
+      <c r="S154" s="22"/>
+      <c r="T154" s="22"/>
+      <c r="U154" s="22"/>
+      <c r="V154" s="23"/>
+    </row>
+    <row r="155" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A155" s="21"/>
+      <c r="B155" s="22"/>
+      <c r="C155" s="22"/>
+      <c r="D155" s="22"/>
+      <c r="E155" s="22"/>
+      <c r="F155" s="22"/>
+      <c r="G155" s="22"/>
+      <c r="H155" s="22"/>
+      <c r="I155" s="22"/>
+      <c r="J155" s="22"/>
+      <c r="K155" s="22"/>
+      <c r="L155" s="22"/>
+      <c r="M155" s="22"/>
+      <c r="N155" s="22"/>
+      <c r="O155" s="22"/>
+      <c r="P155" s="22"/>
+      <c r="Q155" s="22"/>
+      <c r="R155" s="22"/>
+      <c r="S155" s="22"/>
+      <c r="T155" s="22"/>
+      <c r="U155" s="22"/>
+      <c r="V155" s="23"/>
+    </row>
+    <row r="156" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A156" s="21"/>
+      <c r="B156" s="22"/>
+      <c r="C156" s="22"/>
+      <c r="D156" s="22"/>
+      <c r="E156" s="22"/>
+      <c r="F156" s="22"/>
+      <c r="G156" s="22"/>
+      <c r="H156" s="22"/>
+      <c r="I156" s="22"/>
+      <c r="J156" s="22"/>
+      <c r="K156" s="22"/>
+      <c r="L156" s="22"/>
+      <c r="M156" s="22"/>
+      <c r="N156" s="22"/>
+      <c r="O156" s="22"/>
+      <c r="P156" s="22"/>
+      <c r="Q156" s="22"/>
+      <c r="R156" s="22"/>
+      <c r="S156" s="22"/>
+      <c r="T156" s="22"/>
+      <c r="U156" s="22"/>
+      <c r="V156" s="23"/>
+    </row>
+    <row r="157" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A157" s="21"/>
+      <c r="B157" s="22"/>
+      <c r="C157" s="22"/>
+      <c r="D157" s="22"/>
+      <c r="E157" s="22"/>
+      <c r="F157" s="22"/>
+      <c r="G157" s="22"/>
+      <c r="H157" s="22"/>
+      <c r="I157" s="22"/>
+      <c r="J157" s="22"/>
+      <c r="K157" s="22"/>
+      <c r="L157" s="22"/>
+      <c r="M157" s="22"/>
+      <c r="N157" s="22"/>
+      <c r="O157" s="22"/>
+      <c r="P157" s="22"/>
+      <c r="Q157" s="22"/>
+      <c r="R157" s="22"/>
+      <c r="S157" s="22"/>
+      <c r="T157" s="22"/>
+      <c r="U157" s="22"/>
+      <c r="V157" s="23"/>
+    </row>
+    <row r="158" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A158" s="21"/>
+      <c r="B158" s="22"/>
+      <c r="C158" s="22"/>
+      <c r="D158" s="22"/>
+      <c r="E158" s="22"/>
+      <c r="F158" s="22"/>
+      <c r="G158" s="22"/>
+      <c r="H158" s="22"/>
+      <c r="I158" s="22"/>
+      <c r="J158" s="22"/>
+      <c r="K158" s="22"/>
+      <c r="L158" s="22"/>
+      <c r="M158" s="22"/>
+      <c r="N158" s="22"/>
+      <c r="O158" s="22"/>
+      <c r="P158" s="22"/>
+      <c r="Q158" s="22"/>
+      <c r="R158" s="22"/>
+      <c r="S158" s="22"/>
+      <c r="T158" s="22"/>
+      <c r="U158" s="22"/>
+      <c r="V158" s="23"/>
+    </row>
+    <row r="159" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A159" s="21"/>
+      <c r="B159" s="22"/>
+      <c r="C159" s="22"/>
+      <c r="D159" s="22"/>
+      <c r="E159" s="22"/>
+      <c r="F159" s="22"/>
+      <c r="G159" s="22"/>
+      <c r="H159" s="22"/>
+      <c r="I159" s="22"/>
+      <c r="J159" s="22"/>
+      <c r="K159" s="22"/>
+      <c r="L159" s="22"/>
+      <c r="M159" s="22"/>
+      <c r="N159" s="22"/>
+      <c r="O159" s="22"/>
+      <c r="P159" s="22"/>
+      <c r="Q159" s="22"/>
+      <c r="R159" s="22"/>
+      <c r="S159" s="22"/>
+      <c r="T159" s="22"/>
+      <c r="U159" s="22"/>
+      <c r="V159" s="23"/>
+    </row>
+    <row r="160" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A160" s="21"/>
+      <c r="B160" s="22"/>
+      <c r="C160" s="22"/>
+      <c r="D160" s="22"/>
+      <c r="E160" s="22"/>
+      <c r="F160" s="22"/>
+      <c r="G160" s="22"/>
+      <c r="H160" s="22"/>
+      <c r="I160" s="22"/>
+      <c r="J160" s="22"/>
+      <c r="K160" s="22"/>
+      <c r="L160" s="22"/>
+      <c r="M160" s="22"/>
+      <c r="N160" s="22"/>
+      <c r="O160" s="22"/>
+      <c r="P160" s="22"/>
+      <c r="Q160" s="22"/>
+      <c r="R160" s="22"/>
+      <c r="S160" s="22"/>
+      <c r="T160" s="22"/>
+      <c r="U160" s="22"/>
+      <c r="V160" s="23"/>
+    </row>
+    <row r="161" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A161" s="21"/>
+      <c r="B161" s="22"/>
+      <c r="C161" s="22"/>
+      <c r="D161" s="22"/>
+      <c r="E161" s="22"/>
+      <c r="F161" s="22"/>
+      <c r="G161" s="22"/>
+      <c r="H161" s="22"/>
+      <c r="I161" s="22"/>
+      <c r="J161" s="22"/>
+      <c r="K161" s="22"/>
+      <c r="L161" s="22"/>
+      <c r="M161" s="22"/>
+      <c r="N161" s="22"/>
+      <c r="O161" s="22"/>
+      <c r="P161" s="22"/>
+      <c r="Q161" s="22"/>
+      <c r="R161" s="22"/>
+      <c r="S161" s="22"/>
+      <c r="T161" s="22"/>
+      <c r="U161" s="22"/>
+      <c r="V161" s="23"/>
+    </row>
+    <row r="162" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A162" s="21"/>
+      <c r="B162" s="22"/>
+      <c r="C162" s="22"/>
+      <c r="D162" s="22"/>
+      <c r="E162" s="22"/>
+      <c r="F162" s="22"/>
+      <c r="G162" s="22"/>
+      <c r="H162" s="22"/>
+      <c r="I162" s="22"/>
+      <c r="J162" s="22"/>
+      <c r="K162" s="22"/>
+      <c r="L162" s="22"/>
+      <c r="M162" s="22"/>
+      <c r="N162" s="22"/>
+      <c r="O162" s="22"/>
+      <c r="P162" s="22"/>
+      <c r="Q162" s="22"/>
+      <c r="R162" s="22"/>
+      <c r="S162" s="22"/>
+      <c r="T162" s="22"/>
+      <c r="U162" s="22"/>
+      <c r="V162" s="23"/>
+    </row>
+    <row r="163" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A163" s="21"/>
+      <c r="B163" s="22"/>
+      <c r="C163" s="22"/>
+      <c r="D163" s="22"/>
+      <c r="E163" s="22"/>
+      <c r="F163" s="22"/>
+      <c r="G163" s="22"/>
+      <c r="H163" s="22"/>
+      <c r="I163" s="22"/>
+      <c r="J163" s="22"/>
+      <c r="K163" s="22"/>
+      <c r="L163" s="22"/>
+      <c r="M163" s="22"/>
+      <c r="N163" s="22"/>
+      <c r="O163" s="22"/>
+      <c r="P163" s="22"/>
+      <c r="Q163" s="22"/>
+      <c r="R163" s="22"/>
+      <c r="S163" s="22"/>
+      <c r="T163" s="22"/>
+      <c r="U163" s="22"/>
+      <c r="V163" s="23"/>
+    </row>
+    <row r="164" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A164" s="21"/>
+      <c r="B164" s="22"/>
+      <c r="C164" s="22"/>
+      <c r="D164" s="22"/>
+      <c r="E164" s="22"/>
+      <c r="F164" s="22"/>
+      <c r="G164" s="22"/>
+      <c r="H164" s="22"/>
+      <c r="I164" s="22"/>
+      <c r="J164" s="22"/>
+      <c r="K164" s="22"/>
+      <c r="L164" s="22"/>
+      <c r="M164" s="22"/>
+      <c r="N164" s="22"/>
+      <c r="O164" s="22"/>
+      <c r="P164" s="22"/>
+      <c r="Q164" s="22"/>
+      <c r="R164" s="22"/>
+      <c r="S164" s="22"/>
+      <c r="T164" s="22"/>
+      <c r="U164" s="22"/>
+      <c r="V164" s="23"/>
+    </row>
+    <row r="165" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A165" s="21"/>
+      <c r="B165" s="22"/>
+      <c r="C165" s="22"/>
+      <c r="D165" s="22"/>
+      <c r="E165" s="22"/>
+      <c r="F165" s="22"/>
+      <c r="G165" s="22"/>
+      <c r="H165" s="22"/>
+      <c r="I165" s="22"/>
+      <c r="J165" s="22"/>
+      <c r="K165" s="22"/>
+      <c r="L165" s="22"/>
+      <c r="M165" s="22"/>
+      <c r="N165" s="22"/>
+      <c r="O165" s="22"/>
+      <c r="P165" s="22"/>
+      <c r="Q165" s="22"/>
+      <c r="R165" s="22"/>
+      <c r="S165" s="22"/>
+      <c r="T165" s="22"/>
+      <c r="U165" s="22"/>
+      <c r="V165" s="23"/>
+    </row>
+    <row r="166" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A166" s="21"/>
+      <c r="B166" s="22"/>
+      <c r="C166" s="22"/>
+      <c r="D166" s="22"/>
+      <c r="E166" s="22"/>
+      <c r="F166" s="22"/>
+      <c r="G166" s="22"/>
+      <c r="H166" s="22"/>
+      <c r="I166" s="22"/>
+      <c r="J166" s="22"/>
+      <c r="K166" s="22"/>
+      <c r="L166" s="22"/>
+      <c r="M166" s="22"/>
+      <c r="N166" s="22"/>
+      <c r="O166" s="22"/>
+      <c r="P166" s="22"/>
+      <c r="Q166" s="22"/>
+      <c r="R166" s="22"/>
+      <c r="S166" s="22"/>
+      <c r="T166" s="22"/>
+      <c r="U166" s="22"/>
+      <c r="V166" s="23"/>
+    </row>
+    <row r="167" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A167" s="21"/>
+      <c r="B167" s="22"/>
+      <c r="C167" s="22"/>
+      <c r="D167" s="22"/>
+      <c r="E167" s="22"/>
+      <c r="F167" s="22"/>
+      <c r="G167" s="22"/>
+      <c r="H167" s="22"/>
+      <c r="I167" s="22"/>
+      <c r="J167" s="22"/>
+      <c r="K167" s="22"/>
+      <c r="L167" s="22"/>
+      <c r="M167" s="22"/>
+      <c r="N167" s="22"/>
+      <c r="O167" s="22"/>
+      <c r="P167" s="22"/>
+      <c r="Q167" s="22"/>
+      <c r="R167" s="22"/>
+      <c r="S167" s="22"/>
+      <c r="T167" s="22"/>
+      <c r="U167" s="22"/>
+      <c r="V167" s="23"/>
+    </row>
+    <row r="168" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A168" s="21"/>
+      <c r="B168" s="22"/>
+      <c r="C168" s="22"/>
+      <c r="D168" s="22"/>
+      <c r="E168" s="22"/>
+      <c r="F168" s="22"/>
+      <c r="G168" s="22"/>
+      <c r="H168" s="22"/>
+      <c r="I168" s="22"/>
+      <c r="J168" s="22"/>
+      <c r="K168" s="22"/>
+      <c r="L168" s="22"/>
+      <c r="M168" s="22"/>
+      <c r="N168" s="22"/>
+      <c r="O168" s="22"/>
+      <c r="P168" s="22"/>
+      <c r="Q168" s="22"/>
+      <c r="R168" s="22"/>
+      <c r="S168" s="22"/>
+      <c r="T168" s="22"/>
+      <c r="U168" s="22"/>
+      <c r="V168" s="23"/>
+    </row>
+    <row r="169" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A169" s="21"/>
+      <c r="B169" s="22"/>
+      <c r="C169" s="22"/>
+      <c r="D169" s="22"/>
+      <c r="E169" s="22"/>
+      <c r="F169" s="22"/>
+      <c r="G169" s="22"/>
+      <c r="H169" s="22"/>
+      <c r="I169" s="22"/>
+      <c r="J169" s="22"/>
+      <c r="K169" s="22"/>
+      <c r="L169" s="22"/>
+      <c r="M169" s="22"/>
+      <c r="N169" s="22"/>
+      <c r="O169" s="22"/>
+      <c r="P169" s="22"/>
+      <c r="Q169" s="22"/>
+      <c r="R169" s="22"/>
+      <c r="S169" s="22"/>
+      <c r="T169" s="22"/>
+      <c r="U169" s="22"/>
+      <c r="V169" s="23"/>
+    </row>
+    <row r="170" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A170" s="21"/>
+      <c r="B170" s="22"/>
+      <c r="C170" s="22"/>
+      <c r="D170" s="22"/>
+      <c r="E170" s="22"/>
+      <c r="F170" s="22"/>
+      <c r="G170" s="22"/>
+      <c r="H170" s="22"/>
+      <c r="I170" s="22"/>
+      <c r="J170" s="22"/>
+      <c r="K170" s="22"/>
+      <c r="L170" s="22"/>
+      <c r="M170" s="22"/>
+      <c r="N170" s="22"/>
+      <c r="O170" s="22"/>
+      <c r="P170" s="22"/>
+      <c r="Q170" s="22"/>
+      <c r="R170" s="22"/>
+      <c r="S170" s="22"/>
+      <c r="T170" s="22"/>
+      <c r="U170" s="22"/>
+      <c r="V170" s="23"/>
+    </row>
+    <row r="171" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A171" s="21"/>
+      <c r="B171" s="22"/>
+      <c r="C171" s="22"/>
+      <c r="D171" s="22"/>
+      <c r="E171" s="22"/>
+      <c r="F171" s="22"/>
+      <c r="G171" s="22"/>
+      <c r="H171" s="22"/>
+      <c r="I171" s="22"/>
+      <c r="J171" s="22"/>
+      <c r="K171" s="22"/>
+      <c r="L171" s="22"/>
+      <c r="M171" s="22"/>
+      <c r="N171" s="22"/>
+      <c r="O171" s="22"/>
+      <c r="P171" s="22"/>
+      <c r="Q171" s="22"/>
+      <c r="R171" s="22"/>
+      <c r="S171" s="22"/>
+      <c r="T171" s="22"/>
+      <c r="U171" s="22"/>
+      <c r="V171" s="23"/>
+    </row>
+    <row r="172" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A172" s="21"/>
+      <c r="B172" s="22"/>
+      <c r="C172" s="22"/>
+      <c r="D172" s="22"/>
+      <c r="E172" s="22"/>
+      <c r="F172" s="22"/>
+      <c r="G172" s="22"/>
+      <c r="H172" s="22"/>
+      <c r="I172" s="22"/>
+      <c r="J172" s="22"/>
+      <c r="K172" s="22"/>
+      <c r="L172" s="22"/>
+      <c r="M172" s="22"/>
+      <c r="N172" s="22"/>
+      <c r="O172" s="22"/>
+      <c r="P172" s="22"/>
+      <c r="Q172" s="22"/>
+      <c r="R172" s="22"/>
+      <c r="S172" s="22"/>
+      <c r="T172" s="22"/>
+      <c r="U172" s="22"/>
+      <c r="V172" s="23"/>
+    </row>
+    <row r="173" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A173" s="21"/>
+      <c r="B173" s="22"/>
+      <c r="C173" s="22"/>
+      <c r="D173" s="22"/>
+      <c r="E173" s="22"/>
+      <c r="F173" s="22"/>
+      <c r="G173" s="22"/>
+      <c r="H173" s="22"/>
+      <c r="I173" s="22"/>
+      <c r="J173" s="22"/>
+      <c r="K173" s="22"/>
+      <c r="L173" s="22"/>
+      <c r="M173" s="22"/>
+      <c r="N173" s="22"/>
+      <c r="O173" s="22"/>
+      <c r="P173" s="22"/>
+      <c r="Q173" s="22"/>
+      <c r="R173" s="22"/>
+      <c r="S173" s="22"/>
+      <c r="T173" s="22"/>
+      <c r="U173" s="22"/>
+      <c r="V173" s="23"/>
+    </row>
+    <row r="174" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A174" s="21"/>
+      <c r="B174" s="22"/>
+      <c r="C174" s="22"/>
+      <c r="D174" s="22"/>
+      <c r="E174" s="22"/>
+      <c r="F174" s="22"/>
+      <c r="G174" s="22"/>
+      <c r="H174" s="22"/>
+      <c r="I174" s="22"/>
+      <c r="J174" s="22"/>
+      <c r="K174" s="22"/>
+      <c r="L174" s="22"/>
+      <c r="M174" s="22"/>
+      <c r="N174" s="22"/>
+      <c r="O174" s="22"/>
+      <c r="P174" s="22"/>
+      <c r="Q174" s="22"/>
+      <c r="R174" s="22"/>
+      <c r="S174" s="22"/>
+      <c r="T174" s="22"/>
+      <c r="U174" s="22"/>
+      <c r="V174" s="23"/>
+    </row>
+    <row r="175" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A175" s="21"/>
+      <c r="B175" s="22"/>
+      <c r="C175" s="22"/>
+      <c r="D175" s="22"/>
+      <c r="E175" s="22"/>
+      <c r="F175" s="22"/>
+      <c r="G175" s="22"/>
+      <c r="H175" s="22"/>
+      <c r="I175" s="22"/>
+      <c r="J175" s="22"/>
+      <c r="K175" s="22"/>
+      <c r="L175" s="22"/>
+      <c r="M175" s="22"/>
+      <c r="N175" s="22"/>
+      <c r="O175" s="22"/>
+      <c r="P175" s="22"/>
+      <c r="Q175" s="22"/>
+      <c r="R175" s="22"/>
+      <c r="S175" s="22"/>
+      <c r="T175" s="22"/>
+      <c r="U175" s="22"/>
+      <c r="V175" s="23"/>
+    </row>
+    <row r="176" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A176" s="21"/>
+      <c r="B176" s="22"/>
+      <c r="C176" s="22"/>
+      <c r="D176" s="22"/>
+      <c r="E176" s="22"/>
+      <c r="F176" s="22"/>
+      <c r="G176" s="22"/>
+      <c r="H176" s="22"/>
+      <c r="I176" s="22"/>
+      <c r="J176" s="22"/>
+      <c r="K176" s="22"/>
+      <c r="L176" s="22"/>
+      <c r="M176" s="22"/>
+      <c r="N176" s="22"/>
+      <c r="O176" s="22"/>
+      <c r="P176" s="22"/>
+      <c r="Q176" s="22"/>
+      <c r="R176" s="22"/>
+      <c r="S176" s="22"/>
+      <c r="T176" s="22"/>
+      <c r="U176" s="22"/>
+      <c r="V176" s="23"/>
+    </row>
+    <row r="177" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A177" s="21"/>
+      <c r="B177" s="22"/>
+      <c r="C177" s="22"/>
+      <c r="D177" s="22"/>
+      <c r="E177" s="22"/>
+      <c r="F177" s="22"/>
+      <c r="G177" s="22"/>
+      <c r="H177" s="22"/>
+      <c r="I177" s="22"/>
+      <c r="J177" s="22"/>
+      <c r="K177" s="22"/>
+      <c r="L177" s="22"/>
+      <c r="M177" s="22"/>
+      <c r="N177" s="22"/>
+      <c r="O177" s="22"/>
+      <c r="P177" s="22"/>
+      <c r="Q177" s="22"/>
+      <c r="R177" s="22"/>
+      <c r="S177" s="22"/>
+      <c r="T177" s="22"/>
+      <c r="U177" s="22"/>
+      <c r="V177" s="23"/>
+    </row>
+    <row r="178" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A178" s="21"/>
+      <c r="B178" s="22"/>
+      <c r="C178" s="22"/>
+      <c r="D178" s="22"/>
+      <c r="E178" s="22"/>
+      <c r="F178" s="22"/>
+      <c r="G178" s="22"/>
+      <c r="H178" s="22"/>
+      <c r="I178" s="22"/>
+      <c r="J178" s="22"/>
+      <c r="K178" s="22"/>
+      <c r="L178" s="22"/>
+      <c r="M178" s="22"/>
+      <c r="N178" s="22"/>
+      <c r="O178" s="22"/>
+      <c r="P178" s="22"/>
+      <c r="Q178" s="22"/>
+      <c r="R178" s="22"/>
+      <c r="S178" s="22"/>
+      <c r="T178" s="22"/>
+      <c r="U178" s="22"/>
+      <c r="V178" s="23"/>
+    </row>
+    <row r="179" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A179" s="21"/>
+      <c r="B179" s="22"/>
+      <c r="C179" s="22"/>
+      <c r="D179" s="22"/>
+      <c r="E179" s="22"/>
+      <c r="F179" s="22"/>
+      <c r="G179" s="22"/>
+      <c r="H179" s="22"/>
+      <c r="I179" s="22"/>
+      <c r="J179" s="22"/>
+      <c r="K179" s="22"/>
+      <c r="L179" s="22"/>
+      <c r="M179" s="22"/>
+      <c r="N179" s="22"/>
+      <c r="O179" s="22"/>
+      <c r="P179" s="22"/>
+      <c r="Q179" s="22"/>
+      <c r="R179" s="22"/>
+      <c r="S179" s="22"/>
+      <c r="T179" s="22"/>
+      <c r="U179" s="22"/>
+      <c r="V179" s="23"/>
+    </row>
+    <row r="180" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A180" s="21"/>
+      <c r="B180" s="22"/>
+      <c r="C180" s="22"/>
+      <c r="D180" s="22"/>
+      <c r="E180" s="22"/>
+      <c r="F180" s="22"/>
+      <c r="G180" s="22"/>
+      <c r="H180" s="22"/>
+      <c r="I180" s="22"/>
+      <c r="J180" s="22"/>
+      <c r="K180" s="22"/>
+      <c r="L180" s="22"/>
+      <c r="M180" s="22"/>
+      <c r="N180" s="22"/>
+      <c r="O180" s="22"/>
+      <c r="P180" s="22"/>
+      <c r="Q180" s="22"/>
+      <c r="R180" s="22"/>
+      <c r="S180" s="22"/>
+      <c r="T180" s="22"/>
+      <c r="U180" s="22"/>
+      <c r="V180" s="23"/>
+    </row>
+    <row r="181" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A181" s="21"/>
+      <c r="B181" s="22"/>
+      <c r="C181" s="22"/>
+      <c r="D181" s="22"/>
+      <c r="E181" s="22"/>
+      <c r="F181" s="22"/>
+      <c r="G181" s="22"/>
+      <c r="H181" s="22"/>
+      <c r="I181" s="22"/>
+      <c r="J181" s="22"/>
+      <c r="K181" s="22"/>
+      <c r="L181" s="22"/>
+      <c r="M181" s="22"/>
+      <c r="N181" s="22"/>
+      <c r="O181" s="22"/>
+      <c r="P181" s="22"/>
+      <c r="Q181" s="22"/>
+      <c r="R181" s="22"/>
+      <c r="S181" s="22"/>
+      <c r="T181" s="22"/>
+      <c r="U181" s="22"/>
+      <c r="V181" s="23"/>
+    </row>
+    <row r="182" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A182" s="21"/>
+      <c r="B182" s="22"/>
+      <c r="C182" s="22"/>
+      <c r="D182" s="22"/>
+      <c r="E182" s="22"/>
+      <c r="F182" s="22"/>
+      <c r="G182" s="22"/>
+      <c r="H182" s="22"/>
+      <c r="I182" s="22"/>
+      <c r="J182" s="22"/>
+      <c r="K182" s="22"/>
+      <c r="L182" s="22"/>
+      <c r="M182" s="22"/>
+      <c r="N182" s="22"/>
+      <c r="O182" s="22"/>
+      <c r="P182" s="22"/>
+      <c r="Q182" s="22"/>
+      <c r="R182" s="22"/>
+      <c r="S182" s="22"/>
+      <c r="T182" s="22"/>
+      <c r="U182" s="22"/>
+      <c r="V182" s="23"/>
+    </row>
+    <row r="183" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A183" s="21"/>
+      <c r="B183" s="22"/>
+      <c r="C183" s="22"/>
+      <c r="D183" s="22"/>
+      <c r="E183" s="22"/>
+      <c r="F183" s="22"/>
+      <c r="G183" s="22"/>
+      <c r="H183" s="22"/>
+      <c r="I183" s="22"/>
+      <c r="J183" s="22"/>
+      <c r="K183" s="22"/>
+      <c r="L183" s="22"/>
+      <c r="M183" s="22"/>
+      <c r="N183" s="22"/>
+      <c r="O183" s="22"/>
+      <c r="P183" s="22"/>
+      <c r="Q183" s="22"/>
+      <c r="R183" s="22"/>
+      <c r="S183" s="22"/>
+      <c r="T183" s="22"/>
+      <c r="U183" s="22"/>
+      <c r="V183" s="23"/>
+    </row>
+    <row r="184" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A184" s="21"/>
+      <c r="B184" s="22"/>
+      <c r="C184" s="22"/>
+      <c r="D184" s="22"/>
+      <c r="E184" s="22"/>
+      <c r="F184" s="22"/>
+      <c r="G184" s="22"/>
+      <c r="H184" s="22"/>
+      <c r="I184" s="22"/>
+      <c r="J184" s="22"/>
+      <c r="K184" s="22"/>
+      <c r="L184" s="22"/>
+      <c r="M184" s="22"/>
+      <c r="N184" s="22"/>
+      <c r="O184" s="22"/>
+      <c r="P184" s="22"/>
+      <c r="Q184" s="22"/>
+      <c r="R184" s="22"/>
+      <c r="S184" s="22"/>
+      <c r="T184" s="22"/>
+      <c r="U184" s="22"/>
+      <c r="V184" s="23"/>
+    </row>
+    <row r="185" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A185" s="21"/>
+      <c r="B185" s="22"/>
+      <c r="C185" s="22"/>
+      <c r="D185" s="22"/>
+      <c r="E185" s="22"/>
+      <c r="F185" s="22"/>
+      <c r="G185" s="22"/>
+      <c r="H185" s="22"/>
+      <c r="I185" s="22"/>
+      <c r="J185" s="22"/>
+      <c r="K185" s="22"/>
+      <c r="L185" s="22"/>
+      <c r="M185" s="22"/>
+      <c r="N185" s="22"/>
+      <c r="O185" s="22"/>
+      <c r="P185" s="22"/>
+      <c r="Q185" s="22"/>
+      <c r="R185" s="22"/>
+      <c r="S185" s="22"/>
+      <c r="T185" s="22"/>
+      <c r="U185" s="22"/>
+      <c r="V185" s="23"/>
+    </row>
+    <row r="186" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A186" s="21"/>
+      <c r="B186" s="22"/>
+      <c r="C186" s="22"/>
+      <c r="D186" s="22"/>
+      <c r="E186" s="22"/>
+      <c r="F186" s="22"/>
+      <c r="G186" s="22"/>
+      <c r="H186" s="22"/>
+      <c r="I186" s="22"/>
+      <c r="J186" s="22"/>
+      <c r="K186" s="22"/>
+      <c r="L186" s="22"/>
+      <c r="M186" s="22"/>
+      <c r="N186" s="22"/>
+      <c r="O186" s="22"/>
+      <c r="P186" s="22"/>
+      <c r="Q186" s="22"/>
+      <c r="R186" s="22"/>
+      <c r="S186" s="22"/>
+      <c r="T186" s="22"/>
+      <c r="U186" s="22"/>
+      <c r="V186" s="23"/>
+    </row>
+    <row r="187" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A187" s="21"/>
+      <c r="B187" s="22"/>
+      <c r="C187" s="22"/>
+      <c r="D187" s="22"/>
+      <c r="E187" s="22"/>
+      <c r="F187" s="22"/>
+      <c r="G187" s="22"/>
+      <c r="H187" s="22"/>
+      <c r="I187" s="22"/>
+      <c r="J187" s="22"/>
+      <c r="K187" s="22"/>
+      <c r="L187" s="22"/>
+      <c r="M187" s="22"/>
+      <c r="N187" s="22"/>
+      <c r="O187" s="22"/>
+      <c r="P187" s="22"/>
+      <c r="Q187" s="22"/>
+      <c r="R187" s="22"/>
+      <c r="S187" s="22"/>
+      <c r="T187" s="22"/>
+      <c r="U187" s="22"/>
+      <c r="V187" s="23"/>
+    </row>
+    <row r="188" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A188" s="21"/>
+      <c r="B188" s="22"/>
+      <c r="C188" s="22"/>
+      <c r="D188" s="22"/>
+      <c r="E188" s="22"/>
+      <c r="F188" s="22"/>
+      <c r="G188" s="22"/>
+      <c r="H188" s="22"/>
+      <c r="I188" s="22"/>
+      <c r="J188" s="22"/>
+      <c r="K188" s="22"/>
+      <c r="L188" s="22"/>
+      <c r="M188" s="22"/>
+      <c r="N188" s="22"/>
+      <c r="O188" s="22"/>
+      <c r="P188" s="22"/>
+      <c r="Q188" s="22"/>
+      <c r="R188" s="22"/>
+      <c r="S188" s="22"/>
+      <c r="T188" s="22"/>
+      <c r="U188" s="22"/>
+      <c r="V188" s="23"/>
+    </row>
+    <row r="189" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A189" s="21"/>
+      <c r="B189" s="22"/>
+      <c r="C189" s="22"/>
+      <c r="D189" s="22"/>
+      <c r="E189" s="22"/>
+      <c r="F189" s="22"/>
+      <c r="G189" s="22"/>
+      <c r="H189" s="22"/>
+      <c r="I189" s="22"/>
+      <c r="J189" s="22"/>
+      <c r="K189" s="22"/>
+      <c r="L189" s="22"/>
+      <c r="M189" s="22"/>
+      <c r="N189" s="22"/>
+      <c r="O189" s="22"/>
+      <c r="P189" s="22"/>
+      <c r="Q189" s="22"/>
+      <c r="R189" s="22"/>
+      <c r="S189" s="22"/>
+      <c r="T189" s="22"/>
+      <c r="U189" s="22"/>
+      <c r="V189" s="23"/>
+    </row>
+    <row r="190" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A190" s="21"/>
+      <c r="B190" s="22"/>
+      <c r="C190" s="22"/>
+      <c r="D190" s="22"/>
+      <c r="E190" s="22"/>
+      <c r="F190" s="22"/>
+      <c r="G190" s="22"/>
+      <c r="H190" s="22"/>
+      <c r="I190" s="22"/>
+      <c r="J190" s="22"/>
+      <c r="K190" s="22"/>
+      <c r="L190" s="22"/>
+      <c r="M190" s="22"/>
+      <c r="N190" s="22"/>
+      <c r="O190" s="22"/>
+      <c r="P190" s="22"/>
+      <c r="Q190" s="22"/>
+      <c r="R190" s="22"/>
+      <c r="S190" s="22"/>
+      <c r="T190" s="22"/>
+      <c r="U190" s="22"/>
+      <c r="V190" s="23"/>
+    </row>
+    <row r="191" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A191" s="21"/>
+      <c r="B191" s="22"/>
+      <c r="C191" s="22"/>
+      <c r="D191" s="22"/>
+      <c r="E191" s="22"/>
+      <c r="F191" s="22"/>
+      <c r="G191" s="22"/>
+      <c r="H191" s="22"/>
+      <c r="I191" s="22"/>
+      <c r="J191" s="22"/>
+      <c r="K191" s="22"/>
+      <c r="L191" s="22"/>
+      <c r="M191" s="22"/>
+      <c r="N191" s="22"/>
+      <c r="O191" s="22"/>
+      <c r="P191" s="22"/>
+      <c r="Q191" s="22"/>
+      <c r="R191" s="22"/>
+      <c r="S191" s="22"/>
+      <c r="T191" s="22"/>
+      <c r="U191" s="22"/>
+      <c r="V191" s="23"/>
+    </row>
+    <row r="192" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A192" s="21"/>
+      <c r="B192" s="22"/>
+      <c r="C192" s="22"/>
+      <c r="D192" s="22"/>
+      <c r="E192" s="22"/>
+      <c r="F192" s="22"/>
+      <c r="G192" s="22"/>
+      <c r="H192" s="22"/>
+      <c r="I192" s="22"/>
+      <c r="J192" s="22"/>
+      <c r="K192" s="22"/>
+      <c r="L192" s="22"/>
+      <c r="M192" s="22"/>
+      <c r="N192" s="22"/>
+      <c r="O192" s="22"/>
+      <c r="P192" s="22"/>
+      <c r="Q192" s="22"/>
+      <c r="R192" s="22"/>
+      <c r="S192" s="22"/>
+      <c r="T192" s="22"/>
+      <c r="U192" s="22"/>
+      <c r="V192" s="23"/>
+    </row>
+    <row r="193" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A193" s="21"/>
+      <c r="B193" s="22"/>
+      <c r="C193" s="22"/>
+      <c r="D193" s="22"/>
+      <c r="E193" s="22"/>
+      <c r="F193" s="22"/>
+      <c r="G193" s="22"/>
+      <c r="H193" s="22"/>
+      <c r="I193" s="22"/>
+      <c r="J193" s="22"/>
+      <c r="K193" s="22"/>
+      <c r="L193" s="22"/>
+      <c r="M193" s="22"/>
+      <c r="N193" s="22"/>
+      <c r="O193" s="22"/>
+      <c r="P193" s="22"/>
+      <c r="Q193" s="22"/>
+      <c r="R193" s="22"/>
+      <c r="S193" s="22"/>
+      <c r="T193" s="22"/>
+      <c r="U193" s="22"/>
+      <c r="V193" s="23"/>
+    </row>
+    <row r="194" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A194" s="21"/>
+      <c r="B194" s="22"/>
+      <c r="C194" s="22"/>
+      <c r="D194" s="22"/>
+      <c r="E194" s="22"/>
+      <c r="F194" s="22"/>
+      <c r="G194" s="22"/>
+      <c r="H194" s="22"/>
+      <c r="I194" s="22"/>
+      <c r="J194" s="22"/>
+      <c r="K194" s="22"/>
+      <c r="L194" s="22"/>
+      <c r="M194" s="22"/>
+      <c r="N194" s="22"/>
+      <c r="O194" s="22"/>
+      <c r="P194" s="22"/>
+      <c r="Q194" s="22"/>
+      <c r="R194" s="22"/>
+      <c r="S194" s="22"/>
+      <c r="T194" s="22"/>
+      <c r="U194" s="22"/>
+      <c r="V194" s="23"/>
+    </row>
+    <row r="195" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A195" s="21"/>
+      <c r="B195" s="22"/>
+      <c r="C195" s="22"/>
+      <c r="D195" s="22"/>
+      <c r="E195" s="22"/>
+      <c r="F195" s="22"/>
+      <c r="G195" s="22"/>
+      <c r="H195" s="22"/>
+      <c r="I195" s="22"/>
+      <c r="J195" s="22"/>
+      <c r="K195" s="22"/>
+      <c r="L195" s="22"/>
+      <c r="M195" s="22"/>
+      <c r="N195" s="22"/>
+      <c r="O195" s="22"/>
+      <c r="P195" s="22"/>
+      <c r="Q195" s="22"/>
+      <c r="R195" s="22"/>
+      <c r="S195" s="22"/>
+      <c r="T195" s="22"/>
+      <c r="U195" s="22"/>
+      <c r="V195" s="23"/>
+    </row>
+    <row r="196" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A196" s="21"/>
+      <c r="B196" s="22"/>
+      <c r="C196" s="22"/>
+      <c r="D196" s="22"/>
+      <c r="E196" s="22"/>
+      <c r="F196" s="22"/>
+      <c r="G196" s="22"/>
+      <c r="H196" s="22"/>
+      <c r="I196" s="22"/>
+      <c r="J196" s="22"/>
+      <c r="K196" s="22"/>
+      <c r="L196" s="22"/>
+      <c r="M196" s="22"/>
+      <c r="N196" s="22"/>
+      <c r="O196" s="22"/>
+      <c r="P196" s="22"/>
+      <c r="Q196" s="22"/>
+      <c r="R196" s="22"/>
+      <c r="S196" s="22"/>
+      <c r="T196" s="22"/>
+      <c r="U196" s="22"/>
+      <c r="V196" s="23"/>
+    </row>
+    <row r="197" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A197" s="21"/>
+      <c r="B197" s="22"/>
+      <c r="C197" s="22"/>
+      <c r="D197" s="22"/>
+      <c r="E197" s="22"/>
+      <c r="F197" s="22"/>
+      <c r="G197" s="22"/>
+      <c r="H197" s="22"/>
+      <c r="I197" s="22"/>
+      <c r="J197" s="22"/>
+      <c r="K197" s="22"/>
+      <c r="L197" s="22"/>
+      <c r="M197" s="22"/>
+      <c r="N197" s="22"/>
+      <c r="O197" s="22"/>
+      <c r="P197" s="22"/>
+      <c r="Q197" s="22"/>
+      <c r="R197" s="22"/>
+      <c r="S197" s="22"/>
+      <c r="T197" s="22"/>
+      <c r="U197" s="22"/>
+      <c r="V197" s="23"/>
+    </row>
+    <row r="198" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A198" s="24"/>
+      <c r="B198" s="25"/>
+      <c r="C198" s="25"/>
+      <c r="D198" s="25"/>
+      <c r="E198" s="25"/>
+      <c r="F198" s="25"/>
+      <c r="G198" s="25"/>
+      <c r="H198" s="25"/>
+      <c r="I198" s="25"/>
+      <c r="J198" s="25"/>
+      <c r="K198" s="25"/>
+      <c r="L198" s="25"/>
+      <c r="M198" s="25"/>
+      <c r="N198" s="25"/>
+      <c r="O198" s="25"/>
+      <c r="P198" s="25"/>
+      <c r="Q198" s="25"/>
+      <c r="R198" s="25"/>
+      <c r="S198" s="25"/>
+      <c r="T198" s="25"/>
+      <c r="U198" s="25"/>
+      <c r="V198" s="26"/>
+    </row>
+    <row r="201" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A201" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="E76" s="4"/>
-      <c r="F76" s="4"/>
-      <c r="G76" s="4"/>
-      <c r="H76" s="4"/>
-      <c r="I76" s="4"/>
-      <c r="J76" s="4"/>
-      <c r="K76" s="4"/>
-      <c r="L76" s="4"/>
-    </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="D77" s="4"/>
-      <c r="E77" s="4"/>
-      <c r="F77" s="4"/>
-      <c r="G77" s="4"/>
-      <c r="H77" s="4"/>
-      <c r="I77" s="4"/>
-      <c r="J77" s="4"/>
-      <c r="K77" s="4"/>
-      <c r="L77" s="4"/>
-    </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="D78" s="4"/>
-      <c r="E78" s="4"/>
-      <c r="F78" s="4"/>
-      <c r="G78" s="4"/>
-      <c r="H78" s="4"/>
-      <c r="I78" s="4"/>
-      <c r="J78" s="4"/>
-      <c r="K78" s="4"/>
-      <c r="L78" s="4"/>
-    </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="D79" s="4"/>
-      <c r="E79" s="4"/>
-      <c r="F79" s="4"/>
-      <c r="G79" s="4"/>
-      <c r="H79" s="4"/>
-      <c r="I79" s="4"/>
-      <c r="J79" s="4"/>
-      <c r="K79" s="4"/>
-      <c r="L79" s="4"/>
-    </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="D80" s="4"/>
-      <c r="E80" s="4"/>
-      <c r="F80" s="4"/>
-      <c r="G80" s="4"/>
-      <c r="H80" s="4"/>
-      <c r="I80" s="4"/>
-      <c r="J80" s="4"/>
-      <c r="K80" s="4"/>
-      <c r="L80" s="4"/>
-    </row>
-    <row r="81" spans="4:12" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="D81" s="4" t="s">
+    </row>
+    <row r="202" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A202" s="18"/>
+      <c r="B202" s="19"/>
+      <c r="C202" s="19"/>
+      <c r="D202" s="19"/>
+      <c r="E202" s="19"/>
+      <c r="F202" s="19"/>
+      <c r="G202" s="19"/>
+      <c r="H202" s="19"/>
+      <c r="I202" s="19"/>
+      <c r="J202" s="19"/>
+      <c r="K202" s="19"/>
+      <c r="L202" s="19"/>
+      <c r="M202" s="19"/>
+      <c r="N202" s="19"/>
+      <c r="O202" s="19"/>
+      <c r="P202" s="19"/>
+      <c r="Q202" s="19"/>
+      <c r="R202" s="19"/>
+      <c r="S202" s="19"/>
+      <c r="T202" s="19"/>
+      <c r="U202" s="20"/>
+    </row>
+    <row r="203" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A203" s="21"/>
+      <c r="B203" s="22"/>
+      <c r="C203" s="22"/>
+      <c r="D203" s="22"/>
+      <c r="E203" s="22"/>
+      <c r="F203" s="22"/>
+      <c r="G203" s="22"/>
+      <c r="H203" s="22"/>
+      <c r="I203" s="22"/>
+      <c r="J203" s="22"/>
+      <c r="K203" s="22"/>
+      <c r="L203" s="22"/>
+      <c r="M203" s="22"/>
+      <c r="N203" s="22"/>
+      <c r="O203" s="22"/>
+      <c r="P203" s="22"/>
+      <c r="Q203" s="22"/>
+      <c r="R203" s="22"/>
+      <c r="S203" s="22"/>
+      <c r="T203" s="22"/>
+      <c r="U203" s="23"/>
+    </row>
+    <row r="204" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A204" s="21"/>
+      <c r="B204" s="22"/>
+      <c r="C204" s="22"/>
+      <c r="D204" s="22"/>
+      <c r="E204" s="22"/>
+      <c r="F204" s="22"/>
+      <c r="G204" s="22"/>
+      <c r="H204" s="22"/>
+      <c r="I204" s="22"/>
+      <c r="J204" s="22"/>
+      <c r="K204" s="22"/>
+      <c r="L204" s="22"/>
+      <c r="M204" s="22"/>
+      <c r="N204" s="22"/>
+      <c r="O204" s="22"/>
+      <c r="P204" s="22"/>
+      <c r="Q204" s="22"/>
+      <c r="R204" s="22"/>
+      <c r="S204" s="22"/>
+      <c r="T204" s="22"/>
+      <c r="U204" s="23"/>
+    </row>
+    <row r="205" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A205" s="21"/>
+      <c r="B205" s="22"/>
+      <c r="C205" s="22"/>
+      <c r="D205" s="22"/>
+      <c r="E205" s="22"/>
+      <c r="F205" s="22"/>
+      <c r="G205" s="22"/>
+      <c r="H205" s="22"/>
+      <c r="I205" s="22"/>
+      <c r="J205" s="22"/>
+      <c r="K205" s="22"/>
+      <c r="L205" s="22"/>
+      <c r="M205" s="22"/>
+      <c r="N205" s="22"/>
+      <c r="O205" s="22"/>
+      <c r="P205" s="22"/>
+      <c r="Q205" s="22"/>
+      <c r="R205" s="22"/>
+      <c r="S205" s="22"/>
+      <c r="T205" s="22"/>
+      <c r="U205" s="23"/>
+    </row>
+    <row r="206" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A206" s="21"/>
+      <c r="B206" s="22"/>
+      <c r="C206" s="22"/>
+      <c r="D206" s="22"/>
+      <c r="E206" s="22"/>
+      <c r="F206" s="22"/>
+      <c r="G206" s="22"/>
+      <c r="H206" s="22"/>
+      <c r="I206" s="22"/>
+      <c r="J206" s="22"/>
+      <c r="K206" s="22"/>
+      <c r="L206" s="22"/>
+      <c r="M206" s="22"/>
+      <c r="N206" s="22"/>
+      <c r="O206" s="22"/>
+      <c r="P206" s="22"/>
+      <c r="Q206" s="22"/>
+      <c r="R206" s="22"/>
+      <c r="S206" s="22"/>
+      <c r="T206" s="22"/>
+      <c r="U206" s="23"/>
+    </row>
+    <row r="207" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A207" s="21"/>
+      <c r="B207" s="22"/>
+      <c r="C207" s="22"/>
+      <c r="D207" s="22"/>
+      <c r="E207" s="22"/>
+      <c r="F207" s="22"/>
+      <c r="G207" s="22"/>
+      <c r="H207" s="22"/>
+      <c r="I207" s="22"/>
+      <c r="J207" s="22"/>
+      <c r="K207" s="22"/>
+      <c r="L207" s="22"/>
+      <c r="M207" s="22"/>
+      <c r="N207" s="22"/>
+      <c r="O207" s="22"/>
+      <c r="P207" s="22"/>
+      <c r="Q207" s="22"/>
+      <c r="R207" s="22"/>
+      <c r="S207" s="22"/>
+      <c r="T207" s="22"/>
+      <c r="U207" s="23"/>
+    </row>
+    <row r="208" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A208" s="21"/>
+      <c r="B208" s="22"/>
+      <c r="C208" s="22"/>
+      <c r="D208" s="22"/>
+      <c r="E208" s="22"/>
+      <c r="F208" s="22"/>
+      <c r="G208" s="22"/>
+      <c r="H208" s="22"/>
+      <c r="I208" s="22"/>
+      <c r="J208" s="22"/>
+      <c r="K208" s="22"/>
+      <c r="L208" s="22"/>
+      <c r="M208" s="22"/>
+      <c r="N208" s="22"/>
+      <c r="O208" s="22"/>
+      <c r="P208" s="22"/>
+      <c r="Q208" s="22"/>
+      <c r="R208" s="22"/>
+      <c r="S208" s="22"/>
+      <c r="T208" s="22"/>
+      <c r="U208" s="23"/>
+    </row>
+    <row r="209" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A209" s="21"/>
+      <c r="B209" s="22"/>
+      <c r="C209" s="22"/>
+      <c r="D209" s="22"/>
+      <c r="E209" s="22"/>
+      <c r="F209" s="22"/>
+      <c r="G209" s="22"/>
+      <c r="H209" s="22"/>
+      <c r="I209" s="22"/>
+      <c r="J209" s="22"/>
+      <c r="K209" s="22"/>
+      <c r="L209" s="22"/>
+      <c r="M209" s="22"/>
+      <c r="N209" s="22"/>
+      <c r="O209" s="22"/>
+      <c r="P209" s="22"/>
+      <c r="Q209" s="22"/>
+      <c r="R209" s="22"/>
+      <c r="S209" s="22"/>
+      <c r="T209" s="22"/>
+      <c r="U209" s="23"/>
+    </row>
+    <row r="210" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A210" s="21"/>
+      <c r="B210" s="22"/>
+      <c r="C210" s="22"/>
+      <c r="D210" s="22"/>
+      <c r="E210" s="22"/>
+      <c r="F210" s="22"/>
+      <c r="G210" s="22"/>
+      <c r="H210" s="22"/>
+      <c r="I210" s="22"/>
+      <c r="J210" s="22"/>
+      <c r="K210" s="22"/>
+      <c r="L210" s="22"/>
+      <c r="M210" s="22"/>
+      <c r="N210" s="22"/>
+      <c r="O210" s="22"/>
+      <c r="P210" s="22"/>
+      <c r="Q210" s="22"/>
+      <c r="R210" s="22"/>
+      <c r="S210" s="22"/>
+      <c r="T210" s="22"/>
+      <c r="U210" s="23"/>
+    </row>
+    <row r="211" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A211" s="21"/>
+      <c r="B211" s="22"/>
+      <c r="C211" s="22"/>
+      <c r="D211" s="22"/>
+      <c r="E211" s="22"/>
+      <c r="F211" s="22"/>
+      <c r="G211" s="22"/>
+      <c r="H211" s="22"/>
+      <c r="I211" s="22"/>
+      <c r="J211" s="22"/>
+      <c r="K211" s="22"/>
+      <c r="L211" s="22"/>
+      <c r="M211" s="22"/>
+      <c r="N211" s="22"/>
+      <c r="O211" s="22"/>
+      <c r="P211" s="22"/>
+      <c r="Q211" s="22"/>
+      <c r="R211" s="22"/>
+      <c r="S211" s="22"/>
+      <c r="T211" s="22"/>
+      <c r="U211" s="23"/>
+    </row>
+    <row r="212" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A212" s="21"/>
+      <c r="B212" s="22"/>
+      <c r="C212" s="22"/>
+      <c r="D212" s="22"/>
+      <c r="E212" s="22"/>
+      <c r="F212" s="22"/>
+      <c r="G212" s="22"/>
+      <c r="H212" s="22"/>
+      <c r="I212" s="22"/>
+      <c r="J212" s="22"/>
+      <c r="K212" s="22"/>
+      <c r="L212" s="22"/>
+      <c r="M212" s="22"/>
+      <c r="N212" s="22"/>
+      <c r="O212" s="22"/>
+      <c r="P212" s="22"/>
+      <c r="Q212" s="22"/>
+      <c r="R212" s="22"/>
+      <c r="S212" s="22"/>
+      <c r="T212" s="22"/>
+      <c r="U212" s="23"/>
+    </row>
+    <row r="213" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A213" s="21"/>
+      <c r="B213" s="22"/>
+      <c r="C213" s="22"/>
+      <c r="D213" s="22"/>
+      <c r="E213" s="22"/>
+      <c r="F213" s="22"/>
+      <c r="G213" s="22"/>
+      <c r="H213" s="22"/>
+      <c r="I213" s="22"/>
+      <c r="J213" s="22"/>
+      <c r="K213" s="22"/>
+      <c r="L213" s="22"/>
+      <c r="M213" s="22"/>
+      <c r="N213" s="22"/>
+      <c r="O213" s="22"/>
+      <c r="P213" s="22"/>
+      <c r="Q213" s="22"/>
+      <c r="R213" s="22"/>
+      <c r="S213" s="22"/>
+      <c r="T213" s="22"/>
+      <c r="U213" s="23"/>
+    </row>
+    <row r="214" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A214" s="21"/>
+      <c r="B214" s="22"/>
+      <c r="C214" s="22"/>
+      <c r="D214" s="22"/>
+      <c r="E214" s="22"/>
+      <c r="F214" s="22"/>
+      <c r="G214" s="22"/>
+      <c r="H214" s="22"/>
+      <c r="I214" s="22"/>
+      <c r="J214" s="22"/>
+      <c r="K214" s="22"/>
+      <c r="L214" s="22"/>
+      <c r="M214" s="22"/>
+      <c r="N214" s="22"/>
+      <c r="O214" s="22"/>
+      <c r="P214" s="22"/>
+      <c r="Q214" s="22"/>
+      <c r="R214" s="22"/>
+      <c r="S214" s="22"/>
+      <c r="T214" s="22"/>
+      <c r="U214" s="23"/>
+    </row>
+    <row r="215" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A215" s="21"/>
+      <c r="B215" s="22"/>
+      <c r="C215" s="22"/>
+      <c r="D215" s="22"/>
+      <c r="E215" s="22"/>
+      <c r="F215" s="22"/>
+      <c r="G215" s="22"/>
+      <c r="H215" s="22"/>
+      <c r="I215" s="22"/>
+      <c r="J215" s="22"/>
+      <c r="K215" s="22"/>
+      <c r="L215" s="22"/>
+      <c r="M215" s="22"/>
+      <c r="N215" s="22"/>
+      <c r="O215" s="22"/>
+      <c r="P215" s="22"/>
+      <c r="Q215" s="22"/>
+      <c r="R215" s="22"/>
+      <c r="S215" s="22"/>
+      <c r="T215" s="22"/>
+      <c r="U215" s="23"/>
+    </row>
+    <row r="216" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A216" s="21"/>
+      <c r="B216" s="22"/>
+      <c r="C216" s="22"/>
+      <c r="D216" s="22"/>
+      <c r="E216" s="22"/>
+      <c r="F216" s="22"/>
+      <c r="G216" s="22"/>
+      <c r="H216" s="22"/>
+      <c r="I216" s="22"/>
+      <c r="J216" s="22"/>
+      <c r="K216" s="22"/>
+      <c r="L216" s="22"/>
+      <c r="M216" s="22"/>
+      <c r="N216" s="22"/>
+      <c r="O216" s="22"/>
+      <c r="P216" s="22"/>
+      <c r="Q216" s="22"/>
+      <c r="R216" s="22"/>
+      <c r="S216" s="22"/>
+      <c r="T216" s="22"/>
+      <c r="U216" s="23"/>
+    </row>
+    <row r="217" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A217" s="21"/>
+      <c r="B217" s="22"/>
+      <c r="C217" s="22"/>
+      <c r="D217" s="22"/>
+      <c r="E217" s="22"/>
+      <c r="F217" s="22"/>
+      <c r="G217" s="22"/>
+      <c r="H217" s="22"/>
+      <c r="I217" s="22"/>
+      <c r="J217" s="22"/>
+      <c r="K217" s="22"/>
+      <c r="L217" s="22"/>
+      <c r="M217" s="22"/>
+      <c r="N217" s="22"/>
+      <c r="O217" s="22"/>
+      <c r="P217" s="22"/>
+      <c r="Q217" s="22"/>
+      <c r="R217" s="22"/>
+      <c r="S217" s="22"/>
+      <c r="T217" s="22"/>
+      <c r="U217" s="23"/>
+    </row>
+    <row r="218" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A218" s="21"/>
+      <c r="B218" s="22"/>
+      <c r="C218" s="22"/>
+      <c r="D218" s="22"/>
+      <c r="E218" s="22"/>
+      <c r="F218" s="22"/>
+      <c r="G218" s="22"/>
+      <c r="H218" s="22"/>
+      <c r="I218" s="22"/>
+      <c r="J218" s="22"/>
+      <c r="K218" s="22"/>
+      <c r="L218" s="22"/>
+      <c r="M218" s="22"/>
+      <c r="N218" s="22"/>
+      <c r="O218" s="22"/>
+      <c r="P218" s="22"/>
+      <c r="Q218" s="22"/>
+      <c r="R218" s="22"/>
+      <c r="S218" s="22"/>
+      <c r="T218" s="22"/>
+      <c r="U218" s="23"/>
+    </row>
+    <row r="219" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A219" s="21"/>
+      <c r="B219" s="22"/>
+      <c r="C219" s="22"/>
+      <c r="D219" s="22"/>
+      <c r="E219" s="22"/>
+      <c r="F219" s="22"/>
+      <c r="G219" s="22"/>
+      <c r="H219" s="22"/>
+      <c r="I219" s="22"/>
+      <c r="J219" s="22"/>
+      <c r="K219" s="22"/>
+      <c r="L219" s="22"/>
+      <c r="M219" s="22"/>
+      <c r="N219" s="22"/>
+      <c r="O219" s="22"/>
+      <c r="P219" s="22"/>
+      <c r="Q219" s="22"/>
+      <c r="R219" s="22"/>
+      <c r="S219" s="22"/>
+      <c r="T219" s="22"/>
+      <c r="U219" s="23"/>
+    </row>
+    <row r="220" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A220" s="21"/>
+      <c r="B220" s="22"/>
+      <c r="C220" s="22"/>
+      <c r="D220" s="22"/>
+      <c r="E220" s="22"/>
+      <c r="F220" s="22"/>
+      <c r="G220" s="22"/>
+      <c r="H220" s="22"/>
+      <c r="I220" s="22"/>
+      <c r="J220" s="22"/>
+      <c r="K220" s="22"/>
+      <c r="L220" s="22"/>
+      <c r="M220" s="22"/>
+      <c r="N220" s="22"/>
+      <c r="O220" s="22"/>
+      <c r="P220" s="22"/>
+      <c r="Q220" s="22"/>
+      <c r="R220" s="22"/>
+      <c r="S220" s="22"/>
+      <c r="T220" s="22"/>
+      <c r="U220" s="23"/>
+    </row>
+    <row r="221" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A221" s="21"/>
+      <c r="B221" s="22"/>
+      <c r="C221" s="22"/>
+      <c r="D221" s="22"/>
+      <c r="E221" s="22"/>
+      <c r="F221" s="22"/>
+      <c r="G221" s="22"/>
+      <c r="H221" s="22"/>
+      <c r="I221" s="22"/>
+      <c r="J221" s="22"/>
+      <c r="K221" s="22"/>
+      <c r="L221" s="22"/>
+      <c r="M221" s="22"/>
+      <c r="N221" s="22"/>
+      <c r="O221" s="22"/>
+      <c r="P221" s="22"/>
+      <c r="Q221" s="22"/>
+      <c r="R221" s="22"/>
+      <c r="S221" s="22"/>
+      <c r="T221" s="22"/>
+      <c r="U221" s="23"/>
+    </row>
+    <row r="222" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A222" s="21"/>
+      <c r="B222" s="22"/>
+      <c r="C222" s="22"/>
+      <c r="D222" s="22"/>
+      <c r="E222" s="22"/>
+      <c r="F222" s="22"/>
+      <c r="G222" s="22"/>
+      <c r="H222" s="22"/>
+      <c r="I222" s="22"/>
+      <c r="J222" s="22"/>
+      <c r="K222" s="22"/>
+      <c r="L222" s="22"/>
+      <c r="M222" s="22"/>
+      <c r="N222" s="22"/>
+      <c r="O222" s="22"/>
+      <c r="P222" s="22"/>
+      <c r="Q222" s="22"/>
+      <c r="R222" s="22"/>
+      <c r="S222" s="22"/>
+      <c r="T222" s="22"/>
+      <c r="U222" s="23"/>
+    </row>
+    <row r="223" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A223" s="21"/>
+      <c r="B223" s="22"/>
+      <c r="C223" s="22"/>
+      <c r="D223" s="22"/>
+      <c r="E223" s="22"/>
+      <c r="F223" s="22"/>
+      <c r="G223" s="22"/>
+      <c r="H223" s="22"/>
+      <c r="I223" s="22"/>
+      <c r="J223" s="22"/>
+      <c r="K223" s="22"/>
+      <c r="L223" s="22"/>
+      <c r="M223" s="22"/>
+      <c r="N223" s="22"/>
+      <c r="O223" s="22"/>
+      <c r="P223" s="22"/>
+      <c r="Q223" s="22"/>
+      <c r="R223" s="22"/>
+      <c r="S223" s="22"/>
+      <c r="T223" s="22"/>
+      <c r="U223" s="23"/>
+    </row>
+    <row r="224" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A224" s="21"/>
+      <c r="B224" s="22"/>
+      <c r="C224" s="22"/>
+      <c r="D224" s="22"/>
+      <c r="E224" s="22"/>
+      <c r="F224" s="22"/>
+      <c r="G224" s="22"/>
+      <c r="H224" s="22"/>
+      <c r="I224" s="22"/>
+      <c r="J224" s="22"/>
+      <c r="K224" s="22"/>
+      <c r="L224" s="22"/>
+      <c r="M224" s="22"/>
+      <c r="N224" s="22"/>
+      <c r="O224" s="22"/>
+      <c r="P224" s="22"/>
+      <c r="Q224" s="22"/>
+      <c r="R224" s="22"/>
+      <c r="S224" s="22"/>
+      <c r="T224" s="22"/>
+      <c r="U224" s="23"/>
+    </row>
+    <row r="225" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A225" s="21"/>
+      <c r="B225" s="22"/>
+      <c r="C225" s="22"/>
+      <c r="D225" s="22"/>
+      <c r="E225" s="22"/>
+      <c r="F225" s="22"/>
+      <c r="G225" s="22"/>
+      <c r="H225" s="22"/>
+      <c r="I225" s="22"/>
+      <c r="J225" s="22"/>
+      <c r="K225" s="22"/>
+      <c r="L225" s="22"/>
+      <c r="M225" s="22"/>
+      <c r="N225" s="22"/>
+      <c r="O225" s="22"/>
+      <c r="P225" s="22"/>
+      <c r="Q225" s="22"/>
+      <c r="R225" s="22"/>
+      <c r="S225" s="22"/>
+      <c r="T225" s="22"/>
+      <c r="U225" s="23"/>
+    </row>
+    <row r="226" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A226" s="21"/>
+      <c r="B226" s="22"/>
+      <c r="C226" s="22"/>
+      <c r="D226" s="22"/>
+      <c r="E226" s="22"/>
+      <c r="F226" s="22"/>
+      <c r="G226" s="22"/>
+      <c r="H226" s="22"/>
+      <c r="I226" s="22"/>
+      <c r="J226" s="22"/>
+      <c r="K226" s="22"/>
+      <c r="L226" s="22"/>
+      <c r="M226" s="22"/>
+      <c r="N226" s="22"/>
+      <c r="O226" s="22"/>
+      <c r="P226" s="22"/>
+      <c r="Q226" s="22"/>
+      <c r="R226" s="22"/>
+      <c r="S226" s="22"/>
+      <c r="T226" s="22"/>
+      <c r="U226" s="23"/>
+    </row>
+    <row r="227" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A227" s="21"/>
+      <c r="B227" s="22"/>
+      <c r="C227" s="22"/>
+      <c r="D227" s="22"/>
+      <c r="E227" s="22"/>
+      <c r="F227" s="22"/>
+      <c r="G227" s="22"/>
+      <c r="H227" s="22"/>
+      <c r="I227" s="22"/>
+      <c r="J227" s="22"/>
+      <c r="K227" s="22"/>
+      <c r="L227" s="22"/>
+      <c r="M227" s="22"/>
+      <c r="N227" s="22"/>
+      <c r="O227" s="22"/>
+      <c r="P227" s="22"/>
+      <c r="Q227" s="22"/>
+      <c r="R227" s="22"/>
+      <c r="S227" s="22"/>
+      <c r="T227" s="22"/>
+      <c r="U227" s="23"/>
+    </row>
+    <row r="228" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A228" s="21"/>
+      <c r="B228" s="22"/>
+      <c r="C228" s="22"/>
+      <c r="D228" s="22"/>
+      <c r="E228" s="22"/>
+      <c r="F228" s="22"/>
+      <c r="G228" s="22"/>
+      <c r="H228" s="22"/>
+      <c r="I228" s="22"/>
+      <c r="J228" s="22"/>
+      <c r="K228" s="22"/>
+      <c r="L228" s="22"/>
+      <c r="M228" s="22"/>
+      <c r="N228" s="22"/>
+      <c r="O228" s="22"/>
+      <c r="P228" s="22"/>
+      <c r="Q228" s="22"/>
+      <c r="R228" s="22"/>
+      <c r="S228" s="22"/>
+      <c r="T228" s="22"/>
+      <c r="U228" s="23"/>
+    </row>
+    <row r="229" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A229" s="21"/>
+      <c r="B229" s="22"/>
+      <c r="C229" s="22"/>
+      <c r="D229" s="22"/>
+      <c r="E229" s="22"/>
+      <c r="F229" s="22"/>
+      <c r="G229" s="22"/>
+      <c r="H229" s="22"/>
+      <c r="I229" s="22"/>
+      <c r="J229" s="22"/>
+      <c r="K229" s="22"/>
+      <c r="L229" s="22"/>
+      <c r="M229" s="22"/>
+      <c r="N229" s="22"/>
+      <c r="O229" s="22"/>
+      <c r="P229" s="22"/>
+      <c r="Q229" s="22"/>
+      <c r="R229" s="22"/>
+      <c r="S229" s="22"/>
+      <c r="T229" s="22"/>
+      <c r="U229" s="23"/>
+    </row>
+    <row r="230" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A230" s="21"/>
+      <c r="B230" s="22"/>
+      <c r="C230" s="22"/>
+      <c r="D230" s="22"/>
+      <c r="E230" s="22"/>
+      <c r="F230" s="22"/>
+      <c r="G230" s="22"/>
+      <c r="H230" s="22"/>
+      <c r="I230" s="22"/>
+      <c r="J230" s="22"/>
+      <c r="K230" s="22"/>
+      <c r="L230" s="22"/>
+      <c r="M230" s="22"/>
+      <c r="N230" s="22"/>
+      <c r="O230" s="22"/>
+      <c r="P230" s="22"/>
+      <c r="Q230" s="22"/>
+      <c r="R230" s="22"/>
+      <c r="S230" s="22"/>
+      <c r="T230" s="22"/>
+      <c r="U230" s="23"/>
+    </row>
+    <row r="231" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A231" s="21"/>
+      <c r="B231" s="22"/>
+      <c r="C231" s="22"/>
+      <c r="D231" s="22"/>
+      <c r="E231" s="22"/>
+      <c r="F231" s="22"/>
+      <c r="G231" s="22"/>
+      <c r="H231" s="22"/>
+      <c r="I231" s="22"/>
+      <c r="J231" s="22"/>
+      <c r="K231" s="22"/>
+      <c r="L231" s="22"/>
+      <c r="M231" s="22"/>
+      <c r="N231" s="22"/>
+      <c r="O231" s="22"/>
+      <c r="P231" s="22"/>
+      <c r="Q231" s="22"/>
+      <c r="R231" s="22"/>
+      <c r="S231" s="22"/>
+      <c r="T231" s="22"/>
+      <c r="U231" s="23"/>
+    </row>
+    <row r="232" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A232" s="21"/>
+      <c r="B232" s="22"/>
+      <c r="C232" s="22"/>
+      <c r="D232" s="22"/>
+      <c r="E232" s="22"/>
+      <c r="F232" s="22"/>
+      <c r="G232" s="22"/>
+      <c r="H232" s="22"/>
+      <c r="I232" s="22"/>
+      <c r="J232" s="22"/>
+      <c r="K232" s="22"/>
+      <c r="L232" s="22"/>
+      <c r="M232" s="22"/>
+      <c r="N232" s="22"/>
+      <c r="O232" s="22"/>
+      <c r="P232" s="22"/>
+      <c r="Q232" s="22"/>
+      <c r="R232" s="22"/>
+      <c r="S232" s="22"/>
+      <c r="T232" s="22"/>
+      <c r="U232" s="23"/>
+    </row>
+    <row r="233" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A233" s="21"/>
+      <c r="B233" s="22"/>
+      <c r="C233" s="22"/>
+      <c r="D233" s="22"/>
+      <c r="E233" s="22"/>
+      <c r="F233" s="22"/>
+      <c r="G233" s="22"/>
+      <c r="H233" s="22"/>
+      <c r="I233" s="22"/>
+      <c r="J233" s="22"/>
+      <c r="K233" s="22"/>
+      <c r="L233" s="22"/>
+      <c r="M233" s="22"/>
+      <c r="N233" s="22"/>
+      <c r="O233" s="22"/>
+      <c r="P233" s="22"/>
+      <c r="Q233" s="22"/>
+      <c r="R233" s="22"/>
+      <c r="S233" s="22"/>
+      <c r="T233" s="22"/>
+      <c r="U233" s="23"/>
+    </row>
+    <row r="234" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A234" s="21"/>
+      <c r="B234" s="22"/>
+      <c r="C234" s="22"/>
+      <c r="D234" s="22"/>
+      <c r="E234" s="22"/>
+      <c r="F234" s="22"/>
+      <c r="G234" s="22"/>
+      <c r="H234" s="22"/>
+      <c r="I234" s="22"/>
+      <c r="J234" s="22"/>
+      <c r="K234" s="22"/>
+      <c r="L234" s="22"/>
+      <c r="M234" s="22"/>
+      <c r="N234" s="22"/>
+      <c r="O234" s="22"/>
+      <c r="P234" s="22"/>
+      <c r="Q234" s="22"/>
+      <c r="R234" s="22"/>
+      <c r="S234" s="22"/>
+      <c r="T234" s="22"/>
+      <c r="U234" s="23"/>
+    </row>
+    <row r="235" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A235" s="21"/>
+      <c r="B235" s="22"/>
+      <c r="C235" s="22"/>
+      <c r="D235" s="22"/>
+      <c r="E235" s="22"/>
+      <c r="F235" s="22"/>
+      <c r="G235" s="22"/>
+      <c r="H235" s="22"/>
+      <c r="I235" s="22"/>
+      <c r="J235" s="22"/>
+      <c r="K235" s="22"/>
+      <c r="L235" s="22"/>
+      <c r="M235" s="22"/>
+      <c r="N235" s="22"/>
+      <c r="O235" s="22"/>
+      <c r="P235" s="22"/>
+      <c r="Q235" s="22"/>
+      <c r="R235" s="22"/>
+      <c r="S235" s="22"/>
+      <c r="T235" s="22"/>
+      <c r="U235" s="23"/>
+    </row>
+    <row r="236" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A236" s="21"/>
+      <c r="B236" s="22"/>
+      <c r="C236" s="22"/>
+      <c r="D236" s="22"/>
+      <c r="E236" s="22"/>
+      <c r="F236" s="22"/>
+      <c r="G236" s="22"/>
+      <c r="H236" s="22"/>
+      <c r="I236" s="22"/>
+      <c r="J236" s="22"/>
+      <c r="K236" s="22"/>
+      <c r="L236" s="22"/>
+      <c r="M236" s="22"/>
+      <c r="N236" s="22"/>
+      <c r="O236" s="22"/>
+      <c r="P236" s="22"/>
+      <c r="Q236" s="22"/>
+      <c r="R236" s="22"/>
+      <c r="S236" s="22"/>
+      <c r="T236" s="22"/>
+      <c r="U236" s="23"/>
+    </row>
+    <row r="237" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A237" s="21"/>
+      <c r="B237" s="22"/>
+      <c r="C237" s="22"/>
+      <c r="D237" s="22"/>
+      <c r="E237" s="22"/>
+      <c r="F237" s="22"/>
+      <c r="G237" s="22"/>
+      <c r="H237" s="22"/>
+      <c r="I237" s="22"/>
+      <c r="J237" s="22"/>
+      <c r="K237" s="22"/>
+      <c r="L237" s="22"/>
+      <c r="M237" s="22"/>
+      <c r="N237" s="22"/>
+      <c r="O237" s="22"/>
+      <c r="P237" s="22"/>
+      <c r="Q237" s="22"/>
+      <c r="R237" s="22"/>
+      <c r="S237" s="22"/>
+      <c r="T237" s="22"/>
+      <c r="U237" s="23"/>
+    </row>
+    <row r="238" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A238" s="21"/>
+      <c r="B238" s="22"/>
+      <c r="C238" s="22"/>
+      <c r="D238" s="22"/>
+      <c r="E238" s="22"/>
+      <c r="F238" s="22"/>
+      <c r="G238" s="22"/>
+      <c r="H238" s="22"/>
+      <c r="I238" s="22"/>
+      <c r="J238" s="22"/>
+      <c r="K238" s="22"/>
+      <c r="L238" s="22"/>
+      <c r="M238" s="22"/>
+      <c r="N238" s="22"/>
+      <c r="O238" s="22"/>
+      <c r="P238" s="22"/>
+      <c r="Q238" s="22"/>
+      <c r="R238" s="22"/>
+      <c r="S238" s="22"/>
+      <c r="T238" s="22"/>
+      <c r="U238" s="23"/>
+    </row>
+    <row r="239" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A239" s="21"/>
+      <c r="B239" s="22"/>
+      <c r="C239" s="22"/>
+      <c r="D239" s="22"/>
+      <c r="E239" s="22"/>
+      <c r="F239" s="22"/>
+      <c r="G239" s="22"/>
+      <c r="H239" s="22"/>
+      <c r="I239" s="22"/>
+      <c r="J239" s="22"/>
+      <c r="K239" s="22"/>
+      <c r="L239" s="22"/>
+      <c r="M239" s="22"/>
+      <c r="N239" s="22"/>
+      <c r="O239" s="22"/>
+      <c r="P239" s="22"/>
+      <c r="Q239" s="22"/>
+      <c r="R239" s="22"/>
+      <c r="S239" s="22"/>
+      <c r="T239" s="22"/>
+      <c r="U239" s="23"/>
+    </row>
+    <row r="240" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A240" s="21"/>
+      <c r="B240" s="22"/>
+      <c r="C240" s="22"/>
+      <c r="D240" s="22"/>
+      <c r="E240" s="22"/>
+      <c r="F240" s="22"/>
+      <c r="G240" s="22"/>
+      <c r="H240" s="22"/>
+      <c r="I240" s="22"/>
+      <c r="J240" s="22"/>
+      <c r="K240" s="22"/>
+      <c r="L240" s="22"/>
+      <c r="M240" s="22"/>
+      <c r="N240" s="22"/>
+      <c r="O240" s="22"/>
+      <c r="P240" s="22"/>
+      <c r="Q240" s="22"/>
+      <c r="R240" s="22"/>
+      <c r="S240" s="22"/>
+      <c r="T240" s="22"/>
+      <c r="U240" s="23"/>
+    </row>
+    <row r="241" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A241" s="21"/>
+      <c r="B241" s="22"/>
+      <c r="C241" s="22"/>
+      <c r="D241" s="22"/>
+      <c r="E241" s="22"/>
+      <c r="F241" s="22"/>
+      <c r="G241" s="22"/>
+      <c r="H241" s="22"/>
+      <c r="I241" s="22"/>
+      <c r="J241" s="22"/>
+      <c r="K241" s="22"/>
+      <c r="L241" s="22"/>
+      <c r="M241" s="22"/>
+      <c r="N241" s="22"/>
+      <c r="O241" s="22"/>
+      <c r="P241" s="22"/>
+      <c r="Q241" s="22"/>
+      <c r="R241" s="22"/>
+      <c r="S241" s="22"/>
+      <c r="T241" s="22"/>
+      <c r="U241" s="23"/>
+    </row>
+    <row r="242" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A242" s="21"/>
+      <c r="B242" s="22"/>
+      <c r="C242" s="22"/>
+      <c r="D242" s="22"/>
+      <c r="E242" s="22"/>
+      <c r="F242" s="22"/>
+      <c r="G242" s="22"/>
+      <c r="H242" s="22"/>
+      <c r="I242" s="22"/>
+      <c r="J242" s="22"/>
+      <c r="K242" s="22"/>
+      <c r="L242" s="22"/>
+      <c r="M242" s="22"/>
+      <c r="N242" s="22"/>
+      <c r="O242" s="22"/>
+      <c r="P242" s="22"/>
+      <c r="Q242" s="22"/>
+      <c r="R242" s="22"/>
+      <c r="S242" s="22"/>
+      <c r="T242" s="22"/>
+      <c r="U242" s="23"/>
+    </row>
+    <row r="243" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A243" s="21"/>
+      <c r="B243" s="22"/>
+      <c r="C243" s="22"/>
+      <c r="D243" s="22"/>
+      <c r="E243" s="22"/>
+      <c r="F243" s="22"/>
+      <c r="G243" s="22"/>
+      <c r="H243" s="22"/>
+      <c r="I243" s="22"/>
+      <c r="J243" s="22"/>
+      <c r="K243" s="22"/>
+      <c r="L243" s="22"/>
+      <c r="M243" s="22"/>
+      <c r="N243" s="22"/>
+      <c r="O243" s="22"/>
+      <c r="P243" s="22"/>
+      <c r="Q243" s="22"/>
+      <c r="R243" s="22"/>
+      <c r="S243" s="22"/>
+      <c r="T243" s="22"/>
+      <c r="U243" s="23"/>
+    </row>
+    <row r="244" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A244" s="21"/>
+      <c r="B244" s="22"/>
+      <c r="C244" s="22"/>
+      <c r="D244" s="22"/>
+      <c r="E244" s="22"/>
+      <c r="F244" s="22"/>
+      <c r="G244" s="22"/>
+      <c r="H244" s="22"/>
+      <c r="I244" s="22"/>
+      <c r="J244" s="22"/>
+      <c r="K244" s="22"/>
+      <c r="L244" s="22"/>
+      <c r="M244" s="22"/>
+      <c r="N244" s="22"/>
+      <c r="O244" s="22"/>
+      <c r="P244" s="22"/>
+      <c r="Q244" s="22"/>
+      <c r="R244" s="22"/>
+      <c r="S244" s="22"/>
+      <c r="T244" s="22"/>
+      <c r="U244" s="23"/>
+    </row>
+    <row r="245" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A245" s="21"/>
+      <c r="B245" s="22"/>
+      <c r="C245" s="22"/>
+      <c r="D245" s="22"/>
+      <c r="E245" s="22"/>
+      <c r="F245" s="22"/>
+      <c r="G245" s="22"/>
+      <c r="H245" s="22"/>
+      <c r="I245" s="22"/>
+      <c r="J245" s="22"/>
+      <c r="K245" s="22"/>
+      <c r="L245" s="22"/>
+      <c r="M245" s="22"/>
+      <c r="N245" s="22"/>
+      <c r="O245" s="22"/>
+      <c r="P245" s="22"/>
+      <c r="Q245" s="22"/>
+      <c r="R245" s="22"/>
+      <c r="S245" s="22"/>
+      <c r="T245" s="22"/>
+      <c r="U245" s="23"/>
+    </row>
+    <row r="246" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A246" s="21"/>
+      <c r="B246" s="22"/>
+      <c r="C246" s="22"/>
+      <c r="D246" s="22"/>
+      <c r="E246" s="22"/>
+      <c r="F246" s="22"/>
+      <c r="G246" s="22"/>
+      <c r="H246" s="22"/>
+      <c r="I246" s="22"/>
+      <c r="J246" s="22"/>
+      <c r="K246" s="22"/>
+      <c r="L246" s="22"/>
+      <c r="M246" s="22"/>
+      <c r="N246" s="22"/>
+      <c r="O246" s="22"/>
+      <c r="P246" s="22"/>
+      <c r="Q246" s="22"/>
+      <c r="R246" s="22"/>
+      <c r="S246" s="22"/>
+      <c r="T246" s="22"/>
+      <c r="U246" s="23"/>
+    </row>
+    <row r="247" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A247" s="21"/>
+      <c r="B247" s="22"/>
+      <c r="C247" s="22"/>
+      <c r="D247" s="22"/>
+      <c r="E247" s="22"/>
+      <c r="F247" s="22"/>
+      <c r="G247" s="22"/>
+      <c r="H247" s="22"/>
+      <c r="I247" s="22"/>
+      <c r="J247" s="22"/>
+      <c r="K247" s="22"/>
+      <c r="L247" s="22"/>
+      <c r="M247" s="22"/>
+      <c r="N247" s="22"/>
+      <c r="O247" s="22"/>
+      <c r="P247" s="22"/>
+      <c r="Q247" s="22"/>
+      <c r="R247" s="22"/>
+      <c r="S247" s="22"/>
+      <c r="T247" s="22"/>
+      <c r="U247" s="23"/>
+    </row>
+    <row r="248" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A248" s="21"/>
+      <c r="B248" s="22"/>
+      <c r="C248" s="22"/>
+      <c r="D248" s="22"/>
+      <c r="E248" s="22"/>
+      <c r="F248" s="22"/>
+      <c r="G248" s="22"/>
+      <c r="H248" s="22"/>
+      <c r="I248" s="22"/>
+      <c r="J248" s="22"/>
+      <c r="K248" s="22"/>
+      <c r="L248" s="22"/>
+      <c r="M248" s="22"/>
+      <c r="N248" s="22"/>
+      <c r="O248" s="22"/>
+      <c r="P248" s="22"/>
+      <c r="Q248" s="22"/>
+      <c r="R248" s="22"/>
+      <c r="S248" s="22"/>
+      <c r="T248" s="22"/>
+      <c r="U248" s="23"/>
+    </row>
+    <row r="249" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A249" s="21"/>
+      <c r="B249" s="22"/>
+      <c r="C249" s="22"/>
+      <c r="D249" s="22"/>
+      <c r="E249" s="22"/>
+      <c r="F249" s="22"/>
+      <c r="G249" s="22"/>
+      <c r="H249" s="22"/>
+      <c r="I249" s="22"/>
+      <c r="J249" s="22"/>
+      <c r="K249" s="22"/>
+      <c r="L249" s="22"/>
+      <c r="M249" s="22"/>
+      <c r="N249" s="22"/>
+      <c r="O249" s="22"/>
+      <c r="P249" s="22"/>
+      <c r="Q249" s="22"/>
+      <c r="R249" s="22"/>
+      <c r="S249" s="22"/>
+      <c r="T249" s="22"/>
+      <c r="U249" s="23"/>
+    </row>
+    <row r="250" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A250" s="21"/>
+      <c r="B250" s="22"/>
+      <c r="C250" s="22"/>
+      <c r="D250" s="22"/>
+      <c r="E250" s="22"/>
+      <c r="F250" s="22"/>
+      <c r="G250" s="22"/>
+      <c r="H250" s="22"/>
+      <c r="I250" s="22"/>
+      <c r="J250" s="22"/>
+      <c r="K250" s="22"/>
+      <c r="L250" s="22"/>
+      <c r="M250" s="22"/>
+      <c r="N250" s="22"/>
+      <c r="O250" s="22"/>
+      <c r="P250" s="22"/>
+      <c r="Q250" s="22"/>
+      <c r="R250" s="22"/>
+      <c r="S250" s="22"/>
+      <c r="T250" s="22"/>
+      <c r="U250" s="23"/>
+    </row>
+    <row r="251" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A251" s="21"/>
+      <c r="B251" s="22"/>
+      <c r="C251" s="22"/>
+      <c r="D251" s="22"/>
+      <c r="E251" s="22"/>
+      <c r="F251" s="22"/>
+      <c r="G251" s="22"/>
+      <c r="H251" s="22"/>
+      <c r="I251" s="22"/>
+      <c r="J251" s="22"/>
+      <c r="K251" s="22"/>
+      <c r="L251" s="22"/>
+      <c r="M251" s="22"/>
+      <c r="N251" s="22"/>
+      <c r="O251" s="22"/>
+      <c r="P251" s="22"/>
+      <c r="Q251" s="22"/>
+      <c r="R251" s="22"/>
+      <c r="S251" s="22"/>
+      <c r="T251" s="22"/>
+      <c r="U251" s="23"/>
+    </row>
+    <row r="252" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A252" s="21"/>
+      <c r="B252" s="22"/>
+      <c r="C252" s="22"/>
+      <c r="D252" s="22"/>
+      <c r="E252" s="22"/>
+      <c r="F252" s="22"/>
+      <c r="G252" s="22"/>
+      <c r="H252" s="22"/>
+      <c r="I252" s="22"/>
+      <c r="J252" s="22"/>
+      <c r="K252" s="22"/>
+      <c r="L252" s="22"/>
+      <c r="M252" s="22"/>
+      <c r="N252" s="22"/>
+      <c r="O252" s="22"/>
+      <c r="P252" s="22"/>
+      <c r="Q252" s="22"/>
+      <c r="R252" s="22"/>
+      <c r="S252" s="22"/>
+      <c r="T252" s="22"/>
+      <c r="U252" s="23"/>
+    </row>
+    <row r="253" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A253" s="21"/>
+      <c r="B253" s="22"/>
+      <c r="C253" s="22"/>
+      <c r="D253" s="22"/>
+      <c r="E253" s="22"/>
+      <c r="F253" s="22"/>
+      <c r="G253" s="22"/>
+      <c r="H253" s="22"/>
+      <c r="I253" s="22"/>
+      <c r="J253" s="22"/>
+      <c r="K253" s="22"/>
+      <c r="L253" s="22"/>
+      <c r="M253" s="22"/>
+      <c r="N253" s="22"/>
+      <c r="O253" s="22"/>
+      <c r="P253" s="22"/>
+      <c r="Q253" s="22"/>
+      <c r="R253" s="22"/>
+      <c r="S253" s="22"/>
+      <c r="T253" s="22"/>
+      <c r="U253" s="23"/>
+    </row>
+    <row r="254" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A254" s="21"/>
+      <c r="B254" s="22"/>
+      <c r="C254" s="22"/>
+      <c r="D254" s="22"/>
+      <c r="E254" s="22"/>
+      <c r="F254" s="22"/>
+      <c r="G254" s="22"/>
+      <c r="H254" s="22"/>
+      <c r="I254" s="22"/>
+      <c r="J254" s="22"/>
+      <c r="K254" s="22"/>
+      <c r="L254" s="22"/>
+      <c r="M254" s="22"/>
+      <c r="N254" s="22"/>
+      <c r="O254" s="22"/>
+      <c r="P254" s="22"/>
+      <c r="Q254" s="22"/>
+      <c r="R254" s="22"/>
+      <c r="S254" s="22"/>
+      <c r="T254" s="22"/>
+      <c r="U254" s="23"/>
+    </row>
+    <row r="255" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A255" s="21"/>
+      <c r="B255" s="22"/>
+      <c r="C255" s="22"/>
+      <c r="D255" s="22"/>
+      <c r="E255" s="22"/>
+      <c r="F255" s="22"/>
+      <c r="G255" s="22"/>
+      <c r="H255" s="22"/>
+      <c r="I255" s="22"/>
+      <c r="J255" s="22"/>
+      <c r="K255" s="22"/>
+      <c r="L255" s="22"/>
+      <c r="M255" s="22"/>
+      <c r="N255" s="22"/>
+      <c r="O255" s="22"/>
+      <c r="P255" s="22"/>
+      <c r="Q255" s="22"/>
+      <c r="R255" s="22"/>
+      <c r="S255" s="22"/>
+      <c r="T255" s="22"/>
+      <c r="U255" s="23"/>
+    </row>
+    <row r="256" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A256" s="21"/>
+      <c r="B256" s="22"/>
+      <c r="C256" s="22"/>
+      <c r="D256" s="22"/>
+      <c r="E256" s="22"/>
+      <c r="F256" s="22"/>
+      <c r="G256" s="22"/>
+      <c r="H256" s="22"/>
+      <c r="I256" s="22"/>
+      <c r="J256" s="22"/>
+      <c r="K256" s="22"/>
+      <c r="L256" s="22"/>
+      <c r="M256" s="22"/>
+      <c r="N256" s="22"/>
+      <c r="O256" s="22"/>
+      <c r="P256" s="22"/>
+      <c r="Q256" s="22"/>
+      <c r="R256" s="22"/>
+      <c r="S256" s="22"/>
+      <c r="T256" s="22"/>
+      <c r="U256" s="23"/>
+    </row>
+    <row r="257" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A257" s="21"/>
+      <c r="B257" s="22"/>
+      <c r="C257" s="22"/>
+      <c r="D257" s="22"/>
+      <c r="E257" s="22"/>
+      <c r="F257" s="22"/>
+      <c r="G257" s="22"/>
+      <c r="H257" s="22"/>
+      <c r="I257" s="22"/>
+      <c r="J257" s="22"/>
+      <c r="K257" s="22"/>
+      <c r="L257" s="22"/>
+      <c r="M257" s="22"/>
+      <c r="N257" s="22"/>
+      <c r="O257" s="22"/>
+      <c r="P257" s="22"/>
+      <c r="Q257" s="22"/>
+      <c r="R257" s="22"/>
+      <c r="S257" s="22"/>
+      <c r="T257" s="22"/>
+      <c r="U257" s="23"/>
+    </row>
+    <row r="258" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A258" s="21"/>
+      <c r="B258" s="22"/>
+      <c r="C258" s="22"/>
+      <c r="D258" s="22"/>
+      <c r="E258" s="22"/>
+      <c r="F258" s="22"/>
+      <c r="G258" s="22"/>
+      <c r="H258" s="22"/>
+      <c r="I258" s="22"/>
+      <c r="J258" s="22"/>
+      <c r="K258" s="22"/>
+      <c r="L258" s="22"/>
+      <c r="M258" s="22"/>
+      <c r="N258" s="22"/>
+      <c r="O258" s="22"/>
+      <c r="P258" s="22"/>
+      <c r="Q258" s="22"/>
+      <c r="R258" s="22"/>
+      <c r="S258" s="22"/>
+      <c r="T258" s="22"/>
+      <c r="U258" s="23"/>
+    </row>
+    <row r="259" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A259" s="21"/>
+      <c r="B259" s="22"/>
+      <c r="C259" s="22"/>
+      <c r="D259" s="22"/>
+      <c r="E259" s="22"/>
+      <c r="F259" s="22"/>
+      <c r="G259" s="22"/>
+      <c r="H259" s="22"/>
+      <c r="I259" s="22"/>
+      <c r="J259" s="22"/>
+      <c r="K259" s="22"/>
+      <c r="L259" s="22"/>
+      <c r="M259" s="22"/>
+      <c r="N259" s="22"/>
+      <c r="O259" s="22"/>
+      <c r="P259" s="22"/>
+      <c r="Q259" s="22"/>
+      <c r="R259" s="22"/>
+      <c r="S259" s="22"/>
+      <c r="T259" s="22"/>
+      <c r="U259" s="23"/>
+    </row>
+    <row r="260" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A260" s="21"/>
+      <c r="B260" s="22"/>
+      <c r="C260" s="22"/>
+      <c r="D260" s="22"/>
+      <c r="E260" s="22"/>
+      <c r="F260" s="22"/>
+      <c r="G260" s="22"/>
+      <c r="H260" s="22"/>
+      <c r="I260" s="22"/>
+      <c r="J260" s="22"/>
+      <c r="K260" s="22"/>
+      <c r="L260" s="22"/>
+      <c r="M260" s="22"/>
+      <c r="N260" s="22"/>
+      <c r="O260" s="22"/>
+      <c r="P260" s="22"/>
+      <c r="Q260" s="22"/>
+      <c r="R260" s="22"/>
+      <c r="S260" s="22"/>
+      <c r="T260" s="22"/>
+      <c r="U260" s="23"/>
+    </row>
+    <row r="261" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A261" s="21"/>
+      <c r="B261" s="22"/>
+      <c r="C261" s="22"/>
+      <c r="D261" s="22"/>
+      <c r="E261" s="22"/>
+      <c r="F261" s="22"/>
+      <c r="G261" s="22"/>
+      <c r="H261" s="22"/>
+      <c r="I261" s="22"/>
+      <c r="J261" s="22"/>
+      <c r="K261" s="22"/>
+      <c r="L261" s="22"/>
+      <c r="M261" s="22"/>
+      <c r="N261" s="22"/>
+      <c r="O261" s="22"/>
+      <c r="P261" s="22"/>
+      <c r="Q261" s="22"/>
+      <c r="R261" s="22"/>
+      <c r="S261" s="22"/>
+      <c r="T261" s="22"/>
+      <c r="U261" s="23"/>
+    </row>
+    <row r="262" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A262" s="21"/>
+      <c r="B262" s="22"/>
+      <c r="C262" s="22"/>
+      <c r="D262" s="22"/>
+      <c r="E262" s="22"/>
+      <c r="F262" s="22"/>
+      <c r="G262" s="22"/>
+      <c r="H262" s="22"/>
+      <c r="I262" s="22"/>
+      <c r="J262" s="22"/>
+      <c r="K262" s="22"/>
+      <c r="L262" s="22"/>
+      <c r="M262" s="22"/>
+      <c r="N262" s="22"/>
+      <c r="O262" s="22"/>
+      <c r="P262" s="22"/>
+      <c r="Q262" s="22"/>
+      <c r="R262" s="22"/>
+      <c r="S262" s="22"/>
+      <c r="T262" s="22"/>
+      <c r="U262" s="23"/>
+    </row>
+    <row r="263" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A263" s="21"/>
+      <c r="B263" s="22"/>
+      <c r="C263" s="22"/>
+      <c r="D263" s="22"/>
+      <c r="E263" s="22"/>
+      <c r="F263" s="22"/>
+      <c r="G263" s="22"/>
+      <c r="H263" s="22"/>
+      <c r="I263" s="22"/>
+      <c r="J263" s="22"/>
+      <c r="K263" s="22"/>
+      <c r="L263" s="22"/>
+      <c r="M263" s="22"/>
+      <c r="N263" s="22"/>
+      <c r="O263" s="22"/>
+      <c r="P263" s="22"/>
+      <c r="Q263" s="22"/>
+      <c r="R263" s="22"/>
+      <c r="S263" s="22"/>
+      <c r="T263" s="22"/>
+      <c r="U263" s="23"/>
+    </row>
+    <row r="264" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A264" s="21"/>
+      <c r="B264" s="22"/>
+      <c r="C264" s="22"/>
+      <c r="D264" s="22"/>
+      <c r="E264" s="22"/>
+      <c r="F264" s="22"/>
+      <c r="G264" s="22"/>
+      <c r="H264" s="22"/>
+      <c r="I264" s="22"/>
+      <c r="J264" s="22"/>
+      <c r="K264" s="22"/>
+      <c r="L264" s="22"/>
+      <c r="M264" s="22"/>
+      <c r="N264" s="22"/>
+      <c r="O264" s="22"/>
+      <c r="P264" s="22"/>
+      <c r="Q264" s="22"/>
+      <c r="R264" s="22"/>
+      <c r="S264" s="22"/>
+      <c r="T264" s="22"/>
+      <c r="U264" s="23"/>
+    </row>
+    <row r="265" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A265" s="21"/>
+      <c r="B265" s="22"/>
+      <c r="C265" s="22"/>
+      <c r="D265" s="22"/>
+      <c r="E265" s="22"/>
+      <c r="F265" s="22"/>
+      <c r="G265" s="22"/>
+      <c r="H265" s="22"/>
+      <c r="I265" s="22"/>
+      <c r="J265" s="22"/>
+      <c r="K265" s="22"/>
+      <c r="L265" s="22"/>
+      <c r="M265" s="22"/>
+      <c r="N265" s="22"/>
+      <c r="O265" s="22"/>
+      <c r="P265" s="22"/>
+      <c r="Q265" s="22"/>
+      <c r="R265" s="22"/>
+      <c r="S265" s="22"/>
+      <c r="T265" s="22"/>
+      <c r="U265" s="23"/>
+    </row>
+    <row r="266" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A266" s="21"/>
+      <c r="B266" s="22"/>
+      <c r="C266" s="22"/>
+      <c r="D266" s="22"/>
+      <c r="E266" s="22"/>
+      <c r="F266" s="22"/>
+      <c r="G266" s="22"/>
+      <c r="H266" s="22"/>
+      <c r="I266" s="22"/>
+      <c r="J266" s="22"/>
+      <c r="K266" s="22"/>
+      <c r="L266" s="22"/>
+      <c r="M266" s="22"/>
+      <c r="N266" s="22"/>
+      <c r="O266" s="22"/>
+      <c r="P266" s="22"/>
+      <c r="Q266" s="22"/>
+      <c r="R266" s="22"/>
+      <c r="S266" s="22"/>
+      <c r="T266" s="22"/>
+      <c r="U266" s="23"/>
+    </row>
+    <row r="267" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A267" s="21"/>
+      <c r="B267" s="22"/>
+      <c r="C267" s="22"/>
+      <c r="D267" s="22"/>
+      <c r="E267" s="22"/>
+      <c r="F267" s="22"/>
+      <c r="G267" s="22"/>
+      <c r="H267" s="22"/>
+      <c r="I267" s="22"/>
+      <c r="J267" s="22"/>
+      <c r="K267" s="22"/>
+      <c r="L267" s="22"/>
+      <c r="M267" s="22"/>
+      <c r="N267" s="22"/>
+      <c r="O267" s="22"/>
+      <c r="P267" s="22"/>
+      <c r="Q267" s="22"/>
+      <c r="R267" s="22"/>
+      <c r="S267" s="22"/>
+      <c r="T267" s="22"/>
+      <c r="U267" s="23"/>
+    </row>
+    <row r="268" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A268" s="21"/>
+      <c r="B268" s="22"/>
+      <c r="C268" s="22"/>
+      <c r="D268" s="22"/>
+      <c r="E268" s="22"/>
+      <c r="F268" s="22"/>
+      <c r="G268" s="22"/>
+      <c r="H268" s="22"/>
+      <c r="I268" s="22"/>
+      <c r="J268" s="22"/>
+      <c r="K268" s="22"/>
+      <c r="L268" s="22"/>
+      <c r="M268" s="22"/>
+      <c r="N268" s="22"/>
+      <c r="O268" s="22"/>
+      <c r="P268" s="22"/>
+      <c r="Q268" s="22"/>
+      <c r="R268" s="22"/>
+      <c r="S268" s="22"/>
+      <c r="T268" s="22"/>
+      <c r="U268" s="23"/>
+    </row>
+    <row r="269" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A269" s="21"/>
+      <c r="B269" s="22"/>
+      <c r="C269" s="22"/>
+      <c r="D269" s="22"/>
+      <c r="E269" s="22"/>
+      <c r="F269" s="22"/>
+      <c r="G269" s="22"/>
+      <c r="H269" s="22"/>
+      <c r="I269" s="22"/>
+      <c r="J269" s="22"/>
+      <c r="K269" s="22"/>
+      <c r="L269" s="22"/>
+      <c r="M269" s="22"/>
+      <c r="N269" s="22"/>
+      <c r="O269" s="22"/>
+      <c r="P269" s="22"/>
+      <c r="Q269" s="22"/>
+      <c r="R269" s="22"/>
+      <c r="S269" s="22"/>
+      <c r="T269" s="22"/>
+      <c r="U269" s="23"/>
+    </row>
+    <row r="270" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A270" s="21"/>
+      <c r="B270" s="22"/>
+      <c r="C270" s="22"/>
+      <c r="D270" s="22"/>
+      <c r="E270" s="22"/>
+      <c r="F270" s="22"/>
+      <c r="G270" s="22"/>
+      <c r="H270" s="22"/>
+      <c r="I270" s="22"/>
+      <c r="J270" s="22"/>
+      <c r="K270" s="22"/>
+      <c r="L270" s="22"/>
+      <c r="M270" s="22"/>
+      <c r="N270" s="22"/>
+      <c r="O270" s="22"/>
+      <c r="P270" s="22"/>
+      <c r="Q270" s="22"/>
+      <c r="R270" s="22"/>
+      <c r="S270" s="22"/>
+      <c r="T270" s="22"/>
+      <c r="U270" s="23"/>
+    </row>
+    <row r="271" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A271" s="21"/>
+      <c r="B271" s="22"/>
+      <c r="C271" s="22"/>
+      <c r="D271" s="22"/>
+      <c r="E271" s="22"/>
+      <c r="F271" s="22"/>
+      <c r="G271" s="22"/>
+      <c r="H271" s="22"/>
+      <c r="I271" s="22"/>
+      <c r="J271" s="22"/>
+      <c r="K271" s="22"/>
+      <c r="L271" s="22"/>
+      <c r="M271" s="22"/>
+      <c r="N271" s="22"/>
+      <c r="O271" s="22"/>
+      <c r="P271" s="22"/>
+      <c r="Q271" s="22"/>
+      <c r="R271" s="22"/>
+      <c r="S271" s="22"/>
+      <c r="T271" s="22"/>
+      <c r="U271" s="23"/>
+    </row>
+    <row r="272" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A272" s="24"/>
+      <c r="B272" s="25"/>
+      <c r="C272" s="25"/>
+      <c r="D272" s="25"/>
+      <c r="E272" s="25"/>
+      <c r="F272" s="25"/>
+      <c r="G272" s="25"/>
+      <c r="H272" s="25"/>
+      <c r="I272" s="25"/>
+      <c r="J272" s="25"/>
+      <c r="K272" s="25"/>
+      <c r="L272" s="25"/>
+      <c r="M272" s="25"/>
+      <c r="N272" s="25"/>
+      <c r="O272" s="25"/>
+      <c r="P272" s="25"/>
+      <c r="Q272" s="25"/>
+      <c r="R272" s="25"/>
+      <c r="S272" s="25"/>
+      <c r="T272" s="25"/>
+      <c r="U272" s="26"/>
+    </row>
+    <row r="275" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A275" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E81" s="4"/>
-      <c r="F81" s="4"/>
-      <c r="G81" s="4"/>
-      <c r="H81" s="4"/>
-      <c r="I81" s="4"/>
-      <c r="J81" s="4"/>
-      <c r="K81" s="4"/>
-      <c r="L81" s="4"/>
-    </row>
-    <row r="82" spans="4:12" x14ac:dyDescent="0.35">
-      <c r="D82" s="4"/>
-      <c r="E82" s="4"/>
-      <c r="F82" s="4"/>
-      <c r="G82" s="4"/>
-      <c r="H82" s="4"/>
-      <c r="I82" s="4"/>
-      <c r="J82" s="4"/>
-      <c r="K82" s="4"/>
-      <c r="L82" s="4"/>
-    </row>
-    <row r="83" spans="4:12" x14ac:dyDescent="0.35">
-      <c r="D83" s="4"/>
-      <c r="E83" s="4"/>
-      <c r="F83" s="4"/>
-      <c r="G83" s="4"/>
-      <c r="H83" s="4"/>
-      <c r="I83" s="4"/>
-      <c r="J83" s="4"/>
-      <c r="K83" s="4"/>
-      <c r="L83" s="4"/>
-    </row>
-    <row r="84" spans="4:12" x14ac:dyDescent="0.35">
-      <c r="D84" s="4"/>
-      <c r="E84" s="4"/>
-      <c r="F84" s="4"/>
-      <c r="G84" s="4"/>
-      <c r="H84" s="4"/>
-      <c r="I84" s="4"/>
-      <c r="J84" s="4"/>
-      <c r="K84" s="4"/>
-      <c r="L84" s="4"/>
-    </row>
-    <row r="85" spans="4:12" x14ac:dyDescent="0.35">
-      <c r="D85" s="4"/>
-      <c r="E85" s="4"/>
-      <c r="F85" s="4"/>
-      <c r="G85" s="4"/>
-      <c r="H85" s="4"/>
-      <c r="I85" s="4"/>
-      <c r="J85" s="4"/>
-      <c r="K85" s="4"/>
-      <c r="L85" s="4"/>
-    </row>
-    <row r="86" spans="4:12" x14ac:dyDescent="0.35">
-      <c r="D86" s="4"/>
-      <c r="E86" s="4"/>
-      <c r="F86" s="4"/>
-      <c r="G86" s="4"/>
-      <c r="H86" s="4"/>
-      <c r="I86" s="4"/>
-      <c r="J86" s="4"/>
-      <c r="K86" s="4"/>
-      <c r="L86" s="4"/>
-    </row>
-    <row r="87" spans="4:12" x14ac:dyDescent="0.35">
-      <c r="D87" s="4"/>
-      <c r="E87" s="4"/>
-      <c r="F87" s="4"/>
-      <c r="G87" s="4"/>
-      <c r="H87" s="4"/>
-      <c r="I87" s="4"/>
-      <c r="J87" s="4"/>
-      <c r="K87" s="4"/>
-      <c r="L87" s="4"/>
-    </row>
-    <row r="88" spans="4:12" x14ac:dyDescent="0.35">
-      <c r="D88" s="4"/>
-      <c r="E88" s="4"/>
-      <c r="F88" s="4"/>
-      <c r="G88" s="4"/>
-      <c r="H88" s="4"/>
-      <c r="I88" s="4"/>
-      <c r="J88" s="4"/>
-      <c r="K88" s="4"/>
-      <c r="L88" s="4"/>
-    </row>
-    <row r="89" spans="4:12" x14ac:dyDescent="0.35">
-      <c r="D89" s="4"/>
-      <c r="E89" s="4"/>
-      <c r="F89" s="4"/>
-      <c r="G89" s="4"/>
-      <c r="H89" s="4"/>
-      <c r="I89" s="4"/>
-      <c r="J89" s="4"/>
-      <c r="K89" s="4"/>
-      <c r="L89" s="4"/>
-    </row>
-    <row r="90" spans="4:12" x14ac:dyDescent="0.35">
-      <c r="D90" s="4"/>
-      <c r="E90" s="4"/>
-      <c r="F90" s="4"/>
-      <c r="G90" s="4"/>
-      <c r="H90" s="4"/>
-      <c r="I90" s="4"/>
-      <c r="J90" s="4"/>
-      <c r="K90" s="4"/>
-      <c r="L90" s="4"/>
-    </row>
-    <row r="91" spans="4:12" x14ac:dyDescent="0.35">
-      <c r="D91" s="4"/>
-      <c r="E91" s="4"/>
-      <c r="F91" s="4"/>
-      <c r="G91" s="4"/>
-      <c r="H91" s="4"/>
-      <c r="I91" s="4"/>
-      <c r="J91" s="4"/>
-      <c r="K91" s="4"/>
-      <c r="L91" s="4"/>
+    </row>
+    <row r="276" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A276" s="18"/>
+      <c r="B276" s="19"/>
+      <c r="C276" s="19"/>
+      <c r="D276" s="19"/>
+      <c r="E276" s="19"/>
+      <c r="F276" s="19"/>
+      <c r="G276" s="19"/>
+      <c r="H276" s="19"/>
+      <c r="I276" s="19"/>
+      <c r="J276" s="19"/>
+      <c r="K276" s="19"/>
+      <c r="L276" s="19"/>
+      <c r="M276" s="20"/>
+    </row>
+    <row r="277" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A277" s="21"/>
+      <c r="B277" s="22"/>
+      <c r="C277" s="22"/>
+      <c r="D277" s="22"/>
+      <c r="E277" s="22"/>
+      <c r="F277" s="22"/>
+      <c r="G277" s="22"/>
+      <c r="H277" s="22"/>
+      <c r="I277" s="22"/>
+      <c r="J277" s="22"/>
+      <c r="K277" s="22"/>
+      <c r="L277" s="22"/>
+      <c r="M277" s="23"/>
+    </row>
+    <row r="278" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A278" s="21"/>
+      <c r="B278" s="22"/>
+      <c r="C278" s="22"/>
+      <c r="D278" s="22"/>
+      <c r="E278" s="22"/>
+      <c r="F278" s="22"/>
+      <c r="G278" s="22"/>
+      <c r="H278" s="22"/>
+      <c r="I278" s="22"/>
+      <c r="J278" s="22"/>
+      <c r="K278" s="22"/>
+      <c r="L278" s="22"/>
+      <c r="M278" s="23"/>
+    </row>
+    <row r="279" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A279" s="21"/>
+      <c r="B279" s="22"/>
+      <c r="C279" s="22"/>
+      <c r="D279" s="22"/>
+      <c r="E279" s="22"/>
+      <c r="F279" s="22"/>
+      <c r="G279" s="22"/>
+      <c r="H279" s="22"/>
+      <c r="I279" s="22"/>
+      <c r="J279" s="22"/>
+      <c r="K279" s="22"/>
+      <c r="L279" s="22"/>
+      <c r="M279" s="23"/>
+    </row>
+    <row r="280" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A280" s="21"/>
+      <c r="B280" s="22"/>
+      <c r="C280" s="22"/>
+      <c r="D280" s="22"/>
+      <c r="E280" s="22"/>
+      <c r="F280" s="22"/>
+      <c r="G280" s="22"/>
+      <c r="H280" s="22"/>
+      <c r="I280" s="22"/>
+      <c r="J280" s="22"/>
+      <c r="K280" s="22"/>
+      <c r="L280" s="22"/>
+      <c r="M280" s="23"/>
+    </row>
+    <row r="281" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A281" s="21"/>
+      <c r="B281" s="22"/>
+      <c r="C281" s="22"/>
+      <c r="D281" s="22"/>
+      <c r="E281" s="22"/>
+      <c r="F281" s="22"/>
+      <c r="G281" s="22"/>
+      <c r="H281" s="22"/>
+      <c r="I281" s="22"/>
+      <c r="J281" s="22"/>
+      <c r="K281" s="22"/>
+      <c r="L281" s="22"/>
+      <c r="M281" s="23"/>
+    </row>
+    <row r="282" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A282" s="21"/>
+      <c r="B282" s="22"/>
+      <c r="C282" s="22"/>
+      <c r="D282" s="22"/>
+      <c r="E282" s="22"/>
+      <c r="F282" s="22"/>
+      <c r="G282" s="22"/>
+      <c r="H282" s="22"/>
+      <c r="I282" s="22"/>
+      <c r="J282" s="22"/>
+      <c r="K282" s="22"/>
+      <c r="L282" s="22"/>
+      <c r="M282" s="23"/>
+    </row>
+    <row r="283" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A283" s="21"/>
+      <c r="B283" s="22"/>
+      <c r="C283" s="22"/>
+      <c r="D283" s="22"/>
+      <c r="E283" s="22"/>
+      <c r="F283" s="22"/>
+      <c r="G283" s="22"/>
+      <c r="H283" s="22"/>
+      <c r="I283" s="22"/>
+      <c r="J283" s="22"/>
+      <c r="K283" s="22"/>
+      <c r="L283" s="22"/>
+      <c r="M283" s="23"/>
+    </row>
+    <row r="284" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A284" s="21"/>
+      <c r="B284" s="22"/>
+      <c r="C284" s="22"/>
+      <c r="D284" s="22"/>
+      <c r="E284" s="22"/>
+      <c r="F284" s="22"/>
+      <c r="G284" s="22"/>
+      <c r="H284" s="22"/>
+      <c r="I284" s="22"/>
+      <c r="J284" s="22"/>
+      <c r="K284" s="22"/>
+      <c r="L284" s="22"/>
+      <c r="M284" s="23"/>
+    </row>
+    <row r="285" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A285" s="21"/>
+      <c r="B285" s="22"/>
+      <c r="C285" s="22"/>
+      <c r="D285" s="22"/>
+      <c r="E285" s="22"/>
+      <c r="F285" s="22"/>
+      <c r="G285" s="22"/>
+      <c r="H285" s="22"/>
+      <c r="I285" s="22"/>
+      <c r="J285" s="22"/>
+      <c r="K285" s="22"/>
+      <c r="L285" s="22"/>
+      <c r="M285" s="23"/>
+    </row>
+    <row r="286" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A286" s="21"/>
+      <c r="B286" s="22"/>
+      <c r="C286" s="22"/>
+      <c r="D286" s="22"/>
+      <c r="E286" s="22"/>
+      <c r="F286" s="22"/>
+      <c r="G286" s="22"/>
+      <c r="H286" s="22"/>
+      <c r="I286" s="22"/>
+      <c r="J286" s="22"/>
+      <c r="K286" s="22"/>
+      <c r="L286" s="22"/>
+      <c r="M286" s="23"/>
+    </row>
+    <row r="287" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A287" s="21"/>
+      <c r="B287" s="22"/>
+      <c r="C287" s="22"/>
+      <c r="D287" s="22"/>
+      <c r="E287" s="22"/>
+      <c r="F287" s="22"/>
+      <c r="G287" s="22"/>
+      <c r="H287" s="22"/>
+      <c r="I287" s="22"/>
+      <c r="J287" s="22"/>
+      <c r="K287" s="22"/>
+      <c r="L287" s="22"/>
+      <c r="M287" s="23"/>
+    </row>
+    <row r="288" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A288" s="21"/>
+      <c r="B288" s="22"/>
+      <c r="C288" s="22"/>
+      <c r="D288" s="22"/>
+      <c r="E288" s="22"/>
+      <c r="F288" s="22"/>
+      <c r="G288" s="22"/>
+      <c r="H288" s="22"/>
+      <c r="I288" s="22"/>
+      <c r="J288" s="22"/>
+      <c r="K288" s="22"/>
+      <c r="L288" s="22"/>
+      <c r="M288" s="23"/>
+    </row>
+    <row r="289" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="A289" s="21"/>
+      <c r="B289" s="22"/>
+      <c r="C289" s="22"/>
+      <c r="D289" s="22"/>
+      <c r="E289" s="22"/>
+      <c r="F289" s="22"/>
+      <c r="G289" s="22"/>
+      <c r="H289" s="22"/>
+      <c r="I289" s="22"/>
+      <c r="J289" s="22"/>
+      <c r="K289" s="22"/>
+      <c r="L289" s="22"/>
+      <c r="M289" s="23"/>
+    </row>
+    <row r="290" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="A290" s="21"/>
+      <c r="B290" s="22"/>
+      <c r="C290" s="22"/>
+      <c r="D290" s="22"/>
+      <c r="E290" s="22"/>
+      <c r="F290" s="22"/>
+      <c r="G290" s="22"/>
+      <c r="H290" s="22"/>
+      <c r="I290" s="22"/>
+      <c r="J290" s="22"/>
+      <c r="K290" s="22"/>
+      <c r="L290" s="22"/>
+      <c r="M290" s="23"/>
+    </row>
+    <row r="291" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="A291" s="21"/>
+      <c r="B291" s="22"/>
+      <c r="C291" s="22"/>
+      <c r="D291" s="22"/>
+      <c r="E291" s="22"/>
+      <c r="F291" s="22"/>
+      <c r="G291" s="22"/>
+      <c r="H291" s="22"/>
+      <c r="I291" s="22"/>
+      <c r="J291" s="22"/>
+      <c r="K291" s="22"/>
+      <c r="L291" s="22"/>
+      <c r="M291" s="23"/>
+    </row>
+    <row r="292" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="A292" s="24"/>
+      <c r="B292" s="25"/>
+      <c r="C292" s="25"/>
+      <c r="D292" s="25"/>
+      <c r="E292" s="25"/>
+      <c r="F292" s="25"/>
+      <c r="G292" s="25"/>
+      <c r="H292" s="25"/>
+      <c r="I292" s="25"/>
+      <c r="J292" s="25"/>
+      <c r="K292" s="25"/>
+      <c r="L292" s="25"/>
+      <c r="M292" s="26"/>
+    </row>
+    <row r="295" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="A295" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B295" s="10"/>
+      <c r="C295" s="10"/>
+      <c r="D295" s="10"/>
+      <c r="E295" s="10"/>
+      <c r="F295" s="10"/>
+      <c r="G295" s="10"/>
+      <c r="H295" s="10"/>
+      <c r="I295" s="10"/>
+      <c r="J295" s="10"/>
+      <c r="K295" s="10"/>
+      <c r="L295" s="10"/>
+      <c r="M295" s="10"/>
+      <c r="N295" s="10"/>
+      <c r="O295" s="11"/>
+      <c r="Q295" s="3"/>
+      <c r="R295" s="3"/>
+      <c r="S295" s="3"/>
+      <c r="T295" s="3"/>
+      <c r="U295" s="3"/>
+      <c r="V295" s="3"/>
+      <c r="W295" s="3"/>
+      <c r="X295" s="3"/>
+      <c r="Y295" s="3"/>
+      <c r="Z295" s="3"/>
+      <c r="AA295" s="3"/>
+      <c r="AB295" s="3"/>
+      <c r="AC295" s="3"/>
+      <c r="AD295" s="3"/>
+      <c r="AE295" s="3"/>
+    </row>
+    <row r="296" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="A296" s="12"/>
+      <c r="B296" s="13"/>
+      <c r="C296" s="13"/>
+      <c r="D296" s="13"/>
+      <c r="E296" s="13"/>
+      <c r="F296" s="13"/>
+      <c r="G296" s="13"/>
+      <c r="H296" s="13"/>
+      <c r="I296" s="13"/>
+      <c r="J296" s="13"/>
+      <c r="K296" s="13"/>
+      <c r="L296" s="13"/>
+      <c r="M296" s="13"/>
+      <c r="N296" s="13"/>
+      <c r="O296" s="14"/>
+      <c r="Q296" s="3"/>
+      <c r="R296" s="3"/>
+      <c r="S296" s="3"/>
+      <c r="T296" s="3"/>
+      <c r="U296" s="3"/>
+      <c r="V296" s="3"/>
+      <c r="W296" s="3"/>
+      <c r="X296" s="3"/>
+      <c r="Y296" s="3"/>
+      <c r="Z296" s="3"/>
+      <c r="AA296" s="3"/>
+      <c r="AB296" s="3"/>
+      <c r="AC296" s="3"/>
+      <c r="AD296" s="3"/>
+      <c r="AE296" s="3"/>
+    </row>
+    <row r="297" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="A297" s="12"/>
+      <c r="B297" s="13"/>
+      <c r="C297" s="13"/>
+      <c r="D297" s="13"/>
+      <c r="E297" s="13"/>
+      <c r="F297" s="13"/>
+      <c r="G297" s="13"/>
+      <c r="H297" s="13"/>
+      <c r="I297" s="13"/>
+      <c r="J297" s="13"/>
+      <c r="K297" s="13"/>
+      <c r="L297" s="13"/>
+      <c r="M297" s="13"/>
+      <c r="N297" s="13"/>
+      <c r="O297" s="14"/>
+      <c r="Q297" s="3"/>
+      <c r="R297" s="3"/>
+      <c r="S297" s="3"/>
+      <c r="T297" s="3"/>
+      <c r="U297" s="3"/>
+      <c r="V297" s="3"/>
+      <c r="W297" s="3"/>
+      <c r="X297" s="3"/>
+      <c r="Y297" s="3"/>
+      <c r="Z297" s="3"/>
+      <c r="AA297" s="3"/>
+      <c r="AB297" s="3"/>
+      <c r="AC297" s="3"/>
+      <c r="AD297" s="3"/>
+      <c r="AE297" s="3"/>
+    </row>
+    <row r="298" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="A298" s="12"/>
+      <c r="B298" s="13"/>
+      <c r="C298" s="13"/>
+      <c r="D298" s="13"/>
+      <c r="E298" s="13"/>
+      <c r="F298" s="13"/>
+      <c r="G298" s="13"/>
+      <c r="H298" s="13"/>
+      <c r="I298" s="13"/>
+      <c r="J298" s="13"/>
+      <c r="K298" s="13"/>
+      <c r="L298" s="13"/>
+      <c r="M298" s="13"/>
+      <c r="N298" s="13"/>
+      <c r="O298" s="14"/>
+      <c r="Q298" s="3"/>
+      <c r="R298" s="3"/>
+      <c r="S298" s="3"/>
+      <c r="T298" s="3"/>
+      <c r="U298" s="3"/>
+      <c r="V298" s="3"/>
+      <c r="W298" s="3"/>
+      <c r="X298" s="3"/>
+      <c r="Y298" s="3"/>
+      <c r="Z298" s="3"/>
+      <c r="AA298" s="3"/>
+      <c r="AB298" s="3"/>
+      <c r="AC298" s="3"/>
+      <c r="AD298" s="3"/>
+      <c r="AE298" s="3"/>
+    </row>
+    <row r="299" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="A299" s="12"/>
+      <c r="B299" s="13"/>
+      <c r="C299" s="13"/>
+      <c r="D299" s="13"/>
+      <c r="E299" s="13"/>
+      <c r="F299" s="13"/>
+      <c r="G299" s="13"/>
+      <c r="H299" s="13"/>
+      <c r="I299" s="13"/>
+      <c r="J299" s="13"/>
+      <c r="K299" s="13"/>
+      <c r="L299" s="13"/>
+      <c r="M299" s="13"/>
+      <c r="N299" s="13"/>
+      <c r="O299" s="14"/>
+      <c r="Q299" s="3"/>
+      <c r="R299" s="3"/>
+      <c r="S299" s="3"/>
+      <c r="T299" s="3"/>
+      <c r="U299" s="3"/>
+      <c r="V299" s="3"/>
+      <c r="W299" s="3"/>
+      <c r="X299" s="3"/>
+      <c r="Y299" s="3"/>
+      <c r="Z299" s="3"/>
+      <c r="AA299" s="3"/>
+      <c r="AB299" s="3"/>
+      <c r="AC299" s="3"/>
+      <c r="AD299" s="3"/>
+      <c r="AE299" s="3"/>
+    </row>
+    <row r="300" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="A300" s="12"/>
+      <c r="B300" s="13"/>
+      <c r="C300" s="13"/>
+      <c r="D300" s="13"/>
+      <c r="E300" s="13"/>
+      <c r="F300" s="13"/>
+      <c r="G300" s="13"/>
+      <c r="H300" s="13"/>
+      <c r="I300" s="13"/>
+      <c r="J300" s="13"/>
+      <c r="K300" s="13"/>
+      <c r="L300" s="13"/>
+      <c r="M300" s="13"/>
+      <c r="N300" s="13"/>
+      <c r="O300" s="14"/>
+      <c r="Q300" s="3"/>
+      <c r="R300" s="3"/>
+      <c r="S300" s="3"/>
+      <c r="T300" s="3"/>
+      <c r="U300" s="3"/>
+      <c r="V300" s="3"/>
+      <c r="W300" s="3"/>
+      <c r="X300" s="3"/>
+      <c r="Y300" s="3"/>
+      <c r="Z300" s="3"/>
+      <c r="AA300" s="3"/>
+      <c r="AB300" s="3"/>
+      <c r="AC300" s="3"/>
+      <c r="AD300" s="3"/>
+      <c r="AE300" s="3"/>
+    </row>
+    <row r="301" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="A301" s="12"/>
+      <c r="B301" s="13"/>
+      <c r="C301" s="13"/>
+      <c r="D301" s="13"/>
+      <c r="E301" s="13"/>
+      <c r="F301" s="13"/>
+      <c r="G301" s="13"/>
+      <c r="H301" s="13"/>
+      <c r="I301" s="13"/>
+      <c r="J301" s="13"/>
+      <c r="K301" s="13"/>
+      <c r="L301" s="13"/>
+      <c r="M301" s="13"/>
+      <c r="N301" s="13"/>
+      <c r="O301" s="14"/>
+      <c r="Q301" s="3"/>
+      <c r="R301" s="3"/>
+      <c r="S301" s="3"/>
+      <c r="T301" s="3"/>
+      <c r="U301" s="3"/>
+      <c r="V301" s="3"/>
+      <c r="W301" s="3"/>
+      <c r="X301" s="3"/>
+      <c r="Y301" s="3"/>
+      <c r="Z301" s="3"/>
+      <c r="AA301" s="3"/>
+      <c r="AB301" s="3"/>
+      <c r="AC301" s="3"/>
+      <c r="AD301" s="3"/>
+      <c r="AE301" s="3"/>
+    </row>
+    <row r="302" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="A302" s="12"/>
+      <c r="B302" s="13"/>
+      <c r="C302" s="13"/>
+      <c r="D302" s="13"/>
+      <c r="E302" s="13"/>
+      <c r="F302" s="13"/>
+      <c r="G302" s="13"/>
+      <c r="H302" s="13"/>
+      <c r="I302" s="13"/>
+      <c r="J302" s="13"/>
+      <c r="K302" s="13"/>
+      <c r="L302" s="13"/>
+      <c r="M302" s="13"/>
+      <c r="N302" s="13"/>
+      <c r="O302" s="14"/>
+      <c r="Q302" s="3"/>
+      <c r="R302" s="3"/>
+      <c r="S302" s="3"/>
+      <c r="T302" s="3"/>
+      <c r="U302" s="3"/>
+      <c r="V302" s="3"/>
+      <c r="W302" s="3"/>
+      <c r="X302" s="3"/>
+      <c r="Y302" s="3"/>
+      <c r="Z302" s="3"/>
+      <c r="AA302" s="3"/>
+      <c r="AB302" s="3"/>
+      <c r="AC302" s="3"/>
+      <c r="AD302" s="3"/>
+      <c r="AE302" s="3"/>
+    </row>
+    <row r="303" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="A303" s="12"/>
+      <c r="B303" s="13"/>
+      <c r="C303" s="13"/>
+      <c r="D303" s="13"/>
+      <c r="E303" s="13"/>
+      <c r="F303" s="13"/>
+      <c r="G303" s="13"/>
+      <c r="H303" s="13"/>
+      <c r="I303" s="13"/>
+      <c r="J303" s="13"/>
+      <c r="K303" s="13"/>
+      <c r="L303" s="13"/>
+      <c r="M303" s="13"/>
+      <c r="N303" s="13"/>
+      <c r="O303" s="14"/>
+      <c r="Q303" s="3"/>
+      <c r="R303" s="3"/>
+      <c r="S303" s="3"/>
+      <c r="T303" s="3"/>
+      <c r="U303" s="3"/>
+      <c r="V303" s="3"/>
+      <c r="W303" s="3"/>
+      <c r="X303" s="3"/>
+      <c r="Y303" s="3"/>
+      <c r="Z303" s="3"/>
+      <c r="AA303" s="3"/>
+      <c r="AB303" s="3"/>
+      <c r="AC303" s="3"/>
+      <c r="AD303" s="3"/>
+      <c r="AE303" s="3"/>
+    </row>
+    <row r="304" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="A304" s="12"/>
+      <c r="B304" s="13"/>
+      <c r="C304" s="13"/>
+      <c r="D304" s="13"/>
+      <c r="E304" s="13"/>
+      <c r="F304" s="13"/>
+      <c r="G304" s="13"/>
+      <c r="H304" s="13"/>
+      <c r="I304" s="13"/>
+      <c r="J304" s="13"/>
+      <c r="K304" s="13"/>
+      <c r="L304" s="13"/>
+      <c r="M304" s="13"/>
+      <c r="N304" s="13"/>
+      <c r="O304" s="14"/>
+      <c r="Q304" s="3"/>
+      <c r="R304" s="3"/>
+      <c r="S304" s="3"/>
+      <c r="T304" s="3"/>
+      <c r="U304" s="3"/>
+      <c r="V304" s="3"/>
+      <c r="W304" s="3"/>
+      <c r="X304" s="3"/>
+      <c r="Y304" s="3"/>
+      <c r="Z304" s="3"/>
+      <c r="AA304" s="3"/>
+      <c r="AB304" s="3"/>
+      <c r="AC304" s="3"/>
+      <c r="AD304" s="3"/>
+      <c r="AE304" s="3"/>
+    </row>
+    <row r="305" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="A305" s="12"/>
+      <c r="B305" s="13"/>
+      <c r="C305" s="13"/>
+      <c r="D305" s="13"/>
+      <c r="E305" s="13"/>
+      <c r="F305" s="13"/>
+      <c r="G305" s="13"/>
+      <c r="H305" s="13"/>
+      <c r="I305" s="13"/>
+      <c r="J305" s="13"/>
+      <c r="K305" s="13"/>
+      <c r="L305" s="13"/>
+      <c r="M305" s="13"/>
+      <c r="N305" s="13"/>
+      <c r="O305" s="14"/>
+      <c r="Q305" s="3"/>
+      <c r="R305" s="3"/>
+      <c r="S305" s="3"/>
+      <c r="T305" s="3"/>
+      <c r="U305" s="3"/>
+      <c r="V305" s="3"/>
+      <c r="W305" s="3"/>
+      <c r="X305" s="3"/>
+      <c r="Y305" s="3"/>
+      <c r="Z305" s="3"/>
+      <c r="AA305" s="3"/>
+      <c r="AB305" s="3"/>
+      <c r="AC305" s="3"/>
+      <c r="AD305" s="3"/>
+      <c r="AE305" s="3"/>
+    </row>
+    <row r="306" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="A306" s="12"/>
+      <c r="B306" s="13"/>
+      <c r="C306" s="13"/>
+      <c r="D306" s="13"/>
+      <c r="E306" s="13"/>
+      <c r="F306" s="13"/>
+      <c r="G306" s="13"/>
+      <c r="H306" s="13"/>
+      <c r="I306" s="13"/>
+      <c r="J306" s="13"/>
+      <c r="K306" s="13"/>
+      <c r="L306" s="13"/>
+      <c r="M306" s="13"/>
+      <c r="N306" s="13"/>
+      <c r="O306" s="14"/>
+      <c r="Q306" s="3"/>
+      <c r="R306" s="3"/>
+      <c r="S306" s="3"/>
+      <c r="T306" s="3"/>
+      <c r="U306" s="3"/>
+      <c r="V306" s="3"/>
+      <c r="W306" s="3"/>
+      <c r="X306" s="3"/>
+      <c r="Y306" s="3"/>
+      <c r="Z306" s="3"/>
+      <c r="AA306" s="3"/>
+      <c r="AB306" s="3"/>
+      <c r="AC306" s="3"/>
+      <c r="AD306" s="3"/>
+      <c r="AE306" s="3"/>
+    </row>
+    <row r="307" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="A307" s="12"/>
+      <c r="B307" s="13"/>
+      <c r="C307" s="13"/>
+      <c r="D307" s="13"/>
+      <c r="E307" s="13"/>
+      <c r="F307" s="13"/>
+      <c r="G307" s="13"/>
+      <c r="H307" s="13"/>
+      <c r="I307" s="13"/>
+      <c r="J307" s="13"/>
+      <c r="K307" s="13"/>
+      <c r="L307" s="13"/>
+      <c r="M307" s="13"/>
+      <c r="N307" s="13"/>
+      <c r="O307" s="14"/>
+      <c r="Q307" s="3"/>
+      <c r="R307" s="3"/>
+      <c r="S307" s="3"/>
+      <c r="T307" s="3"/>
+      <c r="U307" s="3"/>
+      <c r="V307" s="3"/>
+      <c r="W307" s="3"/>
+      <c r="X307" s="3"/>
+      <c r="Y307" s="3"/>
+      <c r="Z307" s="3"/>
+      <c r="AA307" s="3"/>
+      <c r="AB307" s="3"/>
+      <c r="AC307" s="3"/>
+      <c r="AD307" s="3"/>
+      <c r="AE307" s="3"/>
+    </row>
+    <row r="308" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="A308" s="12"/>
+      <c r="B308" s="13"/>
+      <c r="C308" s="13"/>
+      <c r="D308" s="13"/>
+      <c r="E308" s="13"/>
+      <c r="F308" s="13"/>
+      <c r="G308" s="13"/>
+      <c r="H308" s="13"/>
+      <c r="I308" s="13"/>
+      <c r="J308" s="13"/>
+      <c r="K308" s="13"/>
+      <c r="L308" s="13"/>
+      <c r="M308" s="13"/>
+      <c r="N308" s="13"/>
+      <c r="O308" s="14"/>
+      <c r="Q308" s="3"/>
+      <c r="R308" s="3"/>
+      <c r="S308" s="3"/>
+      <c r="T308" s="3"/>
+      <c r="U308" s="3"/>
+      <c r="V308" s="3"/>
+      <c r="W308" s="3"/>
+      <c r="X308" s="3"/>
+      <c r="Y308" s="3"/>
+      <c r="Z308" s="3"/>
+      <c r="AA308" s="3"/>
+      <c r="AB308" s="3"/>
+      <c r="AC308" s="3"/>
+      <c r="AD308" s="3"/>
+      <c r="AE308" s="3"/>
+    </row>
+    <row r="309" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="A309" s="15"/>
+      <c r="B309" s="16"/>
+      <c r="C309" s="16"/>
+      <c r="D309" s="16"/>
+      <c r="E309" s="16"/>
+      <c r="F309" s="16"/>
+      <c r="G309" s="16"/>
+      <c r="H309" s="16"/>
+      <c r="I309" s="16"/>
+      <c r="J309" s="16"/>
+      <c r="K309" s="16"/>
+      <c r="L309" s="16"/>
+      <c r="M309" s="16"/>
+      <c r="N309" s="16"/>
+      <c r="O309" s="17"/>
+      <c r="Q309" s="3"/>
+      <c r="R309" s="3"/>
+      <c r="S309" s="3"/>
+      <c r="T309" s="3"/>
+      <c r="U309" s="3"/>
+      <c r="V309" s="3"/>
+      <c r="W309" s="3"/>
+      <c r="X309" s="3"/>
+      <c r="Y309" s="3"/>
+      <c r="Z309" s="3"/>
+      <c r="AA309" s="3"/>
+      <c r="AB309" s="3"/>
+      <c r="AC309" s="3"/>
+      <c r="AD309" s="3"/>
+      <c r="AE309" s="3"/>
+    </row>
+    <row r="310" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="A310" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B310" s="10"/>
+      <c r="C310" s="10"/>
+      <c r="D310" s="10"/>
+      <c r="E310" s="10"/>
+      <c r="F310" s="10"/>
+      <c r="G310" s="10"/>
+      <c r="H310" s="10"/>
+      <c r="I310" s="10"/>
+      <c r="J310" s="10"/>
+      <c r="K310" s="10"/>
+      <c r="L310" s="10"/>
+      <c r="M310" s="10"/>
+      <c r="N310" s="10"/>
+      <c r="O310" s="11"/>
+    </row>
+    <row r="311" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="A311" s="12"/>
+      <c r="B311" s="13"/>
+      <c r="C311" s="13"/>
+      <c r="D311" s="13"/>
+      <c r="E311" s="13"/>
+      <c r="F311" s="13"/>
+      <c r="G311" s="13"/>
+      <c r="H311" s="13"/>
+      <c r="I311" s="13"/>
+      <c r="J311" s="13"/>
+      <c r="K311" s="13"/>
+      <c r="L311" s="13"/>
+      <c r="M311" s="13"/>
+      <c r="N311" s="13"/>
+      <c r="O311" s="14"/>
+    </row>
+    <row r="312" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="A312" s="12"/>
+      <c r="B312" s="13"/>
+      <c r="C312" s="13"/>
+      <c r="D312" s="13"/>
+      <c r="E312" s="13"/>
+      <c r="F312" s="13"/>
+      <c r="G312" s="13"/>
+      <c r="H312" s="13"/>
+      <c r="I312" s="13"/>
+      <c r="J312" s="13"/>
+      <c r="K312" s="13"/>
+      <c r="L312" s="13"/>
+      <c r="M312" s="13"/>
+      <c r="N312" s="13"/>
+      <c r="O312" s="14"/>
+    </row>
+    <row r="313" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="A313" s="12"/>
+      <c r="B313" s="13"/>
+      <c r="C313" s="13"/>
+      <c r="D313" s="13"/>
+      <c r="E313" s="13"/>
+      <c r="F313" s="13"/>
+      <c r="G313" s="13"/>
+      <c r="H313" s="13"/>
+      <c r="I313" s="13"/>
+      <c r="J313" s="13"/>
+      <c r="K313" s="13"/>
+      <c r="L313" s="13"/>
+      <c r="M313" s="13"/>
+      <c r="N313" s="13"/>
+      <c r="O313" s="14"/>
+    </row>
+    <row r="314" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="A314" s="12"/>
+      <c r="B314" s="13"/>
+      <c r="C314" s="13"/>
+      <c r="D314" s="13"/>
+      <c r="E314" s="13"/>
+      <c r="F314" s="13"/>
+      <c r="G314" s="13"/>
+      <c r="H314" s="13"/>
+      <c r="I314" s="13"/>
+      <c r="J314" s="13"/>
+      <c r="K314" s="13"/>
+      <c r="L314" s="13"/>
+      <c r="M314" s="13"/>
+      <c r="N314" s="13"/>
+      <c r="O314" s="14"/>
+    </row>
+    <row r="315" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="A315" s="12"/>
+      <c r="B315" s="13"/>
+      <c r="C315" s="13"/>
+      <c r="D315" s="13"/>
+      <c r="E315" s="13"/>
+      <c r="F315" s="13"/>
+      <c r="G315" s="13"/>
+      <c r="H315" s="13"/>
+      <c r="I315" s="13"/>
+      <c r="J315" s="13"/>
+      <c r="K315" s="13"/>
+      <c r="L315" s="13"/>
+      <c r="M315" s="13"/>
+      <c r="N315" s="13"/>
+      <c r="O315" s="14"/>
+    </row>
+    <row r="316" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="A316" s="12"/>
+      <c r="B316" s="13"/>
+      <c r="C316" s="13"/>
+      <c r="D316" s="13"/>
+      <c r="E316" s="13"/>
+      <c r="F316" s="13"/>
+      <c r="G316" s="13"/>
+      <c r="H316" s="13"/>
+      <c r="I316" s="13"/>
+      <c r="J316" s="13"/>
+      <c r="K316" s="13"/>
+      <c r="L316" s="13"/>
+      <c r="M316" s="13"/>
+      <c r="N316" s="13"/>
+      <c r="O316" s="14"/>
+    </row>
+    <row r="317" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="A317" s="12"/>
+      <c r="B317" s="13"/>
+      <c r="C317" s="13"/>
+      <c r="D317" s="13"/>
+      <c r="E317" s="13"/>
+      <c r="F317" s="13"/>
+      <c r="G317" s="13"/>
+      <c r="H317" s="13"/>
+      <c r="I317" s="13"/>
+      <c r="J317" s="13"/>
+      <c r="K317" s="13"/>
+      <c r="L317" s="13"/>
+      <c r="M317" s="13"/>
+      <c r="N317" s="13"/>
+      <c r="O317" s="14"/>
+    </row>
+    <row r="318" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="A318" s="12"/>
+      <c r="B318" s="13"/>
+      <c r="C318" s="13"/>
+      <c r="D318" s="13"/>
+      <c r="E318" s="13"/>
+      <c r="F318" s="13"/>
+      <c r="G318" s="13"/>
+      <c r="H318" s="13"/>
+      <c r="I318" s="13"/>
+      <c r="J318" s="13"/>
+      <c r="K318" s="13"/>
+      <c r="L318" s="13"/>
+      <c r="M318" s="13"/>
+      <c r="N318" s="13"/>
+      <c r="O318" s="14"/>
+    </row>
+    <row r="319" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="A319" s="12"/>
+      <c r="B319" s="13"/>
+      <c r="C319" s="13"/>
+      <c r="D319" s="13"/>
+      <c r="E319" s="13"/>
+      <c r="F319" s="13"/>
+      <c r="G319" s="13"/>
+      <c r="H319" s="13"/>
+      <c r="I319" s="13"/>
+      <c r="J319" s="13"/>
+      <c r="K319" s="13"/>
+      <c r="L319" s="13"/>
+      <c r="M319" s="13"/>
+      <c r="N319" s="13"/>
+      <c r="O319" s="14"/>
+    </row>
+    <row r="320" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="A320" s="12"/>
+      <c r="B320" s="13"/>
+      <c r="C320" s="13"/>
+      <c r="D320" s="13"/>
+      <c r="E320" s="13"/>
+      <c r="F320" s="13"/>
+      <c r="G320" s="13"/>
+      <c r="H320" s="13"/>
+      <c r="I320" s="13"/>
+      <c r="J320" s="13"/>
+      <c r="K320" s="13"/>
+      <c r="L320" s="13"/>
+      <c r="M320" s="13"/>
+      <c r="N320" s="13"/>
+      <c r="O320" s="14"/>
+    </row>
+    <row r="321" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A321" s="12"/>
+      <c r="B321" s="13"/>
+      <c r="C321" s="13"/>
+      <c r="D321" s="13"/>
+      <c r="E321" s="13"/>
+      <c r="F321" s="13"/>
+      <c r="G321" s="13"/>
+      <c r="H321" s="13"/>
+      <c r="I321" s="13"/>
+      <c r="J321" s="13"/>
+      <c r="K321" s="13"/>
+      <c r="L321" s="13"/>
+      <c r="M321" s="13"/>
+      <c r="N321" s="13"/>
+      <c r="O321" s="14"/>
+    </row>
+    <row r="322" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A322" s="12"/>
+      <c r="B322" s="13"/>
+      <c r="C322" s="13"/>
+      <c r="D322" s="13"/>
+      <c r="E322" s="13"/>
+      <c r="F322" s="13"/>
+      <c r="G322" s="13"/>
+      <c r="H322" s="13"/>
+      <c r="I322" s="13"/>
+      <c r="J322" s="13"/>
+      <c r="K322" s="13"/>
+      <c r="L322" s="13"/>
+      <c r="M322" s="13"/>
+      <c r="N322" s="13"/>
+      <c r="O322" s="14"/>
+    </row>
+    <row r="323" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A323" s="12"/>
+      <c r="B323" s="13"/>
+      <c r="C323" s="13"/>
+      <c r="D323" s="13"/>
+      <c r="E323" s="13"/>
+      <c r="F323" s="13"/>
+      <c r="G323" s="13"/>
+      <c r="H323" s="13"/>
+      <c r="I323" s="13"/>
+      <c r="J323" s="13"/>
+      <c r="K323" s="13"/>
+      <c r="L323" s="13"/>
+      <c r="M323" s="13"/>
+      <c r="N323" s="13"/>
+      <c r="O323" s="14"/>
+    </row>
+    <row r="324" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A324" s="15"/>
+      <c r="B324" s="16"/>
+      <c r="C324" s="16"/>
+      <c r="D324" s="16"/>
+      <c r="E324" s="16"/>
+      <c r="F324" s="16"/>
+      <c r="G324" s="16"/>
+      <c r="H324" s="16"/>
+      <c r="I324" s="16"/>
+      <c r="J324" s="16"/>
+      <c r="K324" s="16"/>
+      <c r="L324" s="16"/>
+      <c r="M324" s="16"/>
+      <c r="N324" s="16"/>
+      <c r="O324" s="17"/>
+    </row>
+    <row r="325" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A325" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B325" s="10"/>
+      <c r="C325" s="10"/>
+      <c r="D325" s="10"/>
+      <c r="E325" s="10"/>
+      <c r="F325" s="10"/>
+      <c r="G325" s="10"/>
+      <c r="H325" s="10"/>
+      <c r="I325" s="10"/>
+      <c r="J325" s="10"/>
+      <c r="K325" s="10"/>
+      <c r="L325" s="10"/>
+      <c r="M325" s="10"/>
+      <c r="N325" s="10"/>
+      <c r="O325" s="11"/>
+    </row>
+    <row r="326" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A326" s="12"/>
+      <c r="B326" s="13"/>
+      <c r="C326" s="13"/>
+      <c r="D326" s="13"/>
+      <c r="E326" s="13"/>
+      <c r="F326" s="13"/>
+      <c r="G326" s="13"/>
+      <c r="H326" s="13"/>
+      <c r="I326" s="13"/>
+      <c r="J326" s="13"/>
+      <c r="K326" s="13"/>
+      <c r="L326" s="13"/>
+      <c r="M326" s="13"/>
+      <c r="N326" s="13"/>
+      <c r="O326" s="14"/>
+    </row>
+    <row r="327" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A327" s="12"/>
+      <c r="B327" s="13"/>
+      <c r="C327" s="13"/>
+      <c r="D327" s="13"/>
+      <c r="E327" s="13"/>
+      <c r="F327" s="13"/>
+      <c r="G327" s="13"/>
+      <c r="H327" s="13"/>
+      <c r="I327" s="13"/>
+      <c r="J327" s="13"/>
+      <c r="K327" s="13"/>
+      <c r="L327" s="13"/>
+      <c r="M327" s="13"/>
+      <c r="N327" s="13"/>
+      <c r="O327" s="14"/>
+    </row>
+    <row r="328" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A328" s="12"/>
+      <c r="B328" s="13"/>
+      <c r="C328" s="13"/>
+      <c r="D328" s="13"/>
+      <c r="E328" s="13"/>
+      <c r="F328" s="13"/>
+      <c r="G328" s="13"/>
+      <c r="H328" s="13"/>
+      <c r="I328" s="13"/>
+      <c r="J328" s="13"/>
+      <c r="K328" s="13"/>
+      <c r="L328" s="13"/>
+      <c r="M328" s="13"/>
+      <c r="N328" s="13"/>
+      <c r="O328" s="14"/>
+    </row>
+    <row r="329" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A329" s="12"/>
+      <c r="B329" s="13"/>
+      <c r="C329" s="13"/>
+      <c r="D329" s="13"/>
+      <c r="E329" s="13"/>
+      <c r="F329" s="13"/>
+      <c r="G329" s="13"/>
+      <c r="H329" s="13"/>
+      <c r="I329" s="13"/>
+      <c r="J329" s="13"/>
+      <c r="K329" s="13"/>
+      <c r="L329" s="13"/>
+      <c r="M329" s="13"/>
+      <c r="N329" s="13"/>
+      <c r="O329" s="14"/>
+    </row>
+    <row r="330" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A330" s="12"/>
+      <c r="B330" s="13"/>
+      <c r="C330" s="13"/>
+      <c r="D330" s="13"/>
+      <c r="E330" s="13"/>
+      <c r="F330" s="13"/>
+      <c r="G330" s="13"/>
+      <c r="H330" s="13"/>
+      <c r="I330" s="13"/>
+      <c r="J330" s="13"/>
+      <c r="K330" s="13"/>
+      <c r="L330" s="13"/>
+      <c r="M330" s="13"/>
+      <c r="N330" s="13"/>
+      <c r="O330" s="14"/>
+    </row>
+    <row r="331" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A331" s="12"/>
+      <c r="B331" s="13"/>
+      <c r="C331" s="13"/>
+      <c r="D331" s="13"/>
+      <c r="E331" s="13"/>
+      <c r="F331" s="13"/>
+      <c r="G331" s="13"/>
+      <c r="H331" s="13"/>
+      <c r="I331" s="13"/>
+      <c r="J331" s="13"/>
+      <c r="K331" s="13"/>
+      <c r="L331" s="13"/>
+      <c r="M331" s="13"/>
+      <c r="N331" s="13"/>
+      <c r="O331" s="14"/>
+    </row>
+    <row r="332" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A332" s="12"/>
+      <c r="B332" s="13"/>
+      <c r="C332" s="13"/>
+      <c r="D332" s="13"/>
+      <c r="E332" s="13"/>
+      <c r="F332" s="13"/>
+      <c r="G332" s="13"/>
+      <c r="H332" s="13"/>
+      <c r="I332" s="13"/>
+      <c r="J332" s="13"/>
+      <c r="K332" s="13"/>
+      <c r="L332" s="13"/>
+      <c r="M332" s="13"/>
+      <c r="N332" s="13"/>
+      <c r="O332" s="14"/>
+    </row>
+    <row r="333" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A333" s="12"/>
+      <c r="B333" s="13"/>
+      <c r="C333" s="13"/>
+      <c r="D333" s="13"/>
+      <c r="E333" s="13"/>
+      <c r="F333" s="13"/>
+      <c r="G333" s="13"/>
+      <c r="H333" s="13"/>
+      <c r="I333" s="13"/>
+      <c r="J333" s="13"/>
+      <c r="K333" s="13"/>
+      <c r="L333" s="13"/>
+      <c r="M333" s="13"/>
+      <c r="N333" s="13"/>
+      <c r="O333" s="14"/>
+    </row>
+    <row r="334" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A334" s="12"/>
+      <c r="B334" s="13"/>
+      <c r="C334" s="13"/>
+      <c r="D334" s="13"/>
+      <c r="E334" s="13"/>
+      <c r="F334" s="13"/>
+      <c r="G334" s="13"/>
+      <c r="H334" s="13"/>
+      <c r="I334" s="13"/>
+      <c r="J334" s="13"/>
+      <c r="K334" s="13"/>
+      <c r="L334" s="13"/>
+      <c r="M334" s="13"/>
+      <c r="N334" s="13"/>
+      <c r="O334" s="14"/>
+    </row>
+    <row r="335" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A335" s="15"/>
+      <c r="B335" s="16"/>
+      <c r="C335" s="16"/>
+      <c r="D335" s="16"/>
+      <c r="E335" s="16"/>
+      <c r="F335" s="16"/>
+      <c r="G335" s="16"/>
+      <c r="H335" s="16"/>
+      <c r="I335" s="16"/>
+      <c r="J335" s="16"/>
+      <c r="K335" s="16"/>
+      <c r="L335" s="16"/>
+      <c r="M335" s="16"/>
+      <c r="N335" s="16"/>
+      <c r="O335" s="17"/>
+    </row>
+    <row r="339" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A339" s="4"/>
+      <c r="B339" s="4"/>
+      <c r="C339" s="4"/>
+      <c r="D339" s="4"/>
+      <c r="E339" s="4"/>
+      <c r="F339" s="4"/>
+    </row>
+    <row r="340" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A340" s="4"/>
+      <c r="B340" s="4"/>
+      <c r="C340" s="4"/>
+      <c r="D340" s="4"/>
+      <c r="E340" s="4"/>
+      <c r="F340" s="4"/>
+    </row>
+    <row r="341" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A341" s="4"/>
+      <c r="B341" s="4"/>
+      <c r="C341" s="4"/>
+      <c r="D341" s="4"/>
+      <c r="E341" s="4"/>
+      <c r="F341" s="4"/>
+    </row>
+    <row r="342" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A342" s="4"/>
+      <c r="B342" s="4"/>
+      <c r="C342" s="4"/>
+      <c r="D342" s="4"/>
+      <c r="E342" s="4"/>
+      <c r="F342" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="J6:O14"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A52:O57"/>
-    <mergeCell ref="A59:O73"/>
+  <mergeCells count="26">
     <mergeCell ref="A1:G2"/>
     <mergeCell ref="H1:J2"/>
     <mergeCell ref="A6:F6"/>
     <mergeCell ref="A7:F10"/>
     <mergeCell ref="A11:F14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="B18:V23"/>
+    <mergeCell ref="J6:O14"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A52:O57"/>
+    <mergeCell ref="B25:U50"/>
     <mergeCell ref="D81:L91"/>
     <mergeCell ref="A75:C75"/>
     <mergeCell ref="D75:L75"/>
     <mergeCell ref="D76:L80"/>
-    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A59:O73"/>
+    <mergeCell ref="A152:V198"/>
+    <mergeCell ref="I118:W123"/>
+    <mergeCell ref="A118:F121"/>
+    <mergeCell ref="A123:B123"/>
+    <mergeCell ref="A125:U148"/>
+    <mergeCell ref="A310:O324"/>
+    <mergeCell ref="A325:O335"/>
+    <mergeCell ref="A276:M292"/>
+    <mergeCell ref="A202:U272"/>
+    <mergeCell ref="A295:O309"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" r:id="rId1"/>
